--- a/datakas.xlsx
+++ b/datakas.xlsx
@@ -5,43 +5,46 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C19A38-67F1-4ACD-967D-DBCD04CC65AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3437E1BC-0624-4DE2-AAF2-9AC1D6941D52}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="691" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="691" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Jan'26" sheetId="2" r:id="rId1"/>
-    <sheet name="Feb'26" sheetId="3" r:id="rId2"/>
-    <sheet name="Bazar" sheetId="5" r:id="rId3"/>
-    <sheet name="Mar'26" sheetId="4" r:id="rId4"/>
-    <sheet name="Apr'26" sheetId="6" r:id="rId5"/>
-    <sheet name="Mei'26" sheetId="7" r:id="rId6"/>
-    <sheet name="Juni'26" sheetId="8" r:id="rId7"/>
-    <sheet name="Juli'26" sheetId="9" r:id="rId8"/>
-    <sheet name="Agust'26" sheetId="10" r:id="rId9"/>
-    <sheet name="Rekap" sheetId="11" r:id="rId10"/>
+    <sheet name="kas" sheetId="13" r:id="rId1"/>
+    <sheet name="Jan'26" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Feb'26" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Bazar" sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="Mar'26" sheetId="4" state="hidden" r:id="rId5"/>
+    <sheet name="Apr'26" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Mei'26" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="Juni'26" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="Juli'26" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet name="Agust'26" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="Rekap" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Juni''26'!$A$3:$IV$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Mei''26'!$A$3:$IV$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Apr''26'!$A$1:$E$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Feb''26'!$A$1:$E$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Jan''26'!$A$1:$E$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Juni''26'!$A$1:$E$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mar''26'!$A$1:$E$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Mei''26'!$A$1:$E$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Jan''26'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Juni''26'!$3:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Juni''26'!$A$3:$IV$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Mei''26'!$A$3:$IV$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Apr''26'!$A$1:$E$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Feb''26'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Jan''26'!$A$1:$E$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Juni''26'!$A$1:$E$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">kas!$A$1:$E$104</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Mar''26'!$A$1:$E$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Mei''26'!$A$1:$E$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Jan''26'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Juni''26'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">kas!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="185">
   <si>
     <t>LAPORAN KEUANGAN RW.014 GRIYA PERMATA RAYA</t>
   </si>
@@ -853,7 +856,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1071,6 +1074,15 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1112,12 +1124,6 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1427,6 +1433,4095 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583D6716-2EEB-4658-B16A-98EE39ED985B}">
+  <dimension ref="A1:H104"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="62.85546875" style="24" customWidth="1"/>
+    <col min="3" max="4" width="17.42578125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="4" style="24" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="24" customWidth="1"/>
+    <col min="8" max="8" width="35.5703125" style="24" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="17" customFormat="1" ht="18" customHeight="1">
+      <c r="A1" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
+      <c r="A2" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="35">
+        <v>-334000</v>
+      </c>
+      <c r="D2" s="36"/>
+      <c r="E2" s="37">
+        <f>C2-F2</f>
+        <v>-334000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="19" customFormat="1" ht="30">
+      <c r="A3" s="86">
+        <v>46023</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75">
+        <v>100000</v>
+      </c>
+      <c r="E3" s="76">
+        <f t="shared" ref="E3:E33" si="0">E2+C3-D3</f>
+        <v>-434000</v>
+      </c>
+      <c r="G3" s="41"/>
+    </row>
+    <row r="4" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A4" s="87"/>
+      <c r="B4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74">
+        <v>90000</v>
+      </c>
+      <c r="E4" s="40">
+        <f t="shared" si="0"/>
+        <v>-524000</v>
+      </c>
+      <c r="G4" s="42"/>
+    </row>
+    <row r="5" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A5" s="88"/>
+      <c r="B5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74">
+        <v>40000</v>
+      </c>
+      <c r="E5" s="40">
+        <f t="shared" si="0"/>
+        <v>-564000</v>
+      </c>
+      <c r="G5" s="42"/>
+    </row>
+    <row r="6" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A6" s="10">
+        <v>46026</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74">
+        <v>51000</v>
+      </c>
+      <c r="E6" s="40">
+        <f t="shared" si="0"/>
+        <v>-615000</v>
+      </c>
+      <c r="G6" s="42"/>
+    </row>
+    <row r="7" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A7" s="86">
+        <v>46031</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="40">
+        <f t="shared" si="0"/>
+        <v>-620000</v>
+      </c>
+      <c r="G7" s="42"/>
+    </row>
+    <row r="8" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A8" s="88"/>
+      <c r="B8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="74">
+        <v>110000</v>
+      </c>
+      <c r="D8" s="74"/>
+      <c r="E8" s="40">
+        <f t="shared" si="0"/>
+        <v>-510000</v>
+      </c>
+      <c r="G8" s="42"/>
+    </row>
+    <row r="9" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A9" s="86">
+        <v>46033</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="74">
+        <v>600000</v>
+      </c>
+      <c r="D9" s="74"/>
+      <c r="E9" s="40">
+        <f t="shared" si="0"/>
+        <v>90000</v>
+      </c>
+      <c r="G9" s="42"/>
+    </row>
+    <row r="10" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A10" s="88"/>
+      <c r="B10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74">
+        <v>35000</v>
+      </c>
+      <c r="E10" s="40">
+        <f t="shared" si="0"/>
+        <v>55000</v>
+      </c>
+      <c r="G10" s="42"/>
+    </row>
+    <row r="11" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A11" s="10">
+        <v>46036</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74">
+        <v>250000</v>
+      </c>
+      <c r="E11" s="40">
+        <f t="shared" si="0"/>
+        <v>-195000</v>
+      </c>
+      <c r="G11" s="42"/>
+    </row>
+    <row r="12" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A12" s="86">
+        <v>46039</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="74">
+        <v>250000</v>
+      </c>
+      <c r="D12" s="74"/>
+      <c r="E12" s="40">
+        <f t="shared" si="0"/>
+        <v>55000</v>
+      </c>
+      <c r="G12" s="42"/>
+    </row>
+    <row r="13" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A13" s="88"/>
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="74">
+        <v>200000</v>
+      </c>
+      <c r="D13" s="74"/>
+      <c r="E13" s="40">
+        <f t="shared" si="0"/>
+        <v>255000</v>
+      </c>
+      <c r="G13" s="42"/>
+    </row>
+    <row r="14" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A14" s="86">
+        <v>46041</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74">
+        <v>45000</v>
+      </c>
+      <c r="E14" s="40">
+        <f t="shared" si="0"/>
+        <v>210000</v>
+      </c>
+      <c r="G14" s="42"/>
+    </row>
+    <row r="15" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A15" s="88"/>
+      <c r="B15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74">
+        <v>46500</v>
+      </c>
+      <c r="E15" s="40">
+        <f t="shared" si="0"/>
+        <v>163500</v>
+      </c>
+      <c r="G15" s="42"/>
+    </row>
+    <row r="16" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A16" s="10">
+        <v>46043</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74">
+        <v>150000</v>
+      </c>
+      <c r="E16" s="40">
+        <f t="shared" si="0"/>
+        <v>13500</v>
+      </c>
+      <c r="G16" s="42"/>
+    </row>
+    <row r="17" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A17" s="10">
+        <v>46046</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74">
+        <v>341000</v>
+      </c>
+      <c r="E17" s="40">
+        <f t="shared" si="0"/>
+        <v>-327500</v>
+      </c>
+      <c r="G17" s="44">
+        <v>126000</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A18" s="10">
+        <v>46047</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="74">
+        <v>926000</v>
+      </c>
+      <c r="D18" s="74"/>
+      <c r="E18" s="40">
+        <f t="shared" si="0"/>
+        <v>598500</v>
+      </c>
+      <c r="G18" s="44">
+        <v>932000</v>
+      </c>
+      <c r="H18" s="45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A19" s="86">
+        <v>46052</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="74">
+        <v>700000</v>
+      </c>
+      <c r="D19" s="74"/>
+      <c r="E19" s="40">
+        <f t="shared" si="0"/>
+        <v>1298500</v>
+      </c>
+      <c r="G19" s="44">
+        <v>257000</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A20" s="87"/>
+      <c r="B20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="74">
+        <v>760000</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="40">
+        <f t="shared" si="0"/>
+        <v>2058500</v>
+      </c>
+      <c r="G20" s="44">
+        <v>1400000</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
+      <c r="A21" s="88"/>
+      <c r="B21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74">
+        <v>46500</v>
+      </c>
+      <c r="E21" s="40">
+        <f t="shared" si="0"/>
+        <v>2012000</v>
+      </c>
+      <c r="G21" s="44">
+        <v>250000</v>
+      </c>
+      <c r="H21" s="45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="77">
+        <v>46057</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="9">
+        <v>110000</v>
+      </c>
+      <c r="D22" s="39"/>
+      <c r="E22" s="40">
+        <f t="shared" si="0"/>
+        <v>2122000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="77">
+        <v>46060</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="9">
+        <v>354000</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="40">
+        <f t="shared" si="0"/>
+        <v>2476000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="86">
+        <v>46064</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9">
+        <v>250000</v>
+      </c>
+      <c r="E24" s="40">
+        <f t="shared" si="0"/>
+        <v>2226000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="88"/>
+      <c r="B25" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="9">
+        <v>130000</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="40">
+        <f t="shared" si="0"/>
+        <v>2356000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="77">
+        <v>46066</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9">
+        <v>26000</v>
+      </c>
+      <c r="E26" s="40">
+        <f t="shared" si="0"/>
+        <v>2330000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="77">
+        <v>46071</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9">
+        <v>775000</v>
+      </c>
+      <c r="E27" s="40">
+        <f t="shared" si="0"/>
+        <v>1555000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="86">
+        <v>46072</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="9">
+        <v>250000</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="40">
+        <f t="shared" si="0"/>
+        <v>1805000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="88"/>
+      <c r="B29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9">
+        <v>53000</v>
+      </c>
+      <c r="E29" s="40">
+        <f t="shared" si="0"/>
+        <v>1752000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="10">
+        <v>46074</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="9">
+        <v>1183000</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="40">
+        <f t="shared" si="0"/>
+        <v>2935000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="10">
+        <v>46080</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9">
+        <v>37000</v>
+      </c>
+      <c r="E31" s="40">
+        <f t="shared" si="0"/>
+        <v>2898000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="86">
+        <v>46081</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="9">
+        <v>700000</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="40">
+        <f t="shared" si="0"/>
+        <v>3598000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="88"/>
+      <c r="B33" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="9">
+        <v>400000</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="40">
+        <f t="shared" si="0"/>
+        <v>3998000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="77">
+        <v>46082</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="39">
+        <v>52000</v>
+      </c>
+      <c r="E34" s="40">
+        <f>E33+C34-D34</f>
+        <v>3946000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="77">
+        <v>46083</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="9">
+        <v>110000</v>
+      </c>
+      <c r="D35" s="9"/>
+      <c r="E35" s="40">
+        <f t="shared" ref="E35:E53" si="1">E34+C35-D35</f>
+        <v>4056000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="86">
+        <v>46084</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="9">
+        <v>97000</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="40">
+        <f t="shared" si="1"/>
+        <v>4153000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="88"/>
+      <c r="B37" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9">
+        <v>50000</v>
+      </c>
+      <c r="E37" s="40">
+        <f t="shared" si="1"/>
+        <v>4103000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="77">
+        <v>46085</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9">
+        <v>25000</v>
+      </c>
+      <c r="E38" s="40">
+        <f t="shared" si="1"/>
+        <v>4078000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="77">
+        <v>46086</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9">
+        <v>53000</v>
+      </c>
+      <c r="E39" s="40">
+        <f t="shared" si="1"/>
+        <v>4025000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="77">
+        <v>46092</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9">
+        <v>250000</v>
+      </c>
+      <c r="E40" s="40">
+        <f t="shared" si="1"/>
+        <v>3775000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="77">
+        <v>46095</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="9">
+        <v>250000</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="40">
+        <f t="shared" si="1"/>
+        <v>4025000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="86">
+        <v>46096</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9">
+        <v>45000</v>
+      </c>
+      <c r="E42" s="40">
+        <f t="shared" si="1"/>
+        <v>3980000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="88"/>
+      <c r="B43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="9">
+        <v>701000</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="40">
+        <f t="shared" si="1"/>
+        <v>4681000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="91">
+        <v>46101</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9">
+        <v>50000</v>
+      </c>
+      <c r="E44" s="40">
+        <f t="shared" si="1"/>
+        <v>4631000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="91"/>
+      <c r="B45" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="9">
+        <v>1689000</v>
+      </c>
+      <c r="D45" s="9"/>
+      <c r="E45" s="40">
+        <f t="shared" si="1"/>
+        <v>6320000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="87">
+        <v>46107</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9">
+        <v>20000</v>
+      </c>
+      <c r="E46" s="40">
+        <f t="shared" si="1"/>
+        <v>6300000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="87"/>
+      <c r="B47" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9">
+        <v>40000</v>
+      </c>
+      <c r="E47" s="40">
+        <f t="shared" si="1"/>
+        <v>6260000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="88"/>
+      <c r="B48" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9">
+        <v>2000000</v>
+      </c>
+      <c r="E48" s="40">
+        <f t="shared" si="1"/>
+        <v>4260000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="87">
+        <v>46109</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9">
+        <v>24000</v>
+      </c>
+      <c r="E49" s="40">
+        <f t="shared" si="1"/>
+        <v>4236000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="88"/>
+      <c r="B50" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9">
+        <v>36000</v>
+      </c>
+      <c r="E50" s="40">
+        <f t="shared" si="1"/>
+        <v>4200000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="77">
+        <v>46110</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9">
+        <v>44500</v>
+      </c>
+      <c r="E51" s="40">
+        <f t="shared" si="1"/>
+        <v>4155500</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="86">
+        <v>46112</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" s="9">
+        <v>700000</v>
+      </c>
+      <c r="D52" s="9"/>
+      <c r="E52" s="40">
+        <f t="shared" si="1"/>
+        <v>4855500</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="88"/>
+      <c r="B53" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" s="9">
+        <v>300000</v>
+      </c>
+      <c r="D53" s="9"/>
+      <c r="E53" s="40">
+        <f t="shared" si="1"/>
+        <v>5155500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="77">
+        <v>46114</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="9">
+        <v>110000</v>
+      </c>
+      <c r="D54" s="39"/>
+      <c r="E54" s="40">
+        <f>E53+C54-D54</f>
+        <v>5265500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="77">
+        <v>46118</v>
+      </c>
+      <c r="B55" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9">
+        <v>250000</v>
+      </c>
+      <c r="E55" s="40">
+        <f t="shared" ref="E55:E104" si="2">E54+C55-D55</f>
+        <v>5015500</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="77">
+        <v>46122</v>
+      </c>
+      <c r="B56" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9">
+        <v>46500</v>
+      </c>
+      <c r="E56" s="40">
+        <f t="shared" si="2"/>
+        <v>4969000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="77">
+        <v>46130</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="9">
+        <v>1080000</v>
+      </c>
+      <c r="D57" s="9"/>
+      <c r="E57" s="40">
+        <f t="shared" si="2"/>
+        <v>6049000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="77">
+        <v>46131</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9">
+        <v>55500</v>
+      </c>
+      <c r="E58" s="40">
+        <f t="shared" si="2"/>
+        <v>5993500</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="86">
+        <v>46132</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="9">
+        <v>250000</v>
+      </c>
+      <c r="D59" s="9"/>
+      <c r="E59" s="40">
+        <f t="shared" si="2"/>
+        <v>6243500</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="88"/>
+      <c r="B60" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9">
+        <v>60000</v>
+      </c>
+      <c r="E60" s="40">
+        <f t="shared" si="2"/>
+        <v>6183500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="77">
+        <v>46134</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9">
+        <v>200000</v>
+      </c>
+      <c r="E61" s="40">
+        <f t="shared" si="2"/>
+        <v>5983500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="77">
+        <v>46136</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="9">
+        <v>189000</v>
+      </c>
+      <c r="D62" s="9"/>
+      <c r="E62" s="40">
+        <f t="shared" si="2"/>
+        <v>6172500</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="77">
+        <v>46140</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9">
+        <v>140000</v>
+      </c>
+      <c r="E63" s="40">
+        <f t="shared" si="2"/>
+        <v>6032500</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="77">
+        <v>46144</v>
+      </c>
+      <c r="B64" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="9">
+        <v>110000</v>
+      </c>
+      <c r="D64" s="39"/>
+      <c r="E64" s="40">
+        <f t="shared" si="2"/>
+        <v>6142500</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="86">
+        <v>46145</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="9">
+        <v>700000</v>
+      </c>
+      <c r="D65" s="9"/>
+      <c r="E65" s="40">
+        <f t="shared" si="2"/>
+        <v>6842500</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="88"/>
+      <c r="B66" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" s="9">
+        <v>480000</v>
+      </c>
+      <c r="D66" s="9"/>
+      <c r="E66" s="40">
+        <f t="shared" si="2"/>
+        <v>7322500</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="77">
+        <v>46147</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9">
+        <v>57000</v>
+      </c>
+      <c r="E67" s="40">
+        <f t="shared" si="2"/>
+        <v>7265500</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="86">
+        <v>46148</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9">
+        <v>916000</v>
+      </c>
+      <c r="E68" s="40">
+        <f t="shared" si="2"/>
+        <v>6349500</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="88"/>
+      <c r="B69" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9">
+        <v>42500</v>
+      </c>
+      <c r="E69" s="40">
+        <f t="shared" si="2"/>
+        <v>6307000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="86">
+        <v>46151</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9">
+        <v>100000</v>
+      </c>
+      <c r="E70" s="40">
+        <f t="shared" si="2"/>
+        <v>6207000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="88"/>
+      <c r="B71" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9">
+        <v>20000</v>
+      </c>
+      <c r="E71" s="40">
+        <f t="shared" si="2"/>
+        <v>6187000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="77">
+        <v>46154</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9">
+        <v>34000</v>
+      </c>
+      <c r="E72" s="40">
+        <f t="shared" si="2"/>
+        <v>6153000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="86">
+        <v>46155</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9">
+        <v>250000</v>
+      </c>
+      <c r="E73" s="40">
+        <f t="shared" si="2"/>
+        <v>5903000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="88"/>
+      <c r="B74" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9">
+        <v>1000000</v>
+      </c>
+      <c r="E74" s="40">
+        <f t="shared" si="2"/>
+        <v>4903000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="86">
+        <v>46158</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" s="9">
+        <v>1045000</v>
+      </c>
+      <c r="D75" s="9"/>
+      <c r="E75" s="40">
+        <f t="shared" si="2"/>
+        <v>5948000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="88"/>
+      <c r="B76" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C76" s="9">
+        <v>250000</v>
+      </c>
+      <c r="D76" s="9"/>
+      <c r="E76" s="40">
+        <f t="shared" si="2"/>
+        <v>6198000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="77">
+        <v>46160</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="9">
+        <v>100000</v>
+      </c>
+      <c r="D77" s="9"/>
+      <c r="E77" s="40">
+        <f t="shared" si="2"/>
+        <v>6298000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="77">
+        <v>46162</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9">
+        <v>25000</v>
+      </c>
+      <c r="E78" s="40">
+        <f t="shared" si="2"/>
+        <v>6273000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="86">
+        <v>46165</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9">
+        <v>51000</v>
+      </c>
+      <c r="E79" s="40">
+        <f t="shared" si="2"/>
+        <v>6222000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="88"/>
+      <c r="B80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="9">
+        <v>115000</v>
+      </c>
+      <c r="D80" s="9"/>
+      <c r="E80" s="40">
+        <f t="shared" si="2"/>
+        <v>6337000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="77">
+        <v>46175</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C81" s="9">
+        <v>700000</v>
+      </c>
+      <c r="D81" s="39"/>
+      <c r="E81" s="40">
+        <f t="shared" si="2"/>
+        <v>7037000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="79"/>
+      <c r="B82" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C82" s="9">
+        <v>460000</v>
+      </c>
+      <c r="D82" s="9"/>
+      <c r="E82" s="40">
+        <f t="shared" si="2"/>
+        <v>7497000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="61"/>
+      <c r="B83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" s="9">
+        <v>150000</v>
+      </c>
+      <c r="D83" s="9"/>
+      <c r="E83" s="40">
+        <f t="shared" si="2"/>
+        <v>7647000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="63">
+        <v>46176</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9">
+        <v>42500</v>
+      </c>
+      <c r="E84" s="40">
+        <f t="shared" si="2"/>
+        <v>7604500</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="63">
+        <v>46177</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" s="9">
+        <v>110000</v>
+      </c>
+      <c r="D85" s="9"/>
+      <c r="E85" s="40">
+        <f t="shared" si="2"/>
+        <v>7714500</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="63">
+        <v>46178</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9">
+        <v>18000</v>
+      </c>
+      <c r="E86" s="40">
+        <f t="shared" si="2"/>
+        <v>7696500</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="77">
+        <v>46180</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" s="9">
+        <v>204000</v>
+      </c>
+      <c r="D87" s="9"/>
+      <c r="E87" s="40">
+        <f t="shared" si="2"/>
+        <v>7900500</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="64">
+        <v>46182</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9">
+        <v>250000</v>
+      </c>
+      <c r="E88" s="40">
+        <f t="shared" si="2"/>
+        <v>7650500</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="64">
+        <v>46183</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C89" s="9">
+        <v>200000</v>
+      </c>
+      <c r="D89" s="9"/>
+      <c r="E89" s="40">
+        <f t="shared" si="2"/>
+        <v>7850500</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="43"/>
+      <c r="B90" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C90" s="9">
+        <v>230000</v>
+      </c>
+      <c r="D90" s="9"/>
+      <c r="E90" s="40">
+        <f t="shared" si="2"/>
+        <v>8080500</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="43"/>
+      <c r="B91" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C91" s="9">
+        <v>250000</v>
+      </c>
+      <c r="D91" s="9"/>
+      <c r="E91" s="40">
+        <f t="shared" si="2"/>
+        <v>8330500</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="43"/>
+      <c r="B92" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C92" s="9">
+        <v>225000</v>
+      </c>
+      <c r="D92" s="9"/>
+      <c r="E92" s="40">
+        <f t="shared" si="2"/>
+        <v>8555500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="43"/>
+      <c r="B93" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C93" s="9">
+        <v>350000</v>
+      </c>
+      <c r="D93" s="9"/>
+      <c r="E93" s="40">
+        <f t="shared" si="2"/>
+        <v>8905500</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="43"/>
+      <c r="B94" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C94" s="9">
+        <v>230000</v>
+      </c>
+      <c r="D94" s="9"/>
+      <c r="E94" s="40">
+        <f t="shared" si="2"/>
+        <v>9135500</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="43"/>
+      <c r="B95" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C95" s="9">
+        <v>370000</v>
+      </c>
+      <c r="D95" s="9"/>
+      <c r="E95" s="40">
+        <f t="shared" si="2"/>
+        <v>9505500</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="77">
+        <v>46186</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9">
+        <v>60000</v>
+      </c>
+      <c r="E96" s="40">
+        <f t="shared" si="2"/>
+        <v>9445500</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="77">
+        <v>46187</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" s="9">
+        <v>250000</v>
+      </c>
+      <c r="D97" s="9"/>
+      <c r="E97" s="40">
+        <f t="shared" si="2"/>
+        <v>9695500</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="77">
+        <v>46191</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="9">
+        <v>100000</v>
+      </c>
+      <c r="D98" s="9"/>
+      <c r="E98" s="40">
+        <f t="shared" si="2"/>
+        <v>9795500</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="77">
+        <v>46193</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9">
+        <v>26000</v>
+      </c>
+      <c r="E99" s="40">
+        <f t="shared" si="2"/>
+        <v>9769500</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="77">
+        <v>46196</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9">
+        <v>2300000</v>
+      </c>
+      <c r="E100" s="40">
+        <f t="shared" si="2"/>
+        <v>7469500</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="77">
+        <v>46197</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9">
+        <v>25500</v>
+      </c>
+      <c r="E101" s="40">
+        <f t="shared" si="2"/>
+        <v>7444000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="63">
+        <v>46200</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C102" s="9">
+        <v>990000</v>
+      </c>
+      <c r="D102" s="9"/>
+      <c r="E102" s="40">
+        <f t="shared" si="2"/>
+        <v>8434000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="63">
+        <v>46203</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C103" s="9">
+        <v>700000</v>
+      </c>
+      <c r="D103" s="9"/>
+      <c r="E103" s="40">
+        <f t="shared" si="2"/>
+        <v>9134000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="61"/>
+      <c r="B104" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C104" s="9">
+        <v>500000</v>
+      </c>
+      <c r="D104" s="9"/>
+      <c r="E104" s="40">
+        <f t="shared" si="2"/>
+        <v>9634000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A12:A13"/>
+  </mergeCells>
+  <pageMargins left="1" right="0.5" top="0.75" bottom="0.75" header="0.30972222222222201" footer="0.30972222222222201"/>
+  <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="34" max="4" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:IV26"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" style="23" customWidth="1"/>
+    <col min="2" max="2" width="62.85546875" style="24" customWidth="1"/>
+    <col min="3" max="4" width="17.42578125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="4" style="24" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="24" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="24" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18" customHeight="1">
+      <c r="A1" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="80"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1">
+      <c r="A2" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+    </row>
+    <row r="3" spans="1:8" s="17" customFormat="1" ht="18" customHeight="1">
+      <c r="A3" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
+      <c r="A4" s="82" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="35">
+        <f>'Apr''26'!E15</f>
+        <v>6032500</v>
+      </c>
+      <c r="D4" s="36"/>
+      <c r="E4" s="37">
+        <f>C4-F4</f>
+        <v>6032500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="19" customFormat="1" ht="21" customHeight="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="40">
+        <f t="shared" ref="E5:E14" si="0">E4+C5-D5</f>
+        <v>6032500</v>
+      </c>
+      <c r="G5" s="41"/>
+    </row>
+    <row r="6" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
+      <c r="A6" s="86"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="40">
+        <f t="shared" si="0"/>
+        <v>6032500</v>
+      </c>
+      <c r="G6" s="42"/>
+    </row>
+    <row r="7" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
+      <c r="A7" s="88"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="40">
+        <f t="shared" si="0"/>
+        <v>6032500</v>
+      </c>
+      <c r="G7" s="42"/>
+    </row>
+    <row r="8" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="40">
+        <f t="shared" si="0"/>
+        <v>6032500</v>
+      </c>
+      <c r="G8" s="42"/>
+    </row>
+    <row r="9" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
+      <c r="A9" s="11"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="40">
+        <f t="shared" si="0"/>
+        <v>6032500</v>
+      </c>
+      <c r="G9" s="42"/>
+    </row>
+    <row r="10" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="40">
+        <f t="shared" si="0"/>
+        <v>6032500</v>
+      </c>
+      <c r="G10" s="44">
+        <v>126000</v>
+      </c>
+      <c r="H10" s="45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
+      <c r="A11" s="43"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="40">
+        <f t="shared" si="0"/>
+        <v>6032500</v>
+      </c>
+      <c r="G11" s="44">
+        <v>932000</v>
+      </c>
+      <c r="H11" s="45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
+      <c r="A12" s="11"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="40">
+        <f t="shared" si="0"/>
+        <v>6032500</v>
+      </c>
+      <c r="G12" s="44">
+        <v>257000</v>
+      </c>
+      <c r="H12" s="45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
+      <c r="A13" s="11"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="40">
+        <f t="shared" si="0"/>
+        <v>6032500</v>
+      </c>
+      <c r="G13" s="44">
+        <v>1400000</v>
+      </c>
+      <c r="H13" s="45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
+      <c r="A14" s="10"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="40">
+        <f t="shared" si="0"/>
+        <v>6032500</v>
+      </c>
+      <c r="G14" s="44">
+        <v>250000</v>
+      </c>
+      <c r="H14" s="45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A15" s="83" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="83"/>
+      <c r="C15" s="46">
+        <f>SUM(C4:C14)</f>
+        <v>6032500</v>
+      </c>
+      <c r="D15" s="46">
+        <f>SUM(D4:D14)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="37">
+        <f>C15-D15</f>
+        <v>6032500</v>
+      </c>
+      <c r="G15" s="44">
+        <f>SUM(G10:G14)</f>
+        <v>2965000</v>
+      </c>
+      <c r="H15" s="47"/>
+    </row>
+    <row r="16" spans="1:8" s="22" customFormat="1" ht="6.75" customHeight="1">
+      <c r="A16" s="48"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="50"/>
+    </row>
+    <row r="17" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A17" s="84" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="84"/>
+      <c r="C17" s="51">
+        <f>C15-C4</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="49"/>
+      <c r="E17" s="50"/>
+      <c r="G17" s="52">
+        <f>E15-G15</f>
+        <v>3067500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:256" s="22" customFormat="1" ht="5.25" customHeight="1">
+      <c r="A18" s="53"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="50"/>
+    </row>
+    <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A19" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="85"/>
+      <c r="C19" s="54">
+        <f>D15</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="49"/>
+      <c r="E19" s="50"/>
+    </row>
+    <row r="20" spans="1:256" ht="24" customHeight="1">
+      <c r="A20" s="55"/>
+      <c r="D20" s="56"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57">
+        <v>4357500</v>
+      </c>
+      <c r="H20" s="57">
+        <f>G17-G20</f>
+        <v>-1290000</v>
+      </c>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="57"/>
+      <c r="S20" s="57"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="57"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="57"/>
+      <c r="Y20" s="57"/>
+      <c r="Z20" s="57"/>
+      <c r="AA20" s="57"/>
+      <c r="AB20" s="57"/>
+      <c r="AC20" s="57"/>
+      <c r="AD20" s="57"/>
+      <c r="AE20" s="57"/>
+      <c r="AF20" s="57"/>
+      <c r="AG20" s="57"/>
+      <c r="AH20" s="57"/>
+      <c r="AI20" s="57"/>
+      <c r="AJ20" s="57"/>
+      <c r="AK20" s="57"/>
+      <c r="AL20" s="57"/>
+      <c r="AM20" s="57"/>
+      <c r="AN20" s="57"/>
+      <c r="AO20" s="57"/>
+      <c r="AP20" s="57"/>
+      <c r="AQ20" s="57"/>
+      <c r="AR20" s="57"/>
+      <c r="AS20" s="57"/>
+      <c r="AT20" s="57"/>
+      <c r="AU20" s="57"/>
+      <c r="AV20" s="57"/>
+      <c r="AW20" s="57"/>
+      <c r="AX20" s="57"/>
+      <c r="AY20" s="57"/>
+      <c r="AZ20" s="57"/>
+      <c r="BA20" s="57"/>
+      <c r="BB20" s="57"/>
+      <c r="BC20" s="57"/>
+      <c r="BD20" s="57"/>
+      <c r="BE20" s="57"/>
+      <c r="BF20" s="57"/>
+      <c r="BG20" s="57"/>
+      <c r="BH20" s="57"/>
+      <c r="BI20" s="57"/>
+      <c r="BJ20" s="57"/>
+      <c r="BK20" s="57"/>
+      <c r="BL20" s="57"/>
+      <c r="BM20" s="57"/>
+      <c r="BN20" s="57"/>
+      <c r="BO20" s="57"/>
+      <c r="BP20" s="57"/>
+      <c r="BQ20" s="57"/>
+      <c r="BR20" s="57"/>
+      <c r="BS20" s="57"/>
+      <c r="BT20" s="57"/>
+      <c r="BU20" s="57"/>
+      <c r="BV20" s="57"/>
+      <c r="BW20" s="57"/>
+      <c r="BX20" s="57"/>
+      <c r="BY20" s="57"/>
+      <c r="BZ20" s="57"/>
+      <c r="CA20" s="57"/>
+      <c r="CB20" s="57"/>
+      <c r="CC20" s="57"/>
+      <c r="CD20" s="57"/>
+      <c r="CE20" s="57"/>
+      <c r="CF20" s="57"/>
+      <c r="CG20" s="57"/>
+      <c r="CH20" s="57"/>
+      <c r="CI20" s="57"/>
+      <c r="CJ20" s="57"/>
+      <c r="CK20" s="57"/>
+      <c r="CL20" s="57"/>
+      <c r="CM20" s="57"/>
+      <c r="CN20" s="57"/>
+      <c r="CO20" s="57"/>
+      <c r="CP20" s="57"/>
+      <c r="CQ20" s="57"/>
+      <c r="CR20" s="57"/>
+      <c r="CS20" s="57"/>
+      <c r="CT20" s="57"/>
+      <c r="CU20" s="57"/>
+      <c r="CV20" s="57"/>
+      <c r="CW20" s="57"/>
+      <c r="CX20" s="57"/>
+      <c r="CY20" s="57"/>
+      <c r="CZ20" s="57"/>
+      <c r="DA20" s="57"/>
+      <c r="DB20" s="57"/>
+      <c r="DC20" s="57"/>
+      <c r="DD20" s="57"/>
+      <c r="DE20" s="57"/>
+      <c r="DF20" s="57"/>
+      <c r="DG20" s="57"/>
+      <c r="DH20" s="57"/>
+      <c r="DI20" s="57"/>
+      <c r="DJ20" s="57"/>
+      <c r="DK20" s="57"/>
+      <c r="DL20" s="57"/>
+      <c r="DM20" s="57"/>
+      <c r="DN20" s="57"/>
+      <c r="DO20" s="57"/>
+      <c r="DP20" s="57"/>
+      <c r="DQ20" s="57"/>
+      <c r="DR20" s="57"/>
+      <c r="DS20" s="57"/>
+      <c r="DT20" s="57"/>
+      <c r="DU20" s="57"/>
+      <c r="DV20" s="57"/>
+      <c r="DW20" s="57"/>
+      <c r="DX20" s="57"/>
+      <c r="DY20" s="57"/>
+      <c r="DZ20" s="57"/>
+      <c r="EA20" s="57"/>
+      <c r="EB20" s="57"/>
+      <c r="EC20" s="57"/>
+      <c r="ED20" s="57"/>
+      <c r="EE20" s="57"/>
+      <c r="EF20" s="57"/>
+      <c r="EG20" s="57"/>
+      <c r="EH20" s="57"/>
+      <c r="EI20" s="57"/>
+      <c r="EJ20" s="57"/>
+      <c r="EK20" s="57"/>
+      <c r="EL20" s="57"/>
+      <c r="EM20" s="57"/>
+      <c r="EN20" s="57"/>
+      <c r="EO20" s="57"/>
+      <c r="EP20" s="57"/>
+      <c r="EQ20" s="57"/>
+      <c r="ER20" s="57"/>
+      <c r="ES20" s="57"/>
+      <c r="ET20" s="57"/>
+      <c r="EU20" s="57"/>
+      <c r="EV20" s="57"/>
+      <c r="EW20" s="57"/>
+      <c r="EX20" s="57"/>
+      <c r="EY20" s="57"/>
+      <c r="EZ20" s="57"/>
+      <c r="FA20" s="57"/>
+      <c r="FB20" s="57"/>
+      <c r="FC20" s="57"/>
+      <c r="FD20" s="57"/>
+      <c r="FE20" s="57"/>
+      <c r="FF20" s="57"/>
+      <c r="FG20" s="57"/>
+      <c r="FH20" s="57"/>
+      <c r="FI20" s="57"/>
+      <c r="FJ20" s="57"/>
+      <c r="FK20" s="57"/>
+      <c r="FL20" s="57"/>
+      <c r="FM20" s="57"/>
+      <c r="FN20" s="57"/>
+      <c r="FO20" s="57"/>
+      <c r="FP20" s="57"/>
+      <c r="FQ20" s="57"/>
+      <c r="FR20" s="57"/>
+      <c r="FS20" s="57"/>
+      <c r="FT20" s="57"/>
+      <c r="FU20" s="57"/>
+      <c r="FV20" s="57"/>
+      <c r="FW20" s="57"/>
+      <c r="FX20" s="57"/>
+      <c r="FY20" s="57"/>
+      <c r="FZ20" s="57"/>
+      <c r="GA20" s="57"/>
+      <c r="GB20" s="57"/>
+      <c r="GC20" s="57"/>
+      <c r="GD20" s="57"/>
+      <c r="GE20" s="57"/>
+      <c r="GF20" s="57"/>
+      <c r="GG20" s="57"/>
+      <c r="GH20" s="57"/>
+      <c r="GI20" s="57"/>
+      <c r="GJ20" s="57"/>
+      <c r="GK20" s="57"/>
+      <c r="GL20" s="57"/>
+      <c r="GM20" s="57"/>
+      <c r="GN20" s="57"/>
+      <c r="GO20" s="57"/>
+      <c r="GP20" s="57"/>
+      <c r="GQ20" s="57"/>
+      <c r="GR20" s="57"/>
+      <c r="GS20" s="57"/>
+      <c r="GT20" s="57"/>
+      <c r="GU20" s="57"/>
+      <c r="GV20" s="57"/>
+      <c r="GW20" s="57"/>
+      <c r="GX20" s="57"/>
+      <c r="GY20" s="57"/>
+      <c r="GZ20" s="57"/>
+      <c r="HA20" s="57"/>
+      <c r="HB20" s="57"/>
+      <c r="HC20" s="57"/>
+      <c r="HD20" s="57"/>
+      <c r="HE20" s="57"/>
+      <c r="HF20" s="57"/>
+      <c r="HG20" s="57"/>
+      <c r="HH20" s="57"/>
+      <c r="HI20" s="57"/>
+      <c r="HJ20" s="57"/>
+      <c r="HK20" s="57"/>
+      <c r="HL20" s="57"/>
+      <c r="HM20" s="57"/>
+      <c r="HN20" s="57"/>
+      <c r="HO20" s="57"/>
+      <c r="HP20" s="57"/>
+      <c r="HQ20" s="57"/>
+      <c r="HR20" s="57"/>
+      <c r="HS20" s="57"/>
+      <c r="HT20" s="57"/>
+      <c r="HU20" s="57"/>
+      <c r="HV20" s="57"/>
+      <c r="HW20" s="57"/>
+      <c r="HX20" s="57"/>
+      <c r="HY20" s="57"/>
+      <c r="HZ20" s="57"/>
+      <c r="IA20" s="57"/>
+      <c r="IB20" s="57"/>
+      <c r="IC20" s="57"/>
+      <c r="ID20" s="57"/>
+      <c r="IE20" s="57"/>
+      <c r="IF20" s="57"/>
+      <c r="IG20" s="57"/>
+      <c r="IH20" s="57"/>
+      <c r="II20" s="57"/>
+      <c r="IJ20" s="57"/>
+      <c r="IK20" s="57"/>
+      <c r="IL20" s="57"/>
+      <c r="IM20" s="57"/>
+      <c r="IN20" s="57"/>
+      <c r="IO20" s="57"/>
+      <c r="IP20" s="57"/>
+      <c r="IQ20" s="57"/>
+      <c r="IR20" s="57"/>
+      <c r="IS20" s="57"/>
+      <c r="IT20" s="57"/>
+      <c r="IU20" s="57"/>
+      <c r="IV20" s="57"/>
+    </row>
+    <row r="21" spans="1:256">
+      <c r="A21" s="55"/>
+      <c r="D21" s="56" t="s">
+        <v>172</v>
+      </c>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="57"/>
+      <c r="V21" s="57"/>
+      <c r="W21" s="57"/>
+      <c r="X21" s="57"/>
+      <c r="Y21" s="57"/>
+      <c r="Z21" s="57"/>
+      <c r="AA21" s="57"/>
+      <c r="AB21" s="57"/>
+      <c r="AC21" s="57"/>
+      <c r="AD21" s="57"/>
+      <c r="AE21" s="57"/>
+      <c r="AF21" s="57"/>
+      <c r="AG21" s="57"/>
+      <c r="AH21" s="57"/>
+      <c r="AI21" s="57"/>
+      <c r="AJ21" s="57"/>
+      <c r="AK21" s="57"/>
+      <c r="AL21" s="57"/>
+      <c r="AM21" s="57"/>
+      <c r="AN21" s="57"/>
+      <c r="AO21" s="57"/>
+      <c r="AP21" s="57"/>
+      <c r="AQ21" s="57"/>
+      <c r="AR21" s="57"/>
+      <c r="AS21" s="57"/>
+      <c r="AT21" s="57"/>
+      <c r="AU21" s="57"/>
+      <c r="AV21" s="57"/>
+      <c r="AW21" s="57"/>
+      <c r="AX21" s="57"/>
+      <c r="AY21" s="57"/>
+      <c r="AZ21" s="57"/>
+      <c r="BA21" s="57"/>
+      <c r="BB21" s="57"/>
+      <c r="BC21" s="57"/>
+      <c r="BD21" s="57"/>
+      <c r="BE21" s="57"/>
+      <c r="BF21" s="57"/>
+      <c r="BG21" s="57"/>
+      <c r="BH21" s="57"/>
+      <c r="BI21" s="57"/>
+      <c r="BJ21" s="57"/>
+      <c r="BK21" s="57"/>
+      <c r="BL21" s="57"/>
+      <c r="BM21" s="57"/>
+      <c r="BN21" s="57"/>
+      <c r="BO21" s="57"/>
+      <c r="BP21" s="57"/>
+      <c r="BQ21" s="57"/>
+      <c r="BR21" s="57"/>
+      <c r="BS21" s="57"/>
+      <c r="BT21" s="57"/>
+      <c r="BU21" s="57"/>
+      <c r="BV21" s="57"/>
+      <c r="BW21" s="57"/>
+      <c r="BX21" s="57"/>
+      <c r="BY21" s="57"/>
+      <c r="BZ21" s="57"/>
+      <c r="CA21" s="57"/>
+      <c r="CB21" s="57"/>
+      <c r="CC21" s="57"/>
+      <c r="CD21" s="57"/>
+      <c r="CE21" s="57"/>
+      <c r="CF21" s="57"/>
+      <c r="CG21" s="57"/>
+      <c r="CH21" s="57"/>
+      <c r="CI21" s="57"/>
+      <c r="CJ21" s="57"/>
+      <c r="CK21" s="57"/>
+      <c r="CL21" s="57"/>
+      <c r="CM21" s="57"/>
+      <c r="CN21" s="57"/>
+      <c r="CO21" s="57"/>
+      <c r="CP21" s="57"/>
+      <c r="CQ21" s="57"/>
+      <c r="CR21" s="57"/>
+      <c r="CS21" s="57"/>
+      <c r="CT21" s="57"/>
+      <c r="CU21" s="57"/>
+      <c r="CV21" s="57"/>
+      <c r="CW21" s="57"/>
+      <c r="CX21" s="57"/>
+      <c r="CY21" s="57"/>
+      <c r="CZ21" s="57"/>
+      <c r="DA21" s="57"/>
+      <c r="DB21" s="57"/>
+      <c r="DC21" s="57"/>
+      <c r="DD21" s="57"/>
+      <c r="DE21" s="57"/>
+      <c r="DF21" s="57"/>
+      <c r="DG21" s="57"/>
+      <c r="DH21" s="57"/>
+      <c r="DI21" s="57"/>
+      <c r="DJ21" s="57"/>
+      <c r="DK21" s="57"/>
+      <c r="DL21" s="57"/>
+      <c r="DM21" s="57"/>
+      <c r="DN21" s="57"/>
+      <c r="DO21" s="57"/>
+      <c r="DP21" s="57"/>
+      <c r="DQ21" s="57"/>
+      <c r="DR21" s="57"/>
+      <c r="DS21" s="57"/>
+      <c r="DT21" s="57"/>
+      <c r="DU21" s="57"/>
+      <c r="DV21" s="57"/>
+      <c r="DW21" s="57"/>
+      <c r="DX21" s="57"/>
+      <c r="DY21" s="57"/>
+      <c r="DZ21" s="57"/>
+      <c r="EA21" s="57"/>
+      <c r="EB21" s="57"/>
+      <c r="EC21" s="57"/>
+      <c r="ED21" s="57"/>
+      <c r="EE21" s="57"/>
+      <c r="EF21" s="57"/>
+      <c r="EG21" s="57"/>
+      <c r="EH21" s="57"/>
+      <c r="EI21" s="57"/>
+      <c r="EJ21" s="57"/>
+      <c r="EK21" s="57"/>
+      <c r="EL21" s="57"/>
+      <c r="EM21" s="57"/>
+      <c r="EN21" s="57"/>
+      <c r="EO21" s="57"/>
+      <c r="EP21" s="57"/>
+      <c r="EQ21" s="57"/>
+      <c r="ER21" s="57"/>
+      <c r="ES21" s="57"/>
+      <c r="ET21" s="57"/>
+      <c r="EU21" s="57"/>
+      <c r="EV21" s="57"/>
+      <c r="EW21" s="57"/>
+      <c r="EX21" s="57"/>
+      <c r="EY21" s="57"/>
+      <c r="EZ21" s="57"/>
+      <c r="FA21" s="57"/>
+      <c r="FB21" s="57"/>
+      <c r="FC21" s="57"/>
+      <c r="FD21" s="57"/>
+      <c r="FE21" s="57"/>
+      <c r="FF21" s="57"/>
+      <c r="FG21" s="57"/>
+      <c r="FH21" s="57"/>
+      <c r="FI21" s="57"/>
+      <c r="FJ21" s="57"/>
+      <c r="FK21" s="57"/>
+      <c r="FL21" s="57"/>
+      <c r="FM21" s="57"/>
+      <c r="FN21" s="57"/>
+      <c r="FO21" s="57"/>
+      <c r="FP21" s="57"/>
+      <c r="FQ21" s="57"/>
+      <c r="FR21" s="57"/>
+      <c r="FS21" s="57"/>
+      <c r="FT21" s="57"/>
+      <c r="FU21" s="57"/>
+      <c r="FV21" s="57"/>
+      <c r="FW21" s="57"/>
+      <c r="FX21" s="57"/>
+      <c r="FY21" s="57"/>
+      <c r="FZ21" s="57"/>
+      <c r="GA21" s="57"/>
+      <c r="GB21" s="57"/>
+      <c r="GC21" s="57"/>
+      <c r="GD21" s="57"/>
+      <c r="GE21" s="57"/>
+      <c r="GF21" s="57"/>
+      <c r="GG21" s="57"/>
+      <c r="GH21" s="57"/>
+      <c r="GI21" s="57"/>
+      <c r="GJ21" s="57"/>
+      <c r="GK21" s="57"/>
+      <c r="GL21" s="57"/>
+      <c r="GM21" s="57"/>
+      <c r="GN21" s="57"/>
+      <c r="GO21" s="57"/>
+      <c r="GP21" s="57"/>
+      <c r="GQ21" s="57"/>
+      <c r="GR21" s="57"/>
+      <c r="GS21" s="57"/>
+      <c r="GT21" s="57"/>
+      <c r="GU21" s="57"/>
+      <c r="GV21" s="57"/>
+      <c r="GW21" s="57"/>
+      <c r="GX21" s="57"/>
+      <c r="GY21" s="57"/>
+      <c r="GZ21" s="57"/>
+      <c r="HA21" s="57"/>
+      <c r="HB21" s="57"/>
+      <c r="HC21" s="57"/>
+      <c r="HD21" s="57"/>
+      <c r="HE21" s="57"/>
+      <c r="HF21" s="57"/>
+      <c r="HG21" s="57"/>
+      <c r="HH21" s="57"/>
+      <c r="HI21" s="57"/>
+      <c r="HJ21" s="57"/>
+      <c r="HK21" s="57"/>
+      <c r="HL21" s="57"/>
+      <c r="HM21" s="57"/>
+      <c r="HN21" s="57"/>
+      <c r="HO21" s="57"/>
+      <c r="HP21" s="57"/>
+      <c r="HQ21" s="57"/>
+      <c r="HR21" s="57"/>
+      <c r="HS21" s="57"/>
+      <c r="HT21" s="57"/>
+      <c r="HU21" s="57"/>
+      <c r="HV21" s="57"/>
+      <c r="HW21" s="57"/>
+      <c r="HX21" s="57"/>
+      <c r="HY21" s="57"/>
+      <c r="HZ21" s="57"/>
+      <c r="IA21" s="57"/>
+      <c r="IB21" s="57"/>
+      <c r="IC21" s="57"/>
+      <c r="ID21" s="57"/>
+      <c r="IE21" s="57"/>
+      <c r="IF21" s="57"/>
+      <c r="IG21" s="57"/>
+      <c r="IH21" s="57"/>
+      <c r="II21" s="57"/>
+      <c r="IJ21" s="57"/>
+      <c r="IK21" s="57"/>
+      <c r="IL21" s="57"/>
+      <c r="IM21" s="57"/>
+      <c r="IN21" s="57"/>
+      <c r="IO21" s="57"/>
+      <c r="IP21" s="57"/>
+      <c r="IQ21" s="57"/>
+      <c r="IR21" s="57"/>
+      <c r="IS21" s="57"/>
+      <c r="IT21" s="57"/>
+      <c r="IU21" s="57"/>
+      <c r="IV21" s="57"/>
+    </row>
+    <row r="22" spans="1:256">
+      <c r="A22" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="57"/>
+      <c r="Q22" s="57"/>
+      <c r="R22" s="57"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="57"/>
+      <c r="V22" s="57"/>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="57"/>
+      <c r="AG22" s="57"/>
+      <c r="AH22" s="57"/>
+      <c r="AI22" s="57"/>
+      <c r="AJ22" s="57"/>
+      <c r="AK22" s="57"/>
+      <c r="AL22" s="57"/>
+      <c r="AM22" s="57"/>
+      <c r="AN22" s="57"/>
+      <c r="AO22" s="57"/>
+      <c r="AP22" s="57"/>
+      <c r="AQ22" s="57"/>
+      <c r="AR22" s="57"/>
+      <c r="AS22" s="57"/>
+      <c r="AT22" s="57"/>
+      <c r="AU22" s="57"/>
+      <c r="AV22" s="57"/>
+      <c r="AW22" s="57"/>
+      <c r="AX22" s="57"/>
+      <c r="AY22" s="57"/>
+      <c r="AZ22" s="57"/>
+      <c r="BA22" s="57"/>
+      <c r="BB22" s="57"/>
+      <c r="BC22" s="57"/>
+      <c r="BD22" s="57"/>
+      <c r="BE22" s="57"/>
+      <c r="BF22" s="57"/>
+      <c r="BG22" s="57"/>
+      <c r="BH22" s="57"/>
+      <c r="BI22" s="57"/>
+      <c r="BJ22" s="57"/>
+      <c r="BK22" s="57"/>
+      <c r="BL22" s="57"/>
+      <c r="BM22" s="57"/>
+      <c r="BN22" s="57"/>
+      <c r="BO22" s="57"/>
+      <c r="BP22" s="57"/>
+      <c r="BQ22" s="57"/>
+      <c r="BR22" s="57"/>
+      <c r="BS22" s="57"/>
+      <c r="BT22" s="57"/>
+      <c r="BU22" s="57"/>
+      <c r="BV22" s="57"/>
+      <c r="BW22" s="57"/>
+      <c r="BX22" s="57"/>
+      <c r="BY22" s="57"/>
+      <c r="BZ22" s="57"/>
+      <c r="CA22" s="57"/>
+      <c r="CB22" s="57"/>
+      <c r="CC22" s="57"/>
+      <c r="CD22" s="57"/>
+      <c r="CE22" s="57"/>
+      <c r="CF22" s="57"/>
+      <c r="CG22" s="57"/>
+      <c r="CH22" s="57"/>
+      <c r="CI22" s="57"/>
+      <c r="CJ22" s="57"/>
+      <c r="CK22" s="57"/>
+      <c r="CL22" s="57"/>
+      <c r="CM22" s="57"/>
+      <c r="CN22" s="57"/>
+      <c r="CO22" s="57"/>
+      <c r="CP22" s="57"/>
+      <c r="CQ22" s="57"/>
+      <c r="CR22" s="57"/>
+      <c r="CS22" s="57"/>
+      <c r="CT22" s="57"/>
+      <c r="CU22" s="57"/>
+      <c r="CV22" s="57"/>
+      <c r="CW22" s="57"/>
+      <c r="CX22" s="57"/>
+      <c r="CY22" s="57"/>
+      <c r="CZ22" s="57"/>
+      <c r="DA22" s="57"/>
+      <c r="DB22" s="57"/>
+      <c r="DC22" s="57"/>
+      <c r="DD22" s="57"/>
+      <c r="DE22" s="57"/>
+      <c r="DF22" s="57"/>
+      <c r="DG22" s="57"/>
+      <c r="DH22" s="57"/>
+      <c r="DI22" s="57"/>
+      <c r="DJ22" s="57"/>
+      <c r="DK22" s="57"/>
+      <c r="DL22" s="57"/>
+      <c r="DM22" s="57"/>
+      <c r="DN22" s="57"/>
+      <c r="DO22" s="57"/>
+      <c r="DP22" s="57"/>
+      <c r="DQ22" s="57"/>
+      <c r="DR22" s="57"/>
+      <c r="DS22" s="57"/>
+      <c r="DT22" s="57"/>
+      <c r="DU22" s="57"/>
+      <c r="DV22" s="57"/>
+      <c r="DW22" s="57"/>
+      <c r="DX22" s="57"/>
+      <c r="DY22" s="57"/>
+      <c r="DZ22" s="57"/>
+      <c r="EA22" s="57"/>
+      <c r="EB22" s="57"/>
+      <c r="EC22" s="57"/>
+      <c r="ED22" s="57"/>
+      <c r="EE22" s="57"/>
+      <c r="EF22" s="57"/>
+      <c r="EG22" s="57"/>
+      <c r="EH22" s="57"/>
+      <c r="EI22" s="57"/>
+      <c r="EJ22" s="57"/>
+      <c r="EK22" s="57"/>
+      <c r="EL22" s="57"/>
+      <c r="EM22" s="57"/>
+      <c r="EN22" s="57"/>
+      <c r="EO22" s="57"/>
+      <c r="EP22" s="57"/>
+      <c r="EQ22" s="57"/>
+      <c r="ER22" s="57"/>
+      <c r="ES22" s="57"/>
+      <c r="ET22" s="57"/>
+      <c r="EU22" s="57"/>
+      <c r="EV22" s="57"/>
+      <c r="EW22" s="57"/>
+      <c r="EX22" s="57"/>
+      <c r="EY22" s="57"/>
+      <c r="EZ22" s="57"/>
+      <c r="FA22" s="57"/>
+      <c r="FB22" s="57"/>
+      <c r="FC22" s="57"/>
+      <c r="FD22" s="57"/>
+      <c r="FE22" s="57"/>
+      <c r="FF22" s="57"/>
+      <c r="FG22" s="57"/>
+      <c r="FH22" s="57"/>
+      <c r="FI22" s="57"/>
+      <c r="FJ22" s="57"/>
+      <c r="FK22" s="57"/>
+      <c r="FL22" s="57"/>
+      <c r="FM22" s="57"/>
+      <c r="FN22" s="57"/>
+      <c r="FO22" s="57"/>
+      <c r="FP22" s="57"/>
+      <c r="FQ22" s="57"/>
+      <c r="FR22" s="57"/>
+      <c r="FS22" s="57"/>
+      <c r="FT22" s="57"/>
+      <c r="FU22" s="57"/>
+      <c r="FV22" s="57"/>
+      <c r="FW22" s="57"/>
+      <c r="FX22" s="57"/>
+      <c r="FY22" s="57"/>
+      <c r="FZ22" s="57"/>
+      <c r="GA22" s="57"/>
+      <c r="GB22" s="57"/>
+      <c r="GC22" s="57"/>
+      <c r="GD22" s="57"/>
+      <c r="GE22" s="57"/>
+      <c r="GF22" s="57"/>
+      <c r="GG22" s="57"/>
+      <c r="GH22" s="57"/>
+      <c r="GI22" s="57"/>
+      <c r="GJ22" s="57"/>
+      <c r="GK22" s="57"/>
+      <c r="GL22" s="57"/>
+      <c r="GM22" s="57"/>
+      <c r="GN22" s="57"/>
+      <c r="GO22" s="57"/>
+      <c r="GP22" s="57"/>
+      <c r="GQ22" s="57"/>
+      <c r="GR22" s="57"/>
+      <c r="GS22" s="57"/>
+      <c r="GT22" s="57"/>
+      <c r="GU22" s="57"/>
+      <c r="GV22" s="57"/>
+      <c r="GW22" s="57"/>
+      <c r="GX22" s="57"/>
+      <c r="GY22" s="57"/>
+      <c r="GZ22" s="57"/>
+      <c r="HA22" s="57"/>
+      <c r="HB22" s="57"/>
+      <c r="HC22" s="57"/>
+      <c r="HD22" s="57"/>
+      <c r="HE22" s="57"/>
+      <c r="HF22" s="57"/>
+      <c r="HG22" s="57"/>
+      <c r="HH22" s="57"/>
+      <c r="HI22" s="57"/>
+      <c r="HJ22" s="57"/>
+      <c r="HK22" s="57"/>
+      <c r="HL22" s="57"/>
+      <c r="HM22" s="57"/>
+      <c r="HN22" s="57"/>
+      <c r="HO22" s="57"/>
+      <c r="HP22" s="57"/>
+      <c r="HQ22" s="57"/>
+      <c r="HR22" s="57"/>
+      <c r="HS22" s="57"/>
+      <c r="HT22" s="57"/>
+      <c r="HU22" s="57"/>
+      <c r="HV22" s="57"/>
+      <c r="HW22" s="57"/>
+      <c r="HX22" s="57"/>
+      <c r="HY22" s="57"/>
+      <c r="HZ22" s="57"/>
+      <c r="IA22" s="57"/>
+      <c r="IB22" s="57"/>
+      <c r="IC22" s="57"/>
+      <c r="ID22" s="57"/>
+      <c r="IE22" s="57"/>
+      <c r="IF22" s="57"/>
+      <c r="IG22" s="57"/>
+      <c r="IH22" s="57"/>
+      <c r="II22" s="57"/>
+      <c r="IJ22" s="57"/>
+      <c r="IK22" s="57"/>
+      <c r="IL22" s="57"/>
+      <c r="IM22" s="57"/>
+      <c r="IN22" s="57"/>
+      <c r="IO22" s="57"/>
+      <c r="IP22" s="57"/>
+      <c r="IQ22" s="57"/>
+      <c r="IR22" s="57"/>
+      <c r="IS22" s="57"/>
+      <c r="IT22" s="57"/>
+      <c r="IU22" s="57"/>
+      <c r="IV22" s="57"/>
+    </row>
+    <row r="23" spans="1:256">
+      <c r="A23" s="58"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="57"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="57"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="57"/>
+      <c r="V23" s="57"/>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="57"/>
+      <c r="AG23" s="57"/>
+      <c r="AH23" s="57"/>
+      <c r="AI23" s="57"/>
+      <c r="AJ23" s="57"/>
+      <c r="AK23" s="57"/>
+      <c r="AL23" s="57"/>
+      <c r="AM23" s="57"/>
+      <c r="AN23" s="57"/>
+      <c r="AO23" s="57"/>
+      <c r="AP23" s="57"/>
+      <c r="AQ23" s="57"/>
+      <c r="AR23" s="57"/>
+      <c r="AS23" s="57"/>
+      <c r="AT23" s="57"/>
+      <c r="AU23" s="57"/>
+      <c r="AV23" s="57"/>
+      <c r="AW23" s="57"/>
+      <c r="AX23" s="57"/>
+      <c r="AY23" s="57"/>
+      <c r="AZ23" s="57"/>
+      <c r="BA23" s="57"/>
+      <c r="BB23" s="57"/>
+      <c r="BC23" s="57"/>
+      <c r="BD23" s="57"/>
+      <c r="BE23" s="57"/>
+      <c r="BF23" s="57"/>
+      <c r="BG23" s="57"/>
+      <c r="BH23" s="57"/>
+      <c r="BI23" s="57"/>
+      <c r="BJ23" s="57"/>
+      <c r="BK23" s="57"/>
+      <c r="BL23" s="57"/>
+      <c r="BM23" s="57"/>
+      <c r="BN23" s="57"/>
+      <c r="BO23" s="57"/>
+      <c r="BP23" s="57"/>
+      <c r="BQ23" s="57"/>
+      <c r="BR23" s="57"/>
+      <c r="BS23" s="57"/>
+      <c r="BT23" s="57"/>
+      <c r="BU23" s="57"/>
+      <c r="BV23" s="57"/>
+      <c r="BW23" s="57"/>
+      <c r="BX23" s="57"/>
+      <c r="BY23" s="57"/>
+      <c r="BZ23" s="57"/>
+      <c r="CA23" s="57"/>
+      <c r="CB23" s="57"/>
+      <c r="CC23" s="57"/>
+      <c r="CD23" s="57"/>
+      <c r="CE23" s="57"/>
+      <c r="CF23" s="57"/>
+      <c r="CG23" s="57"/>
+      <c r="CH23" s="57"/>
+      <c r="CI23" s="57"/>
+      <c r="CJ23" s="57"/>
+      <c r="CK23" s="57"/>
+      <c r="CL23" s="57"/>
+      <c r="CM23" s="57"/>
+      <c r="CN23" s="57"/>
+      <c r="CO23" s="57"/>
+      <c r="CP23" s="57"/>
+      <c r="CQ23" s="57"/>
+      <c r="CR23" s="57"/>
+      <c r="CS23" s="57"/>
+      <c r="CT23" s="57"/>
+      <c r="CU23" s="57"/>
+      <c r="CV23" s="57"/>
+      <c r="CW23" s="57"/>
+      <c r="CX23" s="57"/>
+      <c r="CY23" s="57"/>
+      <c r="CZ23" s="57"/>
+      <c r="DA23" s="57"/>
+      <c r="DB23" s="57"/>
+      <c r="DC23" s="57"/>
+      <c r="DD23" s="57"/>
+      <c r="DE23" s="57"/>
+      <c r="DF23" s="57"/>
+      <c r="DG23" s="57"/>
+      <c r="DH23" s="57"/>
+      <c r="DI23" s="57"/>
+      <c r="DJ23" s="57"/>
+      <c r="DK23" s="57"/>
+      <c r="DL23" s="57"/>
+      <c r="DM23" s="57"/>
+      <c r="DN23" s="57"/>
+      <c r="DO23" s="57"/>
+      <c r="DP23" s="57"/>
+      <c r="DQ23" s="57"/>
+      <c r="DR23" s="57"/>
+      <c r="DS23" s="57"/>
+      <c r="DT23" s="57"/>
+      <c r="DU23" s="57"/>
+      <c r="DV23" s="57"/>
+      <c r="DW23" s="57"/>
+      <c r="DX23" s="57"/>
+      <c r="DY23" s="57"/>
+      <c r="DZ23" s="57"/>
+      <c r="EA23" s="57"/>
+      <c r="EB23" s="57"/>
+      <c r="EC23" s="57"/>
+      <c r="ED23" s="57"/>
+      <c r="EE23" s="57"/>
+      <c r="EF23" s="57"/>
+      <c r="EG23" s="57"/>
+      <c r="EH23" s="57"/>
+      <c r="EI23" s="57"/>
+      <c r="EJ23" s="57"/>
+      <c r="EK23" s="57"/>
+      <c r="EL23" s="57"/>
+      <c r="EM23" s="57"/>
+      <c r="EN23" s="57"/>
+      <c r="EO23" s="57"/>
+      <c r="EP23" s="57"/>
+      <c r="EQ23" s="57"/>
+      <c r="ER23" s="57"/>
+      <c r="ES23" s="57"/>
+      <c r="ET23" s="57"/>
+      <c r="EU23" s="57"/>
+      <c r="EV23" s="57"/>
+      <c r="EW23" s="57"/>
+      <c r="EX23" s="57"/>
+      <c r="EY23" s="57"/>
+      <c r="EZ23" s="57"/>
+      <c r="FA23" s="57"/>
+      <c r="FB23" s="57"/>
+      <c r="FC23" s="57"/>
+      <c r="FD23" s="57"/>
+      <c r="FE23" s="57"/>
+      <c r="FF23" s="57"/>
+      <c r="FG23" s="57"/>
+      <c r="FH23" s="57"/>
+      <c r="FI23" s="57"/>
+      <c r="FJ23" s="57"/>
+      <c r="FK23" s="57"/>
+      <c r="FL23" s="57"/>
+      <c r="FM23" s="57"/>
+      <c r="FN23" s="57"/>
+      <c r="FO23" s="57"/>
+      <c r="FP23" s="57"/>
+      <c r="FQ23" s="57"/>
+      <c r="FR23" s="57"/>
+      <c r="FS23" s="57"/>
+      <c r="FT23" s="57"/>
+      <c r="FU23" s="57"/>
+      <c r="FV23" s="57"/>
+      <c r="FW23" s="57"/>
+      <c r="FX23" s="57"/>
+      <c r="FY23" s="57"/>
+      <c r="FZ23" s="57"/>
+      <c r="GA23" s="57"/>
+      <c r="GB23" s="57"/>
+      <c r="GC23" s="57"/>
+      <c r="GD23" s="57"/>
+      <c r="GE23" s="57"/>
+      <c r="GF23" s="57"/>
+      <c r="GG23" s="57"/>
+      <c r="GH23" s="57"/>
+      <c r="GI23" s="57"/>
+      <c r="GJ23" s="57"/>
+      <c r="GK23" s="57"/>
+      <c r="GL23" s="57"/>
+      <c r="GM23" s="57"/>
+      <c r="GN23" s="57"/>
+      <c r="GO23" s="57"/>
+      <c r="GP23" s="57"/>
+      <c r="GQ23" s="57"/>
+      <c r="GR23" s="57"/>
+      <c r="GS23" s="57"/>
+      <c r="GT23" s="57"/>
+      <c r="GU23" s="57"/>
+      <c r="GV23" s="57"/>
+      <c r="GW23" s="57"/>
+      <c r="GX23" s="57"/>
+      <c r="GY23" s="57"/>
+      <c r="GZ23" s="57"/>
+      <c r="HA23" s="57"/>
+      <c r="HB23" s="57"/>
+      <c r="HC23" s="57"/>
+      <c r="HD23" s="57"/>
+      <c r="HE23" s="57"/>
+      <c r="HF23" s="57"/>
+      <c r="HG23" s="57"/>
+      <c r="HH23" s="57"/>
+      <c r="HI23" s="57"/>
+      <c r="HJ23" s="57"/>
+      <c r="HK23" s="57"/>
+      <c r="HL23" s="57"/>
+      <c r="HM23" s="57"/>
+      <c r="HN23" s="57"/>
+      <c r="HO23" s="57"/>
+      <c r="HP23" s="57"/>
+      <c r="HQ23" s="57"/>
+      <c r="HR23" s="57"/>
+      <c r="HS23" s="57"/>
+      <c r="HT23" s="57"/>
+      <c r="HU23" s="57"/>
+      <c r="HV23" s="57"/>
+      <c r="HW23" s="57"/>
+      <c r="HX23" s="57"/>
+      <c r="HY23" s="57"/>
+      <c r="HZ23" s="57"/>
+      <c r="IA23" s="57"/>
+      <c r="IB23" s="57"/>
+      <c r="IC23" s="57"/>
+      <c r="ID23" s="57"/>
+      <c r="IE23" s="57"/>
+      <c r="IF23" s="57"/>
+      <c r="IG23" s="57"/>
+      <c r="IH23" s="57"/>
+      <c r="II23" s="57"/>
+      <c r="IJ23" s="57"/>
+      <c r="IK23" s="57"/>
+      <c r="IL23" s="57"/>
+      <c r="IM23" s="57"/>
+      <c r="IN23" s="57"/>
+      <c r="IO23" s="57"/>
+      <c r="IP23" s="57"/>
+      <c r="IQ23" s="57"/>
+      <c r="IR23" s="57"/>
+      <c r="IS23" s="57"/>
+      <c r="IT23" s="57"/>
+      <c r="IU23" s="57"/>
+      <c r="IV23" s="57"/>
+    </row>
+    <row r="24" spans="1:256">
+      <c r="A24" s="58"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="57"/>
+      <c r="P24" s="57"/>
+      <c r="Q24" s="57"/>
+      <c r="R24" s="57"/>
+      <c r="S24" s="57"/>
+      <c r="T24" s="57"/>
+      <c r="U24" s="57"/>
+      <c r="V24" s="57"/>
+      <c r="W24" s="57"/>
+      <c r="X24" s="57"/>
+      <c r="Y24" s="57"/>
+      <c r="Z24" s="57"/>
+      <c r="AA24" s="57"/>
+      <c r="AB24" s="57"/>
+      <c r="AC24" s="57"/>
+      <c r="AD24" s="57"/>
+      <c r="AE24" s="57"/>
+      <c r="AF24" s="57"/>
+      <c r="AG24" s="57"/>
+      <c r="AH24" s="57"/>
+      <c r="AI24" s="57"/>
+      <c r="AJ24" s="57"/>
+      <c r="AK24" s="57"/>
+      <c r="AL24" s="57"/>
+      <c r="AM24" s="57"/>
+      <c r="AN24" s="57"/>
+      <c r="AO24" s="57"/>
+      <c r="AP24" s="57"/>
+      <c r="AQ24" s="57"/>
+      <c r="AR24" s="57"/>
+      <c r="AS24" s="57"/>
+      <c r="AT24" s="57"/>
+      <c r="AU24" s="57"/>
+      <c r="AV24" s="57"/>
+      <c r="AW24" s="57"/>
+      <c r="AX24" s="57"/>
+      <c r="AY24" s="57"/>
+      <c r="AZ24" s="57"/>
+      <c r="BA24" s="57"/>
+      <c r="BB24" s="57"/>
+      <c r="BC24" s="57"/>
+      <c r="BD24" s="57"/>
+      <c r="BE24" s="57"/>
+      <c r="BF24" s="57"/>
+      <c r="BG24" s="57"/>
+      <c r="BH24" s="57"/>
+      <c r="BI24" s="57"/>
+      <c r="BJ24" s="57"/>
+      <c r="BK24" s="57"/>
+      <c r="BL24" s="57"/>
+      <c r="BM24" s="57"/>
+      <c r="BN24" s="57"/>
+      <c r="BO24" s="57"/>
+      <c r="BP24" s="57"/>
+      <c r="BQ24" s="57"/>
+      <c r="BR24" s="57"/>
+      <c r="BS24" s="57"/>
+      <c r="BT24" s="57"/>
+      <c r="BU24" s="57"/>
+      <c r="BV24" s="57"/>
+      <c r="BW24" s="57"/>
+      <c r="BX24" s="57"/>
+      <c r="BY24" s="57"/>
+      <c r="BZ24" s="57"/>
+      <c r="CA24" s="57"/>
+      <c r="CB24" s="57"/>
+      <c r="CC24" s="57"/>
+      <c r="CD24" s="57"/>
+      <c r="CE24" s="57"/>
+      <c r="CF24" s="57"/>
+      <c r="CG24" s="57"/>
+      <c r="CH24" s="57"/>
+      <c r="CI24" s="57"/>
+      <c r="CJ24" s="57"/>
+      <c r="CK24" s="57"/>
+      <c r="CL24" s="57"/>
+      <c r="CM24" s="57"/>
+      <c r="CN24" s="57"/>
+      <c r="CO24" s="57"/>
+      <c r="CP24" s="57"/>
+      <c r="CQ24" s="57"/>
+      <c r="CR24" s="57"/>
+      <c r="CS24" s="57"/>
+      <c r="CT24" s="57"/>
+      <c r="CU24" s="57"/>
+      <c r="CV24" s="57"/>
+      <c r="CW24" s="57"/>
+      <c r="CX24" s="57"/>
+      <c r="CY24" s="57"/>
+      <c r="CZ24" s="57"/>
+      <c r="DA24" s="57"/>
+      <c r="DB24" s="57"/>
+      <c r="DC24" s="57"/>
+      <c r="DD24" s="57"/>
+      <c r="DE24" s="57"/>
+      <c r="DF24" s="57"/>
+      <c r="DG24" s="57"/>
+      <c r="DH24" s="57"/>
+      <c r="DI24" s="57"/>
+      <c r="DJ24" s="57"/>
+      <c r="DK24" s="57"/>
+      <c r="DL24" s="57"/>
+      <c r="DM24" s="57"/>
+      <c r="DN24" s="57"/>
+      <c r="DO24" s="57"/>
+      <c r="DP24" s="57"/>
+      <c r="DQ24" s="57"/>
+      <c r="DR24" s="57"/>
+      <c r="DS24" s="57"/>
+      <c r="DT24" s="57"/>
+      <c r="DU24" s="57"/>
+      <c r="DV24" s="57"/>
+      <c r="DW24" s="57"/>
+      <c r="DX24" s="57"/>
+      <c r="DY24" s="57"/>
+      <c r="DZ24" s="57"/>
+      <c r="EA24" s="57"/>
+      <c r="EB24" s="57"/>
+      <c r="EC24" s="57"/>
+      <c r="ED24" s="57"/>
+      <c r="EE24" s="57"/>
+      <c r="EF24" s="57"/>
+      <c r="EG24" s="57"/>
+      <c r="EH24" s="57"/>
+      <c r="EI24" s="57"/>
+      <c r="EJ24" s="57"/>
+      <c r="EK24" s="57"/>
+      <c r="EL24" s="57"/>
+      <c r="EM24" s="57"/>
+      <c r="EN24" s="57"/>
+      <c r="EO24" s="57"/>
+      <c r="EP24" s="57"/>
+      <c r="EQ24" s="57"/>
+      <c r="ER24" s="57"/>
+      <c r="ES24" s="57"/>
+      <c r="ET24" s="57"/>
+      <c r="EU24" s="57"/>
+      <c r="EV24" s="57"/>
+      <c r="EW24" s="57"/>
+      <c r="EX24" s="57"/>
+      <c r="EY24" s="57"/>
+      <c r="EZ24" s="57"/>
+      <c r="FA24" s="57"/>
+      <c r="FB24" s="57"/>
+      <c r="FC24" s="57"/>
+      <c r="FD24" s="57"/>
+      <c r="FE24" s="57"/>
+      <c r="FF24" s="57"/>
+      <c r="FG24" s="57"/>
+      <c r="FH24" s="57"/>
+      <c r="FI24" s="57"/>
+      <c r="FJ24" s="57"/>
+      <c r="FK24" s="57"/>
+      <c r="FL24" s="57"/>
+      <c r="FM24" s="57"/>
+      <c r="FN24" s="57"/>
+      <c r="FO24" s="57"/>
+      <c r="FP24" s="57"/>
+      <c r="FQ24" s="57"/>
+      <c r="FR24" s="57"/>
+      <c r="FS24" s="57"/>
+      <c r="FT24" s="57"/>
+      <c r="FU24" s="57"/>
+      <c r="FV24" s="57"/>
+      <c r="FW24" s="57"/>
+      <c r="FX24" s="57"/>
+      <c r="FY24" s="57"/>
+      <c r="FZ24" s="57"/>
+      <c r="GA24" s="57"/>
+      <c r="GB24" s="57"/>
+      <c r="GC24" s="57"/>
+      <c r="GD24" s="57"/>
+      <c r="GE24" s="57"/>
+      <c r="GF24" s="57"/>
+      <c r="GG24" s="57"/>
+      <c r="GH24" s="57"/>
+      <c r="GI24" s="57"/>
+      <c r="GJ24" s="57"/>
+      <c r="GK24" s="57"/>
+      <c r="GL24" s="57"/>
+      <c r="GM24" s="57"/>
+      <c r="GN24" s="57"/>
+      <c r="GO24" s="57"/>
+      <c r="GP24" s="57"/>
+      <c r="GQ24" s="57"/>
+      <c r="GR24" s="57"/>
+      <c r="GS24" s="57"/>
+      <c r="GT24" s="57"/>
+      <c r="GU24" s="57"/>
+      <c r="GV24" s="57"/>
+      <c r="GW24" s="57"/>
+      <c r="GX24" s="57"/>
+      <c r="GY24" s="57"/>
+      <c r="GZ24" s="57"/>
+      <c r="HA24" s="57"/>
+      <c r="HB24" s="57"/>
+      <c r="HC24" s="57"/>
+      <c r="HD24" s="57"/>
+      <c r="HE24" s="57"/>
+      <c r="HF24" s="57"/>
+      <c r="HG24" s="57"/>
+      <c r="HH24" s="57"/>
+      <c r="HI24" s="57"/>
+      <c r="HJ24" s="57"/>
+      <c r="HK24" s="57"/>
+      <c r="HL24" s="57"/>
+      <c r="HM24" s="57"/>
+      <c r="HN24" s="57"/>
+      <c r="HO24" s="57"/>
+      <c r="HP24" s="57"/>
+      <c r="HQ24" s="57"/>
+      <c r="HR24" s="57"/>
+      <c r="HS24" s="57"/>
+      <c r="HT24" s="57"/>
+      <c r="HU24" s="57"/>
+      <c r="HV24" s="57"/>
+      <c r="HW24" s="57"/>
+      <c r="HX24" s="57"/>
+      <c r="HY24" s="57"/>
+      <c r="HZ24" s="57"/>
+      <c r="IA24" s="57"/>
+      <c r="IB24" s="57"/>
+      <c r="IC24" s="57"/>
+      <c r="ID24" s="57"/>
+      <c r="IE24" s="57"/>
+      <c r="IF24" s="57"/>
+      <c r="IG24" s="57"/>
+      <c r="IH24" s="57"/>
+      <c r="II24" s="57"/>
+      <c r="IJ24" s="57"/>
+      <c r="IK24" s="57"/>
+      <c r="IL24" s="57"/>
+      <c r="IM24" s="57"/>
+      <c r="IN24" s="57"/>
+      <c r="IO24" s="57"/>
+      <c r="IP24" s="57"/>
+      <c r="IQ24" s="57"/>
+      <c r="IR24" s="57"/>
+      <c r="IS24" s="57"/>
+      <c r="IT24" s="57"/>
+      <c r="IU24" s="57"/>
+      <c r="IV24" s="57"/>
+    </row>
+    <row r="25" spans="1:256" ht="17.25">
+      <c r="A25" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
+      <c r="P25" s="57"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="57"/>
+      <c r="S25" s="57"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="57"/>
+      <c r="V25" s="57"/>
+      <c r="W25" s="57"/>
+      <c r="X25" s="57"/>
+      <c r="Y25" s="57"/>
+      <c r="Z25" s="57"/>
+      <c r="AA25" s="57"/>
+      <c r="AB25" s="57"/>
+      <c r="AC25" s="57"/>
+      <c r="AD25" s="57"/>
+      <c r="AE25" s="57"/>
+      <c r="AF25" s="57"/>
+      <c r="AG25" s="57"/>
+      <c r="AH25" s="57"/>
+      <c r="AI25" s="57"/>
+      <c r="AJ25" s="57"/>
+      <c r="AK25" s="57"/>
+      <c r="AL25" s="57"/>
+      <c r="AM25" s="57"/>
+      <c r="AN25" s="57"/>
+      <c r="AO25" s="57"/>
+      <c r="AP25" s="57"/>
+      <c r="AQ25" s="57"/>
+      <c r="AR25" s="57"/>
+      <c r="AS25" s="57"/>
+      <c r="AT25" s="57"/>
+      <c r="AU25" s="57"/>
+      <c r="AV25" s="57"/>
+      <c r="AW25" s="57"/>
+      <c r="AX25" s="57"/>
+      <c r="AY25" s="57"/>
+      <c r="AZ25" s="57"/>
+      <c r="BA25" s="57"/>
+      <c r="BB25" s="57"/>
+      <c r="BC25" s="57"/>
+      <c r="BD25" s="57"/>
+      <c r="BE25" s="57"/>
+      <c r="BF25" s="57"/>
+      <c r="BG25" s="57"/>
+      <c r="BH25" s="57"/>
+      <c r="BI25" s="57"/>
+      <c r="BJ25" s="57"/>
+      <c r="BK25" s="57"/>
+      <c r="BL25" s="57"/>
+      <c r="BM25" s="57"/>
+      <c r="BN25" s="57"/>
+      <c r="BO25" s="57"/>
+      <c r="BP25" s="57"/>
+      <c r="BQ25" s="57"/>
+      <c r="BR25" s="57"/>
+      <c r="BS25" s="57"/>
+      <c r="BT25" s="57"/>
+      <c r="BU25" s="57"/>
+      <c r="BV25" s="57"/>
+      <c r="BW25" s="57"/>
+      <c r="BX25" s="57"/>
+      <c r="BY25" s="57"/>
+      <c r="BZ25" s="57"/>
+      <c r="CA25" s="57"/>
+      <c r="CB25" s="57"/>
+      <c r="CC25" s="57"/>
+      <c r="CD25" s="57"/>
+      <c r="CE25" s="57"/>
+      <c r="CF25" s="57"/>
+      <c r="CG25" s="57"/>
+      <c r="CH25" s="57"/>
+      <c r="CI25" s="57"/>
+      <c r="CJ25" s="57"/>
+      <c r="CK25" s="57"/>
+      <c r="CL25" s="57"/>
+      <c r="CM25" s="57"/>
+      <c r="CN25" s="57"/>
+      <c r="CO25" s="57"/>
+      <c r="CP25" s="57"/>
+      <c r="CQ25" s="57"/>
+      <c r="CR25" s="57"/>
+      <c r="CS25" s="57"/>
+      <c r="CT25" s="57"/>
+      <c r="CU25" s="57"/>
+      <c r="CV25" s="57"/>
+      <c r="CW25" s="57"/>
+      <c r="CX25" s="57"/>
+      <c r="CY25" s="57"/>
+      <c r="CZ25" s="57"/>
+      <c r="DA25" s="57"/>
+      <c r="DB25" s="57"/>
+      <c r="DC25" s="57"/>
+      <c r="DD25" s="57"/>
+      <c r="DE25" s="57"/>
+      <c r="DF25" s="57"/>
+      <c r="DG25" s="57"/>
+      <c r="DH25" s="57"/>
+      <c r="DI25" s="57"/>
+      <c r="DJ25" s="57"/>
+      <c r="DK25" s="57"/>
+      <c r="DL25" s="57"/>
+      <c r="DM25" s="57"/>
+      <c r="DN25" s="57"/>
+      <c r="DO25" s="57"/>
+      <c r="DP25" s="57"/>
+      <c r="DQ25" s="57"/>
+      <c r="DR25" s="57"/>
+      <c r="DS25" s="57"/>
+      <c r="DT25" s="57"/>
+      <c r="DU25" s="57"/>
+      <c r="DV25" s="57"/>
+      <c r="DW25" s="57"/>
+      <c r="DX25" s="57"/>
+      <c r="DY25" s="57"/>
+      <c r="DZ25" s="57"/>
+      <c r="EA25" s="57"/>
+      <c r="EB25" s="57"/>
+      <c r="EC25" s="57"/>
+      <c r="ED25" s="57"/>
+      <c r="EE25" s="57"/>
+      <c r="EF25" s="57"/>
+      <c r="EG25" s="57"/>
+      <c r="EH25" s="57"/>
+      <c r="EI25" s="57"/>
+      <c r="EJ25" s="57"/>
+      <c r="EK25" s="57"/>
+      <c r="EL25" s="57"/>
+      <c r="EM25" s="57"/>
+      <c r="EN25" s="57"/>
+      <c r="EO25" s="57"/>
+      <c r="EP25" s="57"/>
+      <c r="EQ25" s="57"/>
+      <c r="ER25" s="57"/>
+      <c r="ES25" s="57"/>
+      <c r="ET25" s="57"/>
+      <c r="EU25" s="57"/>
+      <c r="EV25" s="57"/>
+      <c r="EW25" s="57"/>
+      <c r="EX25" s="57"/>
+      <c r="EY25" s="57"/>
+      <c r="EZ25" s="57"/>
+      <c r="FA25" s="57"/>
+      <c r="FB25" s="57"/>
+      <c r="FC25" s="57"/>
+      <c r="FD25" s="57"/>
+      <c r="FE25" s="57"/>
+      <c r="FF25" s="57"/>
+      <c r="FG25" s="57"/>
+      <c r="FH25" s="57"/>
+      <c r="FI25" s="57"/>
+      <c r="FJ25" s="57"/>
+      <c r="FK25" s="57"/>
+      <c r="FL25" s="57"/>
+      <c r="FM25" s="57"/>
+      <c r="FN25" s="57"/>
+      <c r="FO25" s="57"/>
+      <c r="FP25" s="57"/>
+      <c r="FQ25" s="57"/>
+      <c r="FR25" s="57"/>
+      <c r="FS25" s="57"/>
+      <c r="FT25" s="57"/>
+      <c r="FU25" s="57"/>
+      <c r="FV25" s="57"/>
+      <c r="FW25" s="57"/>
+      <c r="FX25" s="57"/>
+      <c r="FY25" s="57"/>
+      <c r="FZ25" s="57"/>
+      <c r="GA25" s="57"/>
+      <c r="GB25" s="57"/>
+      <c r="GC25" s="57"/>
+      <c r="GD25" s="57"/>
+      <c r="GE25" s="57"/>
+      <c r="GF25" s="57"/>
+      <c r="GG25" s="57"/>
+      <c r="GH25" s="57"/>
+      <c r="GI25" s="57"/>
+      <c r="GJ25" s="57"/>
+      <c r="GK25" s="57"/>
+      <c r="GL25" s="57"/>
+      <c r="GM25" s="57"/>
+      <c r="GN25" s="57"/>
+      <c r="GO25" s="57"/>
+      <c r="GP25" s="57"/>
+      <c r="GQ25" s="57"/>
+      <c r="GR25" s="57"/>
+      <c r="GS25" s="57"/>
+      <c r="GT25" s="57"/>
+      <c r="GU25" s="57"/>
+      <c r="GV25" s="57"/>
+      <c r="GW25" s="57"/>
+      <c r="GX25" s="57"/>
+      <c r="GY25" s="57"/>
+      <c r="GZ25" s="57"/>
+      <c r="HA25" s="57"/>
+      <c r="HB25" s="57"/>
+      <c r="HC25" s="57"/>
+      <c r="HD25" s="57"/>
+      <c r="HE25" s="57"/>
+      <c r="HF25" s="57"/>
+      <c r="HG25" s="57"/>
+      <c r="HH25" s="57"/>
+      <c r="HI25" s="57"/>
+      <c r="HJ25" s="57"/>
+      <c r="HK25" s="57"/>
+      <c r="HL25" s="57"/>
+      <c r="HM25" s="57"/>
+      <c r="HN25" s="57"/>
+      <c r="HO25" s="57"/>
+      <c r="HP25" s="57"/>
+      <c r="HQ25" s="57"/>
+      <c r="HR25" s="57"/>
+      <c r="HS25" s="57"/>
+      <c r="HT25" s="57"/>
+      <c r="HU25" s="57"/>
+      <c r="HV25" s="57"/>
+      <c r="HW25" s="57"/>
+      <c r="HX25" s="57"/>
+      <c r="HY25" s="57"/>
+      <c r="HZ25" s="57"/>
+      <c r="IA25" s="57"/>
+      <c r="IB25" s="57"/>
+      <c r="IC25" s="57"/>
+      <c r="ID25" s="57"/>
+      <c r="IE25" s="57"/>
+      <c r="IF25" s="57"/>
+      <c r="IG25" s="57"/>
+      <c r="IH25" s="57"/>
+      <c r="II25" s="57"/>
+      <c r="IJ25" s="57"/>
+      <c r="IK25" s="57"/>
+      <c r="IL25" s="57"/>
+      <c r="IM25" s="57"/>
+      <c r="IN25" s="57"/>
+      <c r="IO25" s="57"/>
+      <c r="IP25" s="57"/>
+      <c r="IQ25" s="57"/>
+      <c r="IR25" s="57"/>
+      <c r="IS25" s="57"/>
+      <c r="IT25" s="57"/>
+      <c r="IU25" s="57"/>
+      <c r="IV25" s="57"/>
+    </row>
+    <row r="26" spans="1:256">
+      <c r="A26" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="57"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="57"/>
+      <c r="U26" s="57"/>
+      <c r="V26" s="57"/>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+      <c r="AF26" s="57"/>
+      <c r="AG26" s="57"/>
+      <c r="AH26" s="57"/>
+      <c r="AI26" s="57"/>
+      <c r="AJ26" s="57"/>
+      <c r="AK26" s="57"/>
+      <c r="AL26" s="57"/>
+      <c r="AM26" s="57"/>
+      <c r="AN26" s="57"/>
+      <c r="AO26" s="57"/>
+      <c r="AP26" s="57"/>
+      <c r="AQ26" s="57"/>
+      <c r="AR26" s="57"/>
+      <c r="AS26" s="57"/>
+      <c r="AT26" s="57"/>
+      <c r="AU26" s="57"/>
+      <c r="AV26" s="57"/>
+      <c r="AW26" s="57"/>
+      <c r="AX26" s="57"/>
+      <c r="AY26" s="57"/>
+      <c r="AZ26" s="57"/>
+      <c r="BA26" s="57"/>
+      <c r="BB26" s="57"/>
+      <c r="BC26" s="57"/>
+      <c r="BD26" s="57"/>
+      <c r="BE26" s="57"/>
+      <c r="BF26" s="57"/>
+      <c r="BG26" s="57"/>
+      <c r="BH26" s="57"/>
+      <c r="BI26" s="57"/>
+      <c r="BJ26" s="57"/>
+      <c r="BK26" s="57"/>
+      <c r="BL26" s="57"/>
+      <c r="BM26" s="57"/>
+      <c r="BN26" s="57"/>
+      <c r="BO26" s="57"/>
+      <c r="BP26" s="57"/>
+      <c r="BQ26" s="57"/>
+      <c r="BR26" s="57"/>
+      <c r="BS26" s="57"/>
+      <c r="BT26" s="57"/>
+      <c r="BU26" s="57"/>
+      <c r="BV26" s="57"/>
+      <c r="BW26" s="57"/>
+      <c r="BX26" s="57"/>
+      <c r="BY26" s="57"/>
+      <c r="BZ26" s="57"/>
+      <c r="CA26" s="57"/>
+      <c r="CB26" s="57"/>
+      <c r="CC26" s="57"/>
+      <c r="CD26" s="57"/>
+      <c r="CE26" s="57"/>
+      <c r="CF26" s="57"/>
+      <c r="CG26" s="57"/>
+      <c r="CH26" s="57"/>
+      <c r="CI26" s="57"/>
+      <c r="CJ26" s="57"/>
+      <c r="CK26" s="57"/>
+      <c r="CL26" s="57"/>
+      <c r="CM26" s="57"/>
+      <c r="CN26" s="57"/>
+      <c r="CO26" s="57"/>
+      <c r="CP26" s="57"/>
+      <c r="CQ26" s="57"/>
+      <c r="CR26" s="57"/>
+      <c r="CS26" s="57"/>
+      <c r="CT26" s="57"/>
+      <c r="CU26" s="57"/>
+      <c r="CV26" s="57"/>
+      <c r="CW26" s="57"/>
+      <c r="CX26" s="57"/>
+      <c r="CY26" s="57"/>
+      <c r="CZ26" s="57"/>
+      <c r="DA26" s="57"/>
+      <c r="DB26" s="57"/>
+      <c r="DC26" s="57"/>
+      <c r="DD26" s="57"/>
+      <c r="DE26" s="57"/>
+      <c r="DF26" s="57"/>
+      <c r="DG26" s="57"/>
+      <c r="DH26" s="57"/>
+      <c r="DI26" s="57"/>
+      <c r="DJ26" s="57"/>
+      <c r="DK26" s="57"/>
+      <c r="DL26" s="57"/>
+      <c r="DM26" s="57"/>
+      <c r="DN26" s="57"/>
+      <c r="DO26" s="57"/>
+      <c r="DP26" s="57"/>
+      <c r="DQ26" s="57"/>
+      <c r="DR26" s="57"/>
+      <c r="DS26" s="57"/>
+      <c r="DT26" s="57"/>
+      <c r="DU26" s="57"/>
+      <c r="DV26" s="57"/>
+      <c r="DW26" s="57"/>
+      <c r="DX26" s="57"/>
+      <c r="DY26" s="57"/>
+      <c r="DZ26" s="57"/>
+      <c r="EA26" s="57"/>
+      <c r="EB26" s="57"/>
+      <c r="EC26" s="57"/>
+      <c r="ED26" s="57"/>
+      <c r="EE26" s="57"/>
+      <c r="EF26" s="57"/>
+      <c r="EG26" s="57"/>
+      <c r="EH26" s="57"/>
+      <c r="EI26" s="57"/>
+      <c r="EJ26" s="57"/>
+      <c r="EK26" s="57"/>
+      <c r="EL26" s="57"/>
+      <c r="EM26" s="57"/>
+      <c r="EN26" s="57"/>
+      <c r="EO26" s="57"/>
+      <c r="EP26" s="57"/>
+      <c r="EQ26" s="57"/>
+      <c r="ER26" s="57"/>
+      <c r="ES26" s="57"/>
+      <c r="ET26" s="57"/>
+      <c r="EU26" s="57"/>
+      <c r="EV26" s="57"/>
+      <c r="EW26" s="57"/>
+      <c r="EX26" s="57"/>
+      <c r="EY26" s="57"/>
+      <c r="EZ26" s="57"/>
+      <c r="FA26" s="57"/>
+      <c r="FB26" s="57"/>
+      <c r="FC26" s="57"/>
+      <c r="FD26" s="57"/>
+      <c r="FE26" s="57"/>
+      <c r="FF26" s="57"/>
+      <c r="FG26" s="57"/>
+      <c r="FH26" s="57"/>
+      <c r="FI26" s="57"/>
+      <c r="FJ26" s="57"/>
+      <c r="FK26" s="57"/>
+      <c r="FL26" s="57"/>
+      <c r="FM26" s="57"/>
+      <c r="FN26" s="57"/>
+      <c r="FO26" s="57"/>
+      <c r="FP26" s="57"/>
+      <c r="FQ26" s="57"/>
+      <c r="FR26" s="57"/>
+      <c r="FS26" s="57"/>
+      <c r="FT26" s="57"/>
+      <c r="FU26" s="57"/>
+      <c r="FV26" s="57"/>
+      <c r="FW26" s="57"/>
+      <c r="FX26" s="57"/>
+      <c r="FY26" s="57"/>
+      <c r="FZ26" s="57"/>
+      <c r="GA26" s="57"/>
+      <c r="GB26" s="57"/>
+      <c r="GC26" s="57"/>
+      <c r="GD26" s="57"/>
+      <c r="GE26" s="57"/>
+      <c r="GF26" s="57"/>
+      <c r="GG26" s="57"/>
+      <c r="GH26" s="57"/>
+      <c r="GI26" s="57"/>
+      <c r="GJ26" s="57"/>
+      <c r="GK26" s="57"/>
+      <c r="GL26" s="57"/>
+      <c r="GM26" s="57"/>
+      <c r="GN26" s="57"/>
+      <c r="GO26" s="57"/>
+      <c r="GP26" s="57"/>
+      <c r="GQ26" s="57"/>
+      <c r="GR26" s="57"/>
+      <c r="GS26" s="57"/>
+      <c r="GT26" s="57"/>
+      <c r="GU26" s="57"/>
+      <c r="GV26" s="57"/>
+      <c r="GW26" s="57"/>
+      <c r="GX26" s="57"/>
+      <c r="GY26" s="57"/>
+      <c r="GZ26" s="57"/>
+      <c r="HA26" s="57"/>
+      <c r="HB26" s="57"/>
+      <c r="HC26" s="57"/>
+      <c r="HD26" s="57"/>
+      <c r="HE26" s="57"/>
+      <c r="HF26" s="57"/>
+      <c r="HG26" s="57"/>
+      <c r="HH26" s="57"/>
+      <c r="HI26" s="57"/>
+      <c r="HJ26" s="57"/>
+      <c r="HK26" s="57"/>
+      <c r="HL26" s="57"/>
+      <c r="HM26" s="57"/>
+      <c r="HN26" s="57"/>
+      <c r="HO26" s="57"/>
+      <c r="HP26" s="57"/>
+      <c r="HQ26" s="57"/>
+      <c r="HR26" s="57"/>
+      <c r="HS26" s="57"/>
+      <c r="HT26" s="57"/>
+      <c r="HU26" s="57"/>
+      <c r="HV26" s="57"/>
+      <c r="HW26" s="57"/>
+      <c r="HX26" s="57"/>
+      <c r="HY26" s="57"/>
+      <c r="HZ26" s="57"/>
+      <c r="IA26" s="57"/>
+      <c r="IB26" s="57"/>
+      <c r="IC26" s="57"/>
+      <c r="ID26" s="57"/>
+      <c r="IE26" s="57"/>
+      <c r="IF26" s="57"/>
+      <c r="IG26" s="57"/>
+      <c r="IH26" s="57"/>
+      <c r="II26" s="57"/>
+      <c r="IJ26" s="57"/>
+      <c r="IK26" s="57"/>
+      <c r="IL26" s="57"/>
+      <c r="IM26" s="57"/>
+      <c r="IN26" s="57"/>
+      <c r="IO26" s="57"/>
+      <c r="IP26" s="57"/>
+      <c r="IQ26" s="57"/>
+      <c r="IR26" s="57"/>
+      <c r="IS26" s="57"/>
+      <c r="IT26" s="57"/>
+      <c r="IU26" s="57"/>
+      <c r="IV26" s="57"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A6:A7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="73" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75">
+      <c r="A1" s="92" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+    </row>
+    <row r="2" spans="1:4" ht="18.75">
+      <c r="A2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="7">
+        <v>46148</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9">
+        <v>916000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="7">
+        <v>46155</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="10">
+        <v>46183</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="9">
+        <v>200000</v>
+      </c>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="10">
+        <v>46183</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="9">
+        <v>230000</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="10">
+        <v>46183</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="9">
+        <v>250000</v>
+      </c>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="10">
+        <v>46183</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="9">
+        <v>225000</v>
+      </c>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="10">
+        <v>46183</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="9">
+        <v>350000</v>
+      </c>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="10">
+        <v>46183</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="9">
+        <v>230000</v>
+      </c>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="10">
+        <v>46183</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="9">
+        <v>370000</v>
+      </c>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="11">
+        <v>46186</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="11">
+        <v>46193</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="11">
+        <v>46196</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9">
+        <v>2300000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="C16" s="9">
+        <f>SUM(C4:C15)</f>
+        <v>1855000</v>
+      </c>
+      <c r="D16" s="9">
+        <f>SUM(D4:D15)</f>
+        <v>4302000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18.75">
+      <c r="A20" s="92" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="92"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+    </row>
+    <row r="21" spans="1:4" ht="18.75">
+      <c r="A21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75">
+      <c r="A22" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" s="14">
+        <f>'Jan''26'!C26</f>
+        <v>3546000</v>
+      </c>
+      <c r="C23" s="14">
+        <f>'Jan''26'!C28</f>
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B24" s="14">
+        <f>'Feb''26'!C19</f>
+        <v>3127000</v>
+      </c>
+      <c r="C24" s="14">
+        <f>'Feb''26'!C21</f>
+        <v>1141000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B25" s="14">
+        <f>'Mar''26'!C27</f>
+        <v>3847000</v>
+      </c>
+      <c r="C25" s="14">
+        <f>'Mar''26'!C29</f>
+        <v>2689500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="14">
+        <f>'Apr''26'!C17</f>
+        <v>1629000</v>
+      </c>
+      <c r="C26" s="14">
+        <f>'Apr''26'!C19</f>
+        <v>752000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="14">
+        <f>'Mei''26'!C24</f>
+        <v>2800000</v>
+      </c>
+      <c r="C27" s="14">
+        <f>'Mei''26'!C26</f>
+        <v>2495500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="14">
+        <f>'Juni''26'!C31</f>
+        <v>6019000</v>
+      </c>
+      <c r="C28" s="14">
+        <f>'Juni''26'!C33</f>
+        <v>2722000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="16">
+        <f>SUM(B23:B28)</f>
+        <v>20968000</v>
+      </c>
+      <c r="C29" s="16">
+        <f>SUM(C23:C28)</f>
+        <v>11000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A20:D20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:IV35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -1442,13 +5537,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="80"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -1477,10 +5572,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="35">
         <v>-334000</v>
       </c>
@@ -1491,7 +5586,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" s="19" customFormat="1" ht="30">
-      <c r="A5" s="83">
+      <c r="A5" s="86">
         <v>46023</v>
       </c>
       <c r="B5" s="38" t="s">
@@ -1508,7 +5603,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A6" s="84"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
@@ -1523,7 +5618,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="85"/>
+      <c r="A7" s="88"/>
       <c r="B7" s="8" t="s">
         <v>10</v>
       </c>
@@ -1555,7 +5650,7 @@
       <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="83">
+      <c r="A9" s="86">
         <v>46031</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -1572,7 +5667,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A10" s="85"/>
+      <c r="A10" s="88"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
@@ -1587,7 +5682,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A11" s="83">
+      <c r="A11" s="86">
         <v>46033</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -1604,7 +5699,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A12" s="85"/>
+      <c r="A12" s="88"/>
       <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
@@ -1636,7 +5731,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="83">
+      <c r="A14" s="86">
         <v>46039</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -1653,7 +5748,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A15" s="85"/>
+      <c r="A15" s="88"/>
       <c r="B15" s="8" t="s">
         <v>18</v>
       </c>
@@ -1668,7 +5763,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A16" s="83">
+      <c r="A16" s="86">
         <v>46041</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -1685,7 +5780,7 @@
       <c r="G16" s="42"/>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A17" s="85"/>
+      <c r="A17" s="88"/>
       <c r="B17" s="8" t="s">
         <v>11</v>
       </c>
@@ -1761,7 +5856,7 @@
       </c>
     </row>
     <row r="21" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A21" s="83">
+      <c r="A21" s="86">
         <v>46052</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -1783,7 +5878,7 @@
       </c>
     </row>
     <row r="22" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A22" s="84"/>
+      <c r="A22" s="87"/>
       <c r="B22" s="8" t="s">
         <v>24</v>
       </c>
@@ -1803,7 +5898,7 @@
       </c>
     </row>
     <row r="23" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A23" s="85"/>
+      <c r="A23" s="88"/>
       <c r="B23" s="8" t="s">
         <v>11</v>
       </c>
@@ -1823,10 +5918,10 @@
       </c>
     </row>
     <row r="24" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="80"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="46">
         <f>SUM(C4:C23)</f>
         <v>3212000</v>
@@ -1852,10 +5947,10 @@
       <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="81" t="s">
+      <c r="A26" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="81"/>
+      <c r="B26" s="84"/>
       <c r="C26" s="51">
         <f>C24-C4</f>
         <v>3546000</v>
@@ -1875,10 +5970,10 @@
       <c r="E27" s="50"/>
     </row>
     <row r="28" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A28" s="82" t="s">
+      <c r="A28" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="82"/>
+      <c r="B28" s="85"/>
       <c r="C28" s="54">
         <f>D24</f>
         <v>1200000</v>
@@ -3702,329 +7797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="73" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="18.75">
-      <c r="A1" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-    </row>
-    <row r="2" spans="1:4" ht="18.75">
-      <c r="A2" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="7">
-        <v>46148</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9">
-        <v>916000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="7">
-        <v>46155</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="10">
-        <v>46183</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="9">
-        <v>200000</v>
-      </c>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="10">
-        <v>46183</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="9">
-        <v>230000</v>
-      </c>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="10">
-        <v>46183</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="9">
-        <v>250000</v>
-      </c>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="10">
-        <v>46183</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C9" s="9">
-        <v>225000</v>
-      </c>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="10">
-        <v>46183</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="9">
-        <v>350000</v>
-      </c>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="10">
-        <v>46183</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="9">
-        <v>230000</v>
-      </c>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="10">
-        <v>46183</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="9">
-        <v>370000</v>
-      </c>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="11">
-        <v>46186</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="11">
-        <v>46193</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9">
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="11">
-        <v>46196</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="C16" s="9">
-        <f>SUM(C4:C15)</f>
-        <v>1855000</v>
-      </c>
-      <c r="D16" s="9">
-        <f>SUM(D4:D15)</f>
-        <v>4302000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="18.75">
-      <c r="A20" s="89" t="s">
-        <v>175</v>
-      </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-    </row>
-    <row r="21" spans="1:4" ht="18.75">
-      <c r="A21" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75">
-      <c r="A22" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B23" s="14">
-        <f>'Jan''26'!C26</f>
-        <v>3546000</v>
-      </c>
-      <c r="C23" s="14">
-        <f>'Jan''26'!C28</f>
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="B24" s="14">
-        <f>'Feb''26'!C19</f>
-        <v>3127000</v>
-      </c>
-      <c r="C24" s="14">
-        <f>'Feb''26'!C21</f>
-        <v>1141000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B25" s="14">
-        <f>'Mar''26'!C27</f>
-        <v>3847000</v>
-      </c>
-      <c r="C25" s="14">
-        <f>'Mar''26'!C29</f>
-        <v>2689500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="B26" s="14">
-        <f>'Apr''26'!C17</f>
-        <v>1629000</v>
-      </c>
-      <c r="C26" s="14">
-        <f>'Apr''26'!C19</f>
-        <v>752000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="B27" s="14">
-        <f>'Mei''26'!C24</f>
-        <v>2800000</v>
-      </c>
-      <c r="C27" s="14">
-        <f>'Mei''26'!C26</f>
-        <v>2495500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="B28" s="14">
-        <f>'Juni''26'!C31</f>
-        <v>6019000</v>
-      </c>
-      <c r="C28" s="14">
-        <f>'Juni''26'!C33</f>
-        <v>2722000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B29" s="16">
-        <f>SUM(B23:B28)</f>
-        <v>20968000</v>
-      </c>
-      <c r="C29" s="16">
-        <f>SUM(C23:C28)</f>
-        <v>11000000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A20:D20"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:IV28"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -4040,13 +7813,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="80"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -4075,10 +7848,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="35">
         <f>'Jan''26'!E24</f>
         <v>2012000</v>
@@ -4124,7 +7897,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="83">
+      <c r="A7" s="86">
         <v>46064</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -4141,7 +7914,7 @@
       <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A8" s="85"/>
+      <c r="A8" s="88"/>
       <c r="B8" s="8" t="s">
         <v>40</v>
       </c>
@@ -4190,7 +7963,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="83">
+      <c r="A11" s="86">
         <v>46072</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -4207,7 +7980,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="85"/>
+      <c r="A12" s="88"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -4271,7 +8044,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="83">
+      <c r="A15" s="86">
         <v>46081</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -4293,7 +8066,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="85"/>
+      <c r="A16" s="88"/>
       <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
@@ -4313,10 +8086,10 @@
       </c>
     </row>
     <row r="17" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="80" t="s">
+      <c r="A17" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="80"/>
+      <c r="B17" s="83"/>
       <c r="C17" s="46">
         <f>SUM(C4:C16)</f>
         <v>5139000</v>
@@ -4342,10 +8115,10 @@
       <c r="E18" s="50"/>
     </row>
     <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="81" t="s">
+      <c r="A19" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="81"/>
+      <c r="B19" s="84"/>
       <c r="C19" s="51">
         <f>C17-C4</f>
         <v>3127000</v>
@@ -4365,10 +8138,10 @@
       <c r="E20" s="50"/>
     </row>
     <row r="21" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A21" s="82" t="s">
+      <c r="A21" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="82"/>
+      <c r="B21" s="85"/>
       <c r="C21" s="54">
         <f>D17</f>
         <v>1141000</v>
@@ -6189,7 +9962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21" customHeight="1"/>
@@ -6202,24 +9975,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
     </row>
     <row r="2" spans="1:6" ht="21" customHeight="1">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
     </row>
     <row r="3" spans="1:6" ht="6.95" customHeight="1"/>
     <row r="4" spans="1:6" s="66" customFormat="1" ht="21" customHeight="1">
@@ -6871,10 +10644,10 @@
       <c r="F40" s="71"/>
     </row>
     <row r="41" spans="1:6" ht="21" customHeight="1">
-      <c r="A41" s="87" t="s">
+      <c r="A41" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="87"/>
+      <c r="B41" s="90"/>
       <c r="C41" s="73">
         <f>SUM(C5:C40)</f>
         <v>2564000</v>
@@ -6899,7 +10672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:IV36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -6915,13 +10688,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="80"/>
     </row>
     <row r="2" spans="1:7" ht="18.75">
       <c r="A2" s="27" t="s">
@@ -6950,10 +10723,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="35">
         <f>'Feb''26'!E17</f>
         <v>3998000</v>
@@ -6999,7 +10772,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A7" s="83">
+      <c r="A7" s="86">
         <v>46084</v>
       </c>
       <c r="B7" s="38" t="s">
@@ -7016,7 +10789,7 @@
       <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A8" s="85"/>
+      <c r="A8" s="88"/>
       <c r="B8" s="8" t="s">
         <v>97</v>
       </c>
@@ -7099,7 +10872,7 @@
       <c r="G12" s="42"/>
     </row>
     <row r="13" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A13" s="83">
+      <c r="A13" s="86">
         <v>46096</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -7116,7 +10889,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A14" s="85"/>
+      <c r="A14" s="88"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -7131,7 +10904,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A15" s="88">
+      <c r="A15" s="91">
         <v>46101</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -7148,7 +10921,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A16" s="88"/>
+      <c r="A16" s="91"/>
       <c r="B16" s="8" t="s">
         <v>103</v>
       </c>
@@ -7163,7 +10936,7 @@
       <c r="G16" s="42"/>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A17" s="84">
+      <c r="A17" s="87">
         <v>46107</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -7180,7 +10953,7 @@
       <c r="G17" s="42"/>
     </row>
     <row r="18" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A18" s="84"/>
+      <c r="A18" s="87"/>
       <c r="B18" s="8" t="s">
         <v>105</v>
       </c>
@@ -7195,7 +10968,7 @@
       <c r="G18" s="42"/>
     </row>
     <row r="19" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A19" s="85"/>
+      <c r="A19" s="88"/>
       <c r="B19" s="8" t="s">
         <v>106</v>
       </c>
@@ -7212,7 +10985,7 @@
       </c>
     </row>
     <row r="20" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A20" s="84">
+      <c r="A20" s="87">
         <v>46109</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -7234,7 +11007,7 @@
       </c>
     </row>
     <row r="21" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A21" s="85"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="8" t="s">
         <v>104</v>
       </c>
@@ -7276,7 +11049,7 @@
       </c>
     </row>
     <row r="23" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A23" s="83">
+      <c r="A23" s="86">
         <v>46112</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -7298,7 +11071,7 @@
       </c>
     </row>
     <row r="24" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A24" s="85"/>
+      <c r="A24" s="88"/>
       <c r="B24" s="8" t="s">
         <v>110</v>
       </c>
@@ -7318,10 +11091,10 @@
       </c>
     </row>
     <row r="25" spans="1:256" s="21" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A25" s="80" t="s">
+      <c r="A25" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="80"/>
+      <c r="B25" s="83"/>
       <c r="C25" s="46">
         <f>SUM(C4:C24)</f>
         <v>7845000</v>
@@ -7347,10 +11120,10 @@
       <c r="E26" s="50"/>
     </row>
     <row r="27" spans="1:256" s="22" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A27" s="81" t="s">
+      <c r="A27" s="84" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="81"/>
+      <c r="B27" s="84"/>
       <c r="C27" s="51">
         <f>C25-C4</f>
         <v>3847000</v>
@@ -7370,10 +11143,10 @@
       <c r="E28" s="50"/>
     </row>
     <row r="29" spans="1:256" s="22" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A29" s="82" t="s">
+      <c r="A29" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="82"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="54">
         <f>D25</f>
         <v>2689500</v>
@@ -9197,7 +12970,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:IV26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -9213,13 +12986,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="80"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -9248,10 +13021,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="35">
         <f>'Mar''26'!E25</f>
         <v>5155500</v>
@@ -9348,7 +13121,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A10" s="83">
+      <c r="A10" s="86">
         <v>46132</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -9370,7 +13143,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="85"/>
+      <c r="A11" s="88"/>
       <c r="B11" s="8" t="s">
         <v>98</v>
       </c>
@@ -9456,10 +13229,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="83" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="80"/>
+      <c r="B15" s="83"/>
       <c r="C15" s="46">
         <f>SUM(C4:C14)</f>
         <v>6784500</v>
@@ -9485,10 +13258,10 @@
       <c r="E16" s="50"/>
     </row>
     <row r="17" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="84" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="81"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="51">
         <f>C15-C4</f>
         <v>1629000</v>
@@ -9508,10 +13281,10 @@
       <c r="E18" s="50"/>
     </row>
     <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="82" t="s">
+      <c r="A19" s="85" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="82"/>
+      <c r="B19" s="85"/>
       <c r="C19" s="54">
         <f>D15</f>
         <v>752000</v>
@@ -11330,7 +15103,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:IV33"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -11346,13 +15119,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="80"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -11381,10 +15154,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="35">
         <f>'Apr''26'!E15</f>
         <v>6032500</v>
@@ -11413,7 +15186,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="83">
+      <c r="A6" s="86">
         <v>46145</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -11430,7 +15203,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="85"/>
+      <c r="A7" s="88"/>
       <c r="B7" s="8" t="s">
         <v>128</v>
       </c>
@@ -11462,7 +15235,7 @@
       <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="83">
+      <c r="A9" s="86">
         <v>46148</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -11479,7 +15252,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A10" s="85"/>
+      <c r="A10" s="88"/>
       <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
@@ -11494,7 +15267,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="83">
+      <c r="A11" s="86">
         <v>46151</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -11511,7 +15284,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="85"/>
+      <c r="A12" s="88"/>
       <c r="B12" s="8" t="s">
         <v>132</v>
       </c>
@@ -11543,7 +15316,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A14" s="83">
+      <c r="A14" s="86">
         <v>46155</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -11560,7 +15333,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="85"/>
+      <c r="A15" s="88"/>
       <c r="B15" s="8" t="s">
         <v>134</v>
       </c>
@@ -11575,7 +15348,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="83">
+      <c r="A16" s="86">
         <v>46158</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -11591,7 +15364,7 @@
       </c>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A17" s="85"/>
+      <c r="A17" s="88"/>
       <c r="B17" s="8" t="s">
         <v>135</v>
       </c>
@@ -11655,7 +15428,7 @@
       </c>
     </row>
     <row r="20" spans="1:256" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A20" s="83">
+      <c r="A20" s="86">
         <v>46165</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -11677,7 +15450,7 @@
       </c>
     </row>
     <row r="21" spans="1:256" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A21" s="85"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="8" t="s">
         <v>13</v>
       </c>
@@ -11697,10 +15470,10 @@
       </c>
     </row>
     <row r="22" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A22" s="80" t="s">
+      <c r="A22" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="80"/>
+      <c r="B22" s="83"/>
       <c r="C22" s="46">
         <f>SUM(C4:C21)</f>
         <v>8832500</v>
@@ -11726,10 +15499,10 @@
       <c r="E23" s="50"/>
     </row>
     <row r="24" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="81" t="s">
+      <c r="A24" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="81"/>
+      <c r="B24" s="84"/>
       <c r="C24" s="51">
         <f>C22-C4</f>
         <v>2800000</v>
@@ -11749,10 +15522,10 @@
       <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="82"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="54">
         <f>D22</f>
         <v>2495500</v>
@@ -13576,7 +17349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:IV42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -13592,13 +17365,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="80"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -13627,10 +17400,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="35">
         <f>'Mei''26'!E22</f>
         <v>6337000</v>
@@ -13642,7 +17415,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A5" s="91">
+      <c r="A5" s="78">
         <v>46175</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -13659,7 +17432,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="92"/>
+      <c r="A6" s="79"/>
       <c r="B6" s="8" t="s">
         <v>146</v>
       </c>
@@ -14026,7 +17799,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A27" s="91">
+      <c r="A27" s="78">
         <v>46203</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -14068,10 +17841,10 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A29" s="80" t="s">
+      <c r="A29" s="83" t="s">
         <v>162</v>
       </c>
-      <c r="B29" s="80"/>
+      <c r="B29" s="83"/>
       <c r="C29" s="46">
         <f>SUM(C4:C28)</f>
         <v>12356000</v>
@@ -14098,10 +17871,10 @@
       <c r="E30" s="50"/>
     </row>
     <row r="31" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A31" s="81" t="s">
+      <c r="A31" s="84" t="s">
         <v>163</v>
       </c>
-      <c r="B31" s="81"/>
+      <c r="B31" s="84"/>
       <c r="C31" s="51">
         <f>C29-C4</f>
         <v>6019000</v>
@@ -14121,10 +17894,10 @@
       <c r="E32" s="50"/>
     </row>
     <row r="33" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A33" s="82" t="s">
+      <c r="A33" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="82"/>
+      <c r="B33" s="85"/>
       <c r="C33" s="54">
         <f>D29</f>
         <v>2722000</v>
@@ -15952,7 +19725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:IV35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -15968,13 +19741,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="80"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -16003,10 +19776,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="79"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="35">
         <f>'Juni''26'!E29</f>
         <v>9634000</v>
@@ -16263,10 +20036,10 @@
       </c>
     </row>
     <row r="24" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="B24" s="80"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="46">
         <f>SUM(C4:C23)</f>
         <v>9744000</v>
@@ -16292,10 +20065,10 @@
       <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="81" t="s">
+      <c r="A26" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="81"/>
+      <c r="B26" s="84"/>
       <c r="C26" s="51">
         <f>C24-C4</f>
         <v>110000</v>
@@ -16315,10 +20088,10 @@
       <c r="E27" s="50"/>
     </row>
     <row r="28" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A28" s="82" t="s">
+      <c r="A28" s="85" t="s">
         <v>169</v>
       </c>
-      <c r="B28" s="82"/>
+      <c r="B28" s="85"/>
       <c r="C28" s="54">
         <f>D24</f>
         <v>0</v>
@@ -18133,2083 +21906,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:IV26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="17.5703125" style="23" customWidth="1"/>
-    <col min="2" max="2" width="62.85546875" style="24" customWidth="1"/>
-    <col min="3" max="4" width="17.42578125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="26" customWidth="1"/>
-    <col min="6" max="6" width="4" style="24" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="24" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" style="24" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="77"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30"/>
-    </row>
-    <row r="3" spans="1:8" s="17" customFormat="1" ht="18" customHeight="1">
-      <c r="A3" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="79" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="35">
-        <f>'Apr''26'!E15</f>
-        <v>6032500</v>
-      </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="37">
-        <f>C4-F4</f>
-        <v>6032500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A5" s="11"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="40">
-        <f t="shared" ref="E5:E14" si="0">E4+C5-D5</f>
-        <v>6032500</v>
-      </c>
-      <c r="G5" s="41"/>
-    </row>
-    <row r="6" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="83"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="40">
-        <f t="shared" si="0"/>
-        <v>6032500</v>
-      </c>
-      <c r="G6" s="42"/>
-    </row>
-    <row r="7" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="85"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="40">
-        <f t="shared" si="0"/>
-        <v>6032500</v>
-      </c>
-      <c r="G7" s="42"/>
-    </row>
-    <row r="8" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A8" s="11"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="40">
-        <f t="shared" si="0"/>
-        <v>6032500</v>
-      </c>
-      <c r="G8" s="42"/>
-    </row>
-    <row r="9" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="11"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="40">
-        <f t="shared" si="0"/>
-        <v>6032500</v>
-      </c>
-      <c r="G9" s="42"/>
-    </row>
-    <row r="10" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A10" s="43"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="40">
-        <f t="shared" si="0"/>
-        <v>6032500</v>
-      </c>
-      <c r="G10" s="44">
-        <v>126000</v>
-      </c>
-      <c r="H10" s="45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="43"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="40">
-        <f t="shared" si="0"/>
-        <v>6032500</v>
-      </c>
-      <c r="G11" s="44">
-        <v>932000</v>
-      </c>
-      <c r="H11" s="45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="40">
-        <f t="shared" si="0"/>
-        <v>6032500</v>
-      </c>
-      <c r="G12" s="44">
-        <v>257000</v>
-      </c>
-      <c r="H12" s="45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A13" s="11"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="40">
-        <f t="shared" si="0"/>
-        <v>6032500</v>
-      </c>
-      <c r="G13" s="44">
-        <v>1400000</v>
-      </c>
-      <c r="H13" s="45" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="40">
-        <f t="shared" si="0"/>
-        <v>6032500</v>
-      </c>
-      <c r="G14" s="44">
-        <v>250000</v>
-      </c>
-      <c r="H14" s="45" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A15" s="80" t="s">
-        <v>136</v>
-      </c>
-      <c r="B15" s="80"/>
-      <c r="C15" s="46">
-        <f>SUM(C4:C14)</f>
-        <v>6032500</v>
-      </c>
-      <c r="D15" s="46">
-        <f>SUM(D4:D14)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="37">
-        <f>C15-D15</f>
-        <v>6032500</v>
-      </c>
-      <c r="G15" s="44">
-        <f>SUM(G10:G14)</f>
-        <v>2965000</v>
-      </c>
-      <c r="H15" s="47"/>
-    </row>
-    <row r="16" spans="1:8" s="22" customFormat="1" ht="6.75" customHeight="1">
-      <c r="A16" s="48"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="50"/>
-    </row>
-    <row r="17" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="81" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="51">
-        <f>C15-C4</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="49"/>
-      <c r="E17" s="50"/>
-      <c r="G17" s="52">
-        <f>E15-G15</f>
-        <v>3067500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:256" s="22" customFormat="1" ht="5.25" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="50"/>
-    </row>
-    <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="82" t="s">
-        <v>138</v>
-      </c>
-      <c r="B19" s="82"/>
-      <c r="C19" s="54">
-        <f>D15</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="50"/>
-    </row>
-    <row r="20" spans="1:256" ht="24" customHeight="1">
-      <c r="A20" s="55"/>
-      <c r="D20" s="56"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57">
-        <v>4357500</v>
-      </c>
-      <c r="H20" s="57">
-        <f>G17-G20</f>
-        <v>-1290000</v>
-      </c>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="57"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="57"/>
-      <c r="S20" s="57"/>
-      <c r="T20" s="57"/>
-      <c r="U20" s="57"/>
-      <c r="V20" s="57"/>
-      <c r="W20" s="57"/>
-      <c r="X20" s="57"/>
-      <c r="Y20" s="57"/>
-      <c r="Z20" s="57"/>
-      <c r="AA20" s="57"/>
-      <c r="AB20" s="57"/>
-      <c r="AC20" s="57"/>
-      <c r="AD20" s="57"/>
-      <c r="AE20" s="57"/>
-      <c r="AF20" s="57"/>
-      <c r="AG20" s="57"/>
-      <c r="AH20" s="57"/>
-      <c r="AI20" s="57"/>
-      <c r="AJ20" s="57"/>
-      <c r="AK20" s="57"/>
-      <c r="AL20" s="57"/>
-      <c r="AM20" s="57"/>
-      <c r="AN20" s="57"/>
-      <c r="AO20" s="57"/>
-      <c r="AP20" s="57"/>
-      <c r="AQ20" s="57"/>
-      <c r="AR20" s="57"/>
-      <c r="AS20" s="57"/>
-      <c r="AT20" s="57"/>
-      <c r="AU20" s="57"/>
-      <c r="AV20" s="57"/>
-      <c r="AW20" s="57"/>
-      <c r="AX20" s="57"/>
-      <c r="AY20" s="57"/>
-      <c r="AZ20" s="57"/>
-      <c r="BA20" s="57"/>
-      <c r="BB20" s="57"/>
-      <c r="BC20" s="57"/>
-      <c r="BD20" s="57"/>
-      <c r="BE20" s="57"/>
-      <c r="BF20" s="57"/>
-      <c r="BG20" s="57"/>
-      <c r="BH20" s="57"/>
-      <c r="BI20" s="57"/>
-      <c r="BJ20" s="57"/>
-      <c r="BK20" s="57"/>
-      <c r="BL20" s="57"/>
-      <c r="BM20" s="57"/>
-      <c r="BN20" s="57"/>
-      <c r="BO20" s="57"/>
-      <c r="BP20" s="57"/>
-      <c r="BQ20" s="57"/>
-      <c r="BR20" s="57"/>
-      <c r="BS20" s="57"/>
-      <c r="BT20" s="57"/>
-      <c r="BU20" s="57"/>
-      <c r="BV20" s="57"/>
-      <c r="BW20" s="57"/>
-      <c r="BX20" s="57"/>
-      <c r="BY20" s="57"/>
-      <c r="BZ20" s="57"/>
-      <c r="CA20" s="57"/>
-      <c r="CB20" s="57"/>
-      <c r="CC20" s="57"/>
-      <c r="CD20" s="57"/>
-      <c r="CE20" s="57"/>
-      <c r="CF20" s="57"/>
-      <c r="CG20" s="57"/>
-      <c r="CH20" s="57"/>
-      <c r="CI20" s="57"/>
-      <c r="CJ20" s="57"/>
-      <c r="CK20" s="57"/>
-      <c r="CL20" s="57"/>
-      <c r="CM20" s="57"/>
-      <c r="CN20" s="57"/>
-      <c r="CO20" s="57"/>
-      <c r="CP20" s="57"/>
-      <c r="CQ20" s="57"/>
-      <c r="CR20" s="57"/>
-      <c r="CS20" s="57"/>
-      <c r="CT20" s="57"/>
-      <c r="CU20" s="57"/>
-      <c r="CV20" s="57"/>
-      <c r="CW20" s="57"/>
-      <c r="CX20" s="57"/>
-      <c r="CY20" s="57"/>
-      <c r="CZ20" s="57"/>
-      <c r="DA20" s="57"/>
-      <c r="DB20" s="57"/>
-      <c r="DC20" s="57"/>
-      <c r="DD20" s="57"/>
-      <c r="DE20" s="57"/>
-      <c r="DF20" s="57"/>
-      <c r="DG20" s="57"/>
-      <c r="DH20" s="57"/>
-      <c r="DI20" s="57"/>
-      <c r="DJ20" s="57"/>
-      <c r="DK20" s="57"/>
-      <c r="DL20" s="57"/>
-      <c r="DM20" s="57"/>
-      <c r="DN20" s="57"/>
-      <c r="DO20" s="57"/>
-      <c r="DP20" s="57"/>
-      <c r="DQ20" s="57"/>
-      <c r="DR20" s="57"/>
-      <c r="DS20" s="57"/>
-      <c r="DT20" s="57"/>
-      <c r="DU20" s="57"/>
-      <c r="DV20" s="57"/>
-      <c r="DW20" s="57"/>
-      <c r="DX20" s="57"/>
-      <c r="DY20" s="57"/>
-      <c r="DZ20" s="57"/>
-      <c r="EA20" s="57"/>
-      <c r="EB20" s="57"/>
-      <c r="EC20" s="57"/>
-      <c r="ED20" s="57"/>
-      <c r="EE20" s="57"/>
-      <c r="EF20" s="57"/>
-      <c r="EG20" s="57"/>
-      <c r="EH20" s="57"/>
-      <c r="EI20" s="57"/>
-      <c r="EJ20" s="57"/>
-      <c r="EK20" s="57"/>
-      <c r="EL20" s="57"/>
-      <c r="EM20" s="57"/>
-      <c r="EN20" s="57"/>
-      <c r="EO20" s="57"/>
-      <c r="EP20" s="57"/>
-      <c r="EQ20" s="57"/>
-      <c r="ER20" s="57"/>
-      <c r="ES20" s="57"/>
-      <c r="ET20" s="57"/>
-      <c r="EU20" s="57"/>
-      <c r="EV20" s="57"/>
-      <c r="EW20" s="57"/>
-      <c r="EX20" s="57"/>
-      <c r="EY20" s="57"/>
-      <c r="EZ20" s="57"/>
-      <c r="FA20" s="57"/>
-      <c r="FB20" s="57"/>
-      <c r="FC20" s="57"/>
-      <c r="FD20" s="57"/>
-      <c r="FE20" s="57"/>
-      <c r="FF20" s="57"/>
-      <c r="FG20" s="57"/>
-      <c r="FH20" s="57"/>
-      <c r="FI20" s="57"/>
-      <c r="FJ20" s="57"/>
-      <c r="FK20" s="57"/>
-      <c r="FL20" s="57"/>
-      <c r="FM20" s="57"/>
-      <c r="FN20" s="57"/>
-      <c r="FO20" s="57"/>
-      <c r="FP20" s="57"/>
-      <c r="FQ20" s="57"/>
-      <c r="FR20" s="57"/>
-      <c r="FS20" s="57"/>
-      <c r="FT20" s="57"/>
-      <c r="FU20" s="57"/>
-      <c r="FV20" s="57"/>
-      <c r="FW20" s="57"/>
-      <c r="FX20" s="57"/>
-      <c r="FY20" s="57"/>
-      <c r="FZ20" s="57"/>
-      <c r="GA20" s="57"/>
-      <c r="GB20" s="57"/>
-      <c r="GC20" s="57"/>
-      <c r="GD20" s="57"/>
-      <c r="GE20" s="57"/>
-      <c r="GF20" s="57"/>
-      <c r="GG20" s="57"/>
-      <c r="GH20" s="57"/>
-      <c r="GI20" s="57"/>
-      <c r="GJ20" s="57"/>
-      <c r="GK20" s="57"/>
-      <c r="GL20" s="57"/>
-      <c r="GM20" s="57"/>
-      <c r="GN20" s="57"/>
-      <c r="GO20" s="57"/>
-      <c r="GP20" s="57"/>
-      <c r="GQ20" s="57"/>
-      <c r="GR20" s="57"/>
-      <c r="GS20" s="57"/>
-      <c r="GT20" s="57"/>
-      <c r="GU20" s="57"/>
-      <c r="GV20" s="57"/>
-      <c r="GW20" s="57"/>
-      <c r="GX20" s="57"/>
-      <c r="GY20" s="57"/>
-      <c r="GZ20" s="57"/>
-      <c r="HA20" s="57"/>
-      <c r="HB20" s="57"/>
-      <c r="HC20" s="57"/>
-      <c r="HD20" s="57"/>
-      <c r="HE20" s="57"/>
-      <c r="HF20" s="57"/>
-      <c r="HG20" s="57"/>
-      <c r="HH20" s="57"/>
-      <c r="HI20" s="57"/>
-      <c r="HJ20" s="57"/>
-      <c r="HK20" s="57"/>
-      <c r="HL20" s="57"/>
-      <c r="HM20" s="57"/>
-      <c r="HN20" s="57"/>
-      <c r="HO20" s="57"/>
-      <c r="HP20" s="57"/>
-      <c r="HQ20" s="57"/>
-      <c r="HR20" s="57"/>
-      <c r="HS20" s="57"/>
-      <c r="HT20" s="57"/>
-      <c r="HU20" s="57"/>
-      <c r="HV20" s="57"/>
-      <c r="HW20" s="57"/>
-      <c r="HX20" s="57"/>
-      <c r="HY20" s="57"/>
-      <c r="HZ20" s="57"/>
-      <c r="IA20" s="57"/>
-      <c r="IB20" s="57"/>
-      <c r="IC20" s="57"/>
-      <c r="ID20" s="57"/>
-      <c r="IE20" s="57"/>
-      <c r="IF20" s="57"/>
-      <c r="IG20" s="57"/>
-      <c r="IH20" s="57"/>
-      <c r="II20" s="57"/>
-      <c r="IJ20" s="57"/>
-      <c r="IK20" s="57"/>
-      <c r="IL20" s="57"/>
-      <c r="IM20" s="57"/>
-      <c r="IN20" s="57"/>
-      <c r="IO20" s="57"/>
-      <c r="IP20" s="57"/>
-      <c r="IQ20" s="57"/>
-      <c r="IR20" s="57"/>
-      <c r="IS20" s="57"/>
-      <c r="IT20" s="57"/>
-      <c r="IU20" s="57"/>
-      <c r="IV20" s="57"/>
-    </row>
-    <row r="21" spans="1:256">
-      <c r="A21" s="55"/>
-      <c r="D21" s="56" t="s">
-        <v>172</v>
-      </c>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="57"/>
-      <c r="P21" s="57"/>
-      <c r="Q21" s="57"/>
-      <c r="R21" s="57"/>
-      <c r="S21" s="57"/>
-      <c r="T21" s="57"/>
-      <c r="U21" s="57"/>
-      <c r="V21" s="57"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="57"/>
-      <c r="Y21" s="57"/>
-      <c r="Z21" s="57"/>
-      <c r="AA21" s="57"/>
-      <c r="AB21" s="57"/>
-      <c r="AC21" s="57"/>
-      <c r="AD21" s="57"/>
-      <c r="AE21" s="57"/>
-      <c r="AF21" s="57"/>
-      <c r="AG21" s="57"/>
-      <c r="AH21" s="57"/>
-      <c r="AI21" s="57"/>
-      <c r="AJ21" s="57"/>
-      <c r="AK21" s="57"/>
-      <c r="AL21" s="57"/>
-      <c r="AM21" s="57"/>
-      <c r="AN21" s="57"/>
-      <c r="AO21" s="57"/>
-      <c r="AP21" s="57"/>
-      <c r="AQ21" s="57"/>
-      <c r="AR21" s="57"/>
-      <c r="AS21" s="57"/>
-      <c r="AT21" s="57"/>
-      <c r="AU21" s="57"/>
-      <c r="AV21" s="57"/>
-      <c r="AW21" s="57"/>
-      <c r="AX21" s="57"/>
-      <c r="AY21" s="57"/>
-      <c r="AZ21" s="57"/>
-      <c r="BA21" s="57"/>
-      <c r="BB21" s="57"/>
-      <c r="BC21" s="57"/>
-      <c r="BD21" s="57"/>
-      <c r="BE21" s="57"/>
-      <c r="BF21" s="57"/>
-      <c r="BG21" s="57"/>
-      <c r="BH21" s="57"/>
-      <c r="BI21" s="57"/>
-      <c r="BJ21" s="57"/>
-      <c r="BK21" s="57"/>
-      <c r="BL21" s="57"/>
-      <c r="BM21" s="57"/>
-      <c r="BN21" s="57"/>
-      <c r="BO21" s="57"/>
-      <c r="BP21" s="57"/>
-      <c r="BQ21" s="57"/>
-      <c r="BR21" s="57"/>
-      <c r="BS21" s="57"/>
-      <c r="BT21" s="57"/>
-      <c r="BU21" s="57"/>
-      <c r="BV21" s="57"/>
-      <c r="BW21" s="57"/>
-      <c r="BX21" s="57"/>
-      <c r="BY21" s="57"/>
-      <c r="BZ21" s="57"/>
-      <c r="CA21" s="57"/>
-      <c r="CB21" s="57"/>
-      <c r="CC21" s="57"/>
-      <c r="CD21" s="57"/>
-      <c r="CE21" s="57"/>
-      <c r="CF21" s="57"/>
-      <c r="CG21" s="57"/>
-      <c r="CH21" s="57"/>
-      <c r="CI21" s="57"/>
-      <c r="CJ21" s="57"/>
-      <c r="CK21" s="57"/>
-      <c r="CL21" s="57"/>
-      <c r="CM21" s="57"/>
-      <c r="CN21" s="57"/>
-      <c r="CO21" s="57"/>
-      <c r="CP21" s="57"/>
-      <c r="CQ21" s="57"/>
-      <c r="CR21" s="57"/>
-      <c r="CS21" s="57"/>
-      <c r="CT21" s="57"/>
-      <c r="CU21" s="57"/>
-      <c r="CV21" s="57"/>
-      <c r="CW21" s="57"/>
-      <c r="CX21" s="57"/>
-      <c r="CY21" s="57"/>
-      <c r="CZ21" s="57"/>
-      <c r="DA21" s="57"/>
-      <c r="DB21" s="57"/>
-      <c r="DC21" s="57"/>
-      <c r="DD21" s="57"/>
-      <c r="DE21" s="57"/>
-      <c r="DF21" s="57"/>
-      <c r="DG21" s="57"/>
-      <c r="DH21" s="57"/>
-      <c r="DI21" s="57"/>
-      <c r="DJ21" s="57"/>
-      <c r="DK21" s="57"/>
-      <c r="DL21" s="57"/>
-      <c r="DM21" s="57"/>
-      <c r="DN21" s="57"/>
-      <c r="DO21" s="57"/>
-      <c r="DP21" s="57"/>
-      <c r="DQ21" s="57"/>
-      <c r="DR21" s="57"/>
-      <c r="DS21" s="57"/>
-      <c r="DT21" s="57"/>
-      <c r="DU21" s="57"/>
-      <c r="DV21" s="57"/>
-      <c r="DW21" s="57"/>
-      <c r="DX21" s="57"/>
-      <c r="DY21" s="57"/>
-      <c r="DZ21" s="57"/>
-      <c r="EA21" s="57"/>
-      <c r="EB21" s="57"/>
-      <c r="EC21" s="57"/>
-      <c r="ED21" s="57"/>
-      <c r="EE21" s="57"/>
-      <c r="EF21" s="57"/>
-      <c r="EG21" s="57"/>
-      <c r="EH21" s="57"/>
-      <c r="EI21" s="57"/>
-      <c r="EJ21" s="57"/>
-      <c r="EK21" s="57"/>
-      <c r="EL21" s="57"/>
-      <c r="EM21" s="57"/>
-      <c r="EN21" s="57"/>
-      <c r="EO21" s="57"/>
-      <c r="EP21" s="57"/>
-      <c r="EQ21" s="57"/>
-      <c r="ER21" s="57"/>
-      <c r="ES21" s="57"/>
-      <c r="ET21" s="57"/>
-      <c r="EU21" s="57"/>
-      <c r="EV21" s="57"/>
-      <c r="EW21" s="57"/>
-      <c r="EX21" s="57"/>
-      <c r="EY21" s="57"/>
-      <c r="EZ21" s="57"/>
-      <c r="FA21" s="57"/>
-      <c r="FB21" s="57"/>
-      <c r="FC21" s="57"/>
-      <c r="FD21" s="57"/>
-      <c r="FE21" s="57"/>
-      <c r="FF21" s="57"/>
-      <c r="FG21" s="57"/>
-      <c r="FH21" s="57"/>
-      <c r="FI21" s="57"/>
-      <c r="FJ21" s="57"/>
-      <c r="FK21" s="57"/>
-      <c r="FL21" s="57"/>
-      <c r="FM21" s="57"/>
-      <c r="FN21" s="57"/>
-      <c r="FO21" s="57"/>
-      <c r="FP21" s="57"/>
-      <c r="FQ21" s="57"/>
-      <c r="FR21" s="57"/>
-      <c r="FS21" s="57"/>
-      <c r="FT21" s="57"/>
-      <c r="FU21" s="57"/>
-      <c r="FV21" s="57"/>
-      <c r="FW21" s="57"/>
-      <c r="FX21" s="57"/>
-      <c r="FY21" s="57"/>
-      <c r="FZ21" s="57"/>
-      <c r="GA21" s="57"/>
-      <c r="GB21" s="57"/>
-      <c r="GC21" s="57"/>
-      <c r="GD21" s="57"/>
-      <c r="GE21" s="57"/>
-      <c r="GF21" s="57"/>
-      <c r="GG21" s="57"/>
-      <c r="GH21" s="57"/>
-      <c r="GI21" s="57"/>
-      <c r="GJ21" s="57"/>
-      <c r="GK21" s="57"/>
-      <c r="GL21" s="57"/>
-      <c r="GM21" s="57"/>
-      <c r="GN21" s="57"/>
-      <c r="GO21" s="57"/>
-      <c r="GP21" s="57"/>
-      <c r="GQ21" s="57"/>
-      <c r="GR21" s="57"/>
-      <c r="GS21" s="57"/>
-      <c r="GT21" s="57"/>
-      <c r="GU21" s="57"/>
-      <c r="GV21" s="57"/>
-      <c r="GW21" s="57"/>
-      <c r="GX21" s="57"/>
-      <c r="GY21" s="57"/>
-      <c r="GZ21" s="57"/>
-      <c r="HA21" s="57"/>
-      <c r="HB21" s="57"/>
-      <c r="HC21" s="57"/>
-      <c r="HD21" s="57"/>
-      <c r="HE21" s="57"/>
-      <c r="HF21" s="57"/>
-      <c r="HG21" s="57"/>
-      <c r="HH21" s="57"/>
-      <c r="HI21" s="57"/>
-      <c r="HJ21" s="57"/>
-      <c r="HK21" s="57"/>
-      <c r="HL21" s="57"/>
-      <c r="HM21" s="57"/>
-      <c r="HN21" s="57"/>
-      <c r="HO21" s="57"/>
-      <c r="HP21" s="57"/>
-      <c r="HQ21" s="57"/>
-      <c r="HR21" s="57"/>
-      <c r="HS21" s="57"/>
-      <c r="HT21" s="57"/>
-      <c r="HU21" s="57"/>
-      <c r="HV21" s="57"/>
-      <c r="HW21" s="57"/>
-      <c r="HX21" s="57"/>
-      <c r="HY21" s="57"/>
-      <c r="HZ21" s="57"/>
-      <c r="IA21" s="57"/>
-      <c r="IB21" s="57"/>
-      <c r="IC21" s="57"/>
-      <c r="ID21" s="57"/>
-      <c r="IE21" s="57"/>
-      <c r="IF21" s="57"/>
-      <c r="IG21" s="57"/>
-      <c r="IH21" s="57"/>
-      <c r="II21" s="57"/>
-      <c r="IJ21" s="57"/>
-      <c r="IK21" s="57"/>
-      <c r="IL21" s="57"/>
-      <c r="IM21" s="57"/>
-      <c r="IN21" s="57"/>
-      <c r="IO21" s="57"/>
-      <c r="IP21" s="57"/>
-      <c r="IQ21" s="57"/>
-      <c r="IR21" s="57"/>
-      <c r="IS21" s="57"/>
-      <c r="IT21" s="57"/>
-      <c r="IU21" s="57"/>
-      <c r="IV21" s="57"/>
-    </row>
-    <row r="22" spans="1:256">
-      <c r="A22" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="57"/>
-      <c r="P22" s="57"/>
-      <c r="Q22" s="57"/>
-      <c r="R22" s="57"/>
-      <c r="S22" s="57"/>
-      <c r="T22" s="57"/>
-      <c r="U22" s="57"/>
-      <c r="V22" s="57"/>
-      <c r="W22" s="57"/>
-      <c r="X22" s="57"/>
-      <c r="Y22" s="57"/>
-      <c r="Z22" s="57"/>
-      <c r="AA22" s="57"/>
-      <c r="AB22" s="57"/>
-      <c r="AC22" s="57"/>
-      <c r="AD22" s="57"/>
-      <c r="AE22" s="57"/>
-      <c r="AF22" s="57"/>
-      <c r="AG22" s="57"/>
-      <c r="AH22" s="57"/>
-      <c r="AI22" s="57"/>
-      <c r="AJ22" s="57"/>
-      <c r="AK22" s="57"/>
-      <c r="AL22" s="57"/>
-      <c r="AM22" s="57"/>
-      <c r="AN22" s="57"/>
-      <c r="AO22" s="57"/>
-      <c r="AP22" s="57"/>
-      <c r="AQ22" s="57"/>
-      <c r="AR22" s="57"/>
-      <c r="AS22" s="57"/>
-      <c r="AT22" s="57"/>
-      <c r="AU22" s="57"/>
-      <c r="AV22" s="57"/>
-      <c r="AW22" s="57"/>
-      <c r="AX22" s="57"/>
-      <c r="AY22" s="57"/>
-      <c r="AZ22" s="57"/>
-      <c r="BA22" s="57"/>
-      <c r="BB22" s="57"/>
-      <c r="BC22" s="57"/>
-      <c r="BD22" s="57"/>
-      <c r="BE22" s="57"/>
-      <c r="BF22" s="57"/>
-      <c r="BG22" s="57"/>
-      <c r="BH22" s="57"/>
-      <c r="BI22" s="57"/>
-      <c r="BJ22" s="57"/>
-      <c r="BK22" s="57"/>
-      <c r="BL22" s="57"/>
-      <c r="BM22" s="57"/>
-      <c r="BN22" s="57"/>
-      <c r="BO22" s="57"/>
-      <c r="BP22" s="57"/>
-      <c r="BQ22" s="57"/>
-      <c r="BR22" s="57"/>
-      <c r="BS22" s="57"/>
-      <c r="BT22" s="57"/>
-      <c r="BU22" s="57"/>
-      <c r="BV22" s="57"/>
-      <c r="BW22" s="57"/>
-      <c r="BX22" s="57"/>
-      <c r="BY22" s="57"/>
-      <c r="BZ22" s="57"/>
-      <c r="CA22" s="57"/>
-      <c r="CB22" s="57"/>
-      <c r="CC22" s="57"/>
-      <c r="CD22" s="57"/>
-      <c r="CE22" s="57"/>
-      <c r="CF22" s="57"/>
-      <c r="CG22" s="57"/>
-      <c r="CH22" s="57"/>
-      <c r="CI22" s="57"/>
-      <c r="CJ22" s="57"/>
-      <c r="CK22" s="57"/>
-      <c r="CL22" s="57"/>
-      <c r="CM22" s="57"/>
-      <c r="CN22" s="57"/>
-      <c r="CO22" s="57"/>
-      <c r="CP22" s="57"/>
-      <c r="CQ22" s="57"/>
-      <c r="CR22" s="57"/>
-      <c r="CS22" s="57"/>
-      <c r="CT22" s="57"/>
-      <c r="CU22" s="57"/>
-      <c r="CV22" s="57"/>
-      <c r="CW22" s="57"/>
-      <c r="CX22" s="57"/>
-      <c r="CY22" s="57"/>
-      <c r="CZ22" s="57"/>
-      <c r="DA22" s="57"/>
-      <c r="DB22" s="57"/>
-      <c r="DC22" s="57"/>
-      <c r="DD22" s="57"/>
-      <c r="DE22" s="57"/>
-      <c r="DF22" s="57"/>
-      <c r="DG22" s="57"/>
-      <c r="DH22" s="57"/>
-      <c r="DI22" s="57"/>
-      <c r="DJ22" s="57"/>
-      <c r="DK22" s="57"/>
-      <c r="DL22" s="57"/>
-      <c r="DM22" s="57"/>
-      <c r="DN22" s="57"/>
-      <c r="DO22" s="57"/>
-      <c r="DP22" s="57"/>
-      <c r="DQ22" s="57"/>
-      <c r="DR22" s="57"/>
-      <c r="DS22" s="57"/>
-      <c r="DT22" s="57"/>
-      <c r="DU22" s="57"/>
-      <c r="DV22" s="57"/>
-      <c r="DW22" s="57"/>
-      <c r="DX22" s="57"/>
-      <c r="DY22" s="57"/>
-      <c r="DZ22" s="57"/>
-      <c r="EA22" s="57"/>
-      <c r="EB22" s="57"/>
-      <c r="EC22" s="57"/>
-      <c r="ED22" s="57"/>
-      <c r="EE22" s="57"/>
-      <c r="EF22" s="57"/>
-      <c r="EG22" s="57"/>
-      <c r="EH22" s="57"/>
-      <c r="EI22" s="57"/>
-      <c r="EJ22" s="57"/>
-      <c r="EK22" s="57"/>
-      <c r="EL22" s="57"/>
-      <c r="EM22" s="57"/>
-      <c r="EN22" s="57"/>
-      <c r="EO22" s="57"/>
-      <c r="EP22" s="57"/>
-      <c r="EQ22" s="57"/>
-      <c r="ER22" s="57"/>
-      <c r="ES22" s="57"/>
-      <c r="ET22" s="57"/>
-      <c r="EU22" s="57"/>
-      <c r="EV22" s="57"/>
-      <c r="EW22" s="57"/>
-      <c r="EX22" s="57"/>
-      <c r="EY22" s="57"/>
-      <c r="EZ22" s="57"/>
-      <c r="FA22" s="57"/>
-      <c r="FB22" s="57"/>
-      <c r="FC22" s="57"/>
-      <c r="FD22" s="57"/>
-      <c r="FE22" s="57"/>
-      <c r="FF22" s="57"/>
-      <c r="FG22" s="57"/>
-      <c r="FH22" s="57"/>
-      <c r="FI22" s="57"/>
-      <c r="FJ22" s="57"/>
-      <c r="FK22" s="57"/>
-      <c r="FL22" s="57"/>
-      <c r="FM22" s="57"/>
-      <c r="FN22" s="57"/>
-      <c r="FO22" s="57"/>
-      <c r="FP22" s="57"/>
-      <c r="FQ22" s="57"/>
-      <c r="FR22" s="57"/>
-      <c r="FS22" s="57"/>
-      <c r="FT22" s="57"/>
-      <c r="FU22" s="57"/>
-      <c r="FV22" s="57"/>
-      <c r="FW22" s="57"/>
-      <c r="FX22" s="57"/>
-      <c r="FY22" s="57"/>
-      <c r="FZ22" s="57"/>
-      <c r="GA22" s="57"/>
-      <c r="GB22" s="57"/>
-      <c r="GC22" s="57"/>
-      <c r="GD22" s="57"/>
-      <c r="GE22" s="57"/>
-      <c r="GF22" s="57"/>
-      <c r="GG22" s="57"/>
-      <c r="GH22" s="57"/>
-      <c r="GI22" s="57"/>
-      <c r="GJ22" s="57"/>
-      <c r="GK22" s="57"/>
-      <c r="GL22" s="57"/>
-      <c r="GM22" s="57"/>
-      <c r="GN22" s="57"/>
-      <c r="GO22" s="57"/>
-      <c r="GP22" s="57"/>
-      <c r="GQ22" s="57"/>
-      <c r="GR22" s="57"/>
-      <c r="GS22" s="57"/>
-      <c r="GT22" s="57"/>
-      <c r="GU22" s="57"/>
-      <c r="GV22" s="57"/>
-      <c r="GW22" s="57"/>
-      <c r="GX22" s="57"/>
-      <c r="GY22" s="57"/>
-      <c r="GZ22" s="57"/>
-      <c r="HA22" s="57"/>
-      <c r="HB22" s="57"/>
-      <c r="HC22" s="57"/>
-      <c r="HD22" s="57"/>
-      <c r="HE22" s="57"/>
-      <c r="HF22" s="57"/>
-      <c r="HG22" s="57"/>
-      <c r="HH22" s="57"/>
-      <c r="HI22" s="57"/>
-      <c r="HJ22" s="57"/>
-      <c r="HK22" s="57"/>
-      <c r="HL22" s="57"/>
-      <c r="HM22" s="57"/>
-      <c r="HN22" s="57"/>
-      <c r="HO22" s="57"/>
-      <c r="HP22" s="57"/>
-      <c r="HQ22" s="57"/>
-      <c r="HR22" s="57"/>
-      <c r="HS22" s="57"/>
-      <c r="HT22" s="57"/>
-      <c r="HU22" s="57"/>
-      <c r="HV22" s="57"/>
-      <c r="HW22" s="57"/>
-      <c r="HX22" s="57"/>
-      <c r="HY22" s="57"/>
-      <c r="HZ22" s="57"/>
-      <c r="IA22" s="57"/>
-      <c r="IB22" s="57"/>
-      <c r="IC22" s="57"/>
-      <c r="ID22" s="57"/>
-      <c r="IE22" s="57"/>
-      <c r="IF22" s="57"/>
-      <c r="IG22" s="57"/>
-      <c r="IH22" s="57"/>
-      <c r="II22" s="57"/>
-      <c r="IJ22" s="57"/>
-      <c r="IK22" s="57"/>
-      <c r="IL22" s="57"/>
-      <c r="IM22" s="57"/>
-      <c r="IN22" s="57"/>
-      <c r="IO22" s="57"/>
-      <c r="IP22" s="57"/>
-      <c r="IQ22" s="57"/>
-      <c r="IR22" s="57"/>
-      <c r="IS22" s="57"/>
-      <c r="IT22" s="57"/>
-      <c r="IU22" s="57"/>
-      <c r="IV22" s="57"/>
-    </row>
-    <row r="23" spans="1:256">
-      <c r="A23" s="58"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="57"/>
-      <c r="P23" s="57"/>
-      <c r="Q23" s="57"/>
-      <c r="R23" s="57"/>
-      <c r="S23" s="57"/>
-      <c r="T23" s="57"/>
-      <c r="U23" s="57"/>
-      <c r="V23" s="57"/>
-      <c r="W23" s="57"/>
-      <c r="X23" s="57"/>
-      <c r="Y23" s="57"/>
-      <c r="Z23" s="57"/>
-      <c r="AA23" s="57"/>
-      <c r="AB23" s="57"/>
-      <c r="AC23" s="57"/>
-      <c r="AD23" s="57"/>
-      <c r="AE23" s="57"/>
-      <c r="AF23" s="57"/>
-      <c r="AG23" s="57"/>
-      <c r="AH23" s="57"/>
-      <c r="AI23" s="57"/>
-      <c r="AJ23" s="57"/>
-      <c r="AK23" s="57"/>
-      <c r="AL23" s="57"/>
-      <c r="AM23" s="57"/>
-      <c r="AN23" s="57"/>
-      <c r="AO23" s="57"/>
-      <c r="AP23" s="57"/>
-      <c r="AQ23" s="57"/>
-      <c r="AR23" s="57"/>
-      <c r="AS23" s="57"/>
-      <c r="AT23" s="57"/>
-      <c r="AU23" s="57"/>
-      <c r="AV23" s="57"/>
-      <c r="AW23" s="57"/>
-      <c r="AX23" s="57"/>
-      <c r="AY23" s="57"/>
-      <c r="AZ23" s="57"/>
-      <c r="BA23" s="57"/>
-      <c r="BB23" s="57"/>
-      <c r="BC23" s="57"/>
-      <c r="BD23" s="57"/>
-      <c r="BE23" s="57"/>
-      <c r="BF23" s="57"/>
-      <c r="BG23" s="57"/>
-      <c r="BH23" s="57"/>
-      <c r="BI23" s="57"/>
-      <c r="BJ23" s="57"/>
-      <c r="BK23" s="57"/>
-      <c r="BL23" s="57"/>
-      <c r="BM23" s="57"/>
-      <c r="BN23" s="57"/>
-      <c r="BO23" s="57"/>
-      <c r="BP23" s="57"/>
-      <c r="BQ23" s="57"/>
-      <c r="BR23" s="57"/>
-      <c r="BS23" s="57"/>
-      <c r="BT23" s="57"/>
-      <c r="BU23" s="57"/>
-      <c r="BV23" s="57"/>
-      <c r="BW23" s="57"/>
-      <c r="BX23" s="57"/>
-      <c r="BY23" s="57"/>
-      <c r="BZ23" s="57"/>
-      <c r="CA23" s="57"/>
-      <c r="CB23" s="57"/>
-      <c r="CC23" s="57"/>
-      <c r="CD23" s="57"/>
-      <c r="CE23" s="57"/>
-      <c r="CF23" s="57"/>
-      <c r="CG23" s="57"/>
-      <c r="CH23" s="57"/>
-      <c r="CI23" s="57"/>
-      <c r="CJ23" s="57"/>
-      <c r="CK23" s="57"/>
-      <c r="CL23" s="57"/>
-      <c r="CM23" s="57"/>
-      <c r="CN23" s="57"/>
-      <c r="CO23" s="57"/>
-      <c r="CP23" s="57"/>
-      <c r="CQ23" s="57"/>
-      <c r="CR23" s="57"/>
-      <c r="CS23" s="57"/>
-      <c r="CT23" s="57"/>
-      <c r="CU23" s="57"/>
-      <c r="CV23" s="57"/>
-      <c r="CW23" s="57"/>
-      <c r="CX23" s="57"/>
-      <c r="CY23" s="57"/>
-      <c r="CZ23" s="57"/>
-      <c r="DA23" s="57"/>
-      <c r="DB23" s="57"/>
-      <c r="DC23" s="57"/>
-      <c r="DD23" s="57"/>
-      <c r="DE23" s="57"/>
-      <c r="DF23" s="57"/>
-      <c r="DG23" s="57"/>
-      <c r="DH23" s="57"/>
-      <c r="DI23" s="57"/>
-      <c r="DJ23" s="57"/>
-      <c r="DK23" s="57"/>
-      <c r="DL23" s="57"/>
-      <c r="DM23" s="57"/>
-      <c r="DN23" s="57"/>
-      <c r="DO23" s="57"/>
-      <c r="DP23" s="57"/>
-      <c r="DQ23" s="57"/>
-      <c r="DR23" s="57"/>
-      <c r="DS23" s="57"/>
-      <c r="DT23" s="57"/>
-      <c r="DU23" s="57"/>
-      <c r="DV23" s="57"/>
-      <c r="DW23" s="57"/>
-      <c r="DX23" s="57"/>
-      <c r="DY23" s="57"/>
-      <c r="DZ23" s="57"/>
-      <c r="EA23" s="57"/>
-      <c r="EB23" s="57"/>
-      <c r="EC23" s="57"/>
-      <c r="ED23" s="57"/>
-      <c r="EE23" s="57"/>
-      <c r="EF23" s="57"/>
-      <c r="EG23" s="57"/>
-      <c r="EH23" s="57"/>
-      <c r="EI23" s="57"/>
-      <c r="EJ23" s="57"/>
-      <c r="EK23" s="57"/>
-      <c r="EL23" s="57"/>
-      <c r="EM23" s="57"/>
-      <c r="EN23" s="57"/>
-      <c r="EO23" s="57"/>
-      <c r="EP23" s="57"/>
-      <c r="EQ23" s="57"/>
-      <c r="ER23" s="57"/>
-      <c r="ES23" s="57"/>
-      <c r="ET23" s="57"/>
-      <c r="EU23" s="57"/>
-      <c r="EV23" s="57"/>
-      <c r="EW23" s="57"/>
-      <c r="EX23" s="57"/>
-      <c r="EY23" s="57"/>
-      <c r="EZ23" s="57"/>
-      <c r="FA23" s="57"/>
-      <c r="FB23" s="57"/>
-      <c r="FC23" s="57"/>
-      <c r="FD23" s="57"/>
-      <c r="FE23" s="57"/>
-      <c r="FF23" s="57"/>
-      <c r="FG23" s="57"/>
-      <c r="FH23" s="57"/>
-      <c r="FI23" s="57"/>
-      <c r="FJ23" s="57"/>
-      <c r="FK23" s="57"/>
-      <c r="FL23" s="57"/>
-      <c r="FM23" s="57"/>
-      <c r="FN23" s="57"/>
-      <c r="FO23" s="57"/>
-      <c r="FP23" s="57"/>
-      <c r="FQ23" s="57"/>
-      <c r="FR23" s="57"/>
-      <c r="FS23" s="57"/>
-      <c r="FT23" s="57"/>
-      <c r="FU23" s="57"/>
-      <c r="FV23" s="57"/>
-      <c r="FW23" s="57"/>
-      <c r="FX23" s="57"/>
-      <c r="FY23" s="57"/>
-      <c r="FZ23" s="57"/>
-      <c r="GA23" s="57"/>
-      <c r="GB23" s="57"/>
-      <c r="GC23" s="57"/>
-      <c r="GD23" s="57"/>
-      <c r="GE23" s="57"/>
-      <c r="GF23" s="57"/>
-      <c r="GG23" s="57"/>
-      <c r="GH23" s="57"/>
-      <c r="GI23" s="57"/>
-      <c r="GJ23" s="57"/>
-      <c r="GK23" s="57"/>
-      <c r="GL23" s="57"/>
-      <c r="GM23" s="57"/>
-      <c r="GN23" s="57"/>
-      <c r="GO23" s="57"/>
-      <c r="GP23" s="57"/>
-      <c r="GQ23" s="57"/>
-      <c r="GR23" s="57"/>
-      <c r="GS23" s="57"/>
-      <c r="GT23" s="57"/>
-      <c r="GU23" s="57"/>
-      <c r="GV23" s="57"/>
-      <c r="GW23" s="57"/>
-      <c r="GX23" s="57"/>
-      <c r="GY23" s="57"/>
-      <c r="GZ23" s="57"/>
-      <c r="HA23" s="57"/>
-      <c r="HB23" s="57"/>
-      <c r="HC23" s="57"/>
-      <c r="HD23" s="57"/>
-      <c r="HE23" s="57"/>
-      <c r="HF23" s="57"/>
-      <c r="HG23" s="57"/>
-      <c r="HH23" s="57"/>
-      <c r="HI23" s="57"/>
-      <c r="HJ23" s="57"/>
-      <c r="HK23" s="57"/>
-      <c r="HL23" s="57"/>
-      <c r="HM23" s="57"/>
-      <c r="HN23" s="57"/>
-      <c r="HO23" s="57"/>
-      <c r="HP23" s="57"/>
-      <c r="HQ23" s="57"/>
-      <c r="HR23" s="57"/>
-      <c r="HS23" s="57"/>
-      <c r="HT23" s="57"/>
-      <c r="HU23" s="57"/>
-      <c r="HV23" s="57"/>
-      <c r="HW23" s="57"/>
-      <c r="HX23" s="57"/>
-      <c r="HY23" s="57"/>
-      <c r="HZ23" s="57"/>
-      <c r="IA23" s="57"/>
-      <c r="IB23" s="57"/>
-      <c r="IC23" s="57"/>
-      <c r="ID23" s="57"/>
-      <c r="IE23" s="57"/>
-      <c r="IF23" s="57"/>
-      <c r="IG23" s="57"/>
-      <c r="IH23" s="57"/>
-      <c r="II23" s="57"/>
-      <c r="IJ23" s="57"/>
-      <c r="IK23" s="57"/>
-      <c r="IL23" s="57"/>
-      <c r="IM23" s="57"/>
-      <c r="IN23" s="57"/>
-      <c r="IO23" s="57"/>
-      <c r="IP23" s="57"/>
-      <c r="IQ23" s="57"/>
-      <c r="IR23" s="57"/>
-      <c r="IS23" s="57"/>
-      <c r="IT23" s="57"/>
-      <c r="IU23" s="57"/>
-      <c r="IV23" s="57"/>
-    </row>
-    <row r="24" spans="1:256">
-      <c r="A24" s="58"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="57"/>
-      <c r="M24" s="57"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="57"/>
-      <c r="P24" s="57"/>
-      <c r="Q24" s="57"/>
-      <c r="R24" s="57"/>
-      <c r="S24" s="57"/>
-      <c r="T24" s="57"/>
-      <c r="U24" s="57"/>
-      <c r="V24" s="57"/>
-      <c r="W24" s="57"/>
-      <c r="X24" s="57"/>
-      <c r="Y24" s="57"/>
-      <c r="Z24" s="57"/>
-      <c r="AA24" s="57"/>
-      <c r="AB24" s="57"/>
-      <c r="AC24" s="57"/>
-      <c r="AD24" s="57"/>
-      <c r="AE24" s="57"/>
-      <c r="AF24" s="57"/>
-      <c r="AG24" s="57"/>
-      <c r="AH24" s="57"/>
-      <c r="AI24" s="57"/>
-      <c r="AJ24" s="57"/>
-      <c r="AK24" s="57"/>
-      <c r="AL24" s="57"/>
-      <c r="AM24" s="57"/>
-      <c r="AN24" s="57"/>
-      <c r="AO24" s="57"/>
-      <c r="AP24" s="57"/>
-      <c r="AQ24" s="57"/>
-      <c r="AR24" s="57"/>
-      <c r="AS24" s="57"/>
-      <c r="AT24" s="57"/>
-      <c r="AU24" s="57"/>
-      <c r="AV24" s="57"/>
-      <c r="AW24" s="57"/>
-      <c r="AX24" s="57"/>
-      <c r="AY24" s="57"/>
-      <c r="AZ24" s="57"/>
-      <c r="BA24" s="57"/>
-      <c r="BB24" s="57"/>
-      <c r="BC24" s="57"/>
-      <c r="BD24" s="57"/>
-      <c r="BE24" s="57"/>
-      <c r="BF24" s="57"/>
-      <c r="BG24" s="57"/>
-      <c r="BH24" s="57"/>
-      <c r="BI24" s="57"/>
-      <c r="BJ24" s="57"/>
-      <c r="BK24" s="57"/>
-      <c r="BL24" s="57"/>
-      <c r="BM24" s="57"/>
-      <c r="BN24" s="57"/>
-      <c r="BO24" s="57"/>
-      <c r="BP24" s="57"/>
-      <c r="BQ24" s="57"/>
-      <c r="BR24" s="57"/>
-      <c r="BS24" s="57"/>
-      <c r="BT24" s="57"/>
-      <c r="BU24" s="57"/>
-      <c r="BV24" s="57"/>
-      <c r="BW24" s="57"/>
-      <c r="BX24" s="57"/>
-      <c r="BY24" s="57"/>
-      <c r="BZ24" s="57"/>
-      <c r="CA24" s="57"/>
-      <c r="CB24" s="57"/>
-      <c r="CC24" s="57"/>
-      <c r="CD24" s="57"/>
-      <c r="CE24" s="57"/>
-      <c r="CF24" s="57"/>
-      <c r="CG24" s="57"/>
-      <c r="CH24" s="57"/>
-      <c r="CI24" s="57"/>
-      <c r="CJ24" s="57"/>
-      <c r="CK24" s="57"/>
-      <c r="CL24" s="57"/>
-      <c r="CM24" s="57"/>
-      <c r="CN24" s="57"/>
-      <c r="CO24" s="57"/>
-      <c r="CP24" s="57"/>
-      <c r="CQ24" s="57"/>
-      <c r="CR24" s="57"/>
-      <c r="CS24" s="57"/>
-      <c r="CT24" s="57"/>
-      <c r="CU24" s="57"/>
-      <c r="CV24" s="57"/>
-      <c r="CW24" s="57"/>
-      <c r="CX24" s="57"/>
-      <c r="CY24" s="57"/>
-      <c r="CZ24" s="57"/>
-      <c r="DA24" s="57"/>
-      <c r="DB24" s="57"/>
-      <c r="DC24" s="57"/>
-      <c r="DD24" s="57"/>
-      <c r="DE24" s="57"/>
-      <c r="DF24" s="57"/>
-      <c r="DG24" s="57"/>
-      <c r="DH24" s="57"/>
-      <c r="DI24" s="57"/>
-      <c r="DJ24" s="57"/>
-      <c r="DK24" s="57"/>
-      <c r="DL24" s="57"/>
-      <c r="DM24" s="57"/>
-      <c r="DN24" s="57"/>
-      <c r="DO24" s="57"/>
-      <c r="DP24" s="57"/>
-      <c r="DQ24" s="57"/>
-      <c r="DR24" s="57"/>
-      <c r="DS24" s="57"/>
-      <c r="DT24" s="57"/>
-      <c r="DU24" s="57"/>
-      <c r="DV24" s="57"/>
-      <c r="DW24" s="57"/>
-      <c r="DX24" s="57"/>
-      <c r="DY24" s="57"/>
-      <c r="DZ24" s="57"/>
-      <c r="EA24" s="57"/>
-      <c r="EB24" s="57"/>
-      <c r="EC24" s="57"/>
-      <c r="ED24" s="57"/>
-      <c r="EE24" s="57"/>
-      <c r="EF24" s="57"/>
-      <c r="EG24" s="57"/>
-      <c r="EH24" s="57"/>
-      <c r="EI24" s="57"/>
-      <c r="EJ24" s="57"/>
-      <c r="EK24" s="57"/>
-      <c r="EL24" s="57"/>
-      <c r="EM24" s="57"/>
-      <c r="EN24" s="57"/>
-      <c r="EO24" s="57"/>
-      <c r="EP24" s="57"/>
-      <c r="EQ24" s="57"/>
-      <c r="ER24" s="57"/>
-      <c r="ES24" s="57"/>
-      <c r="ET24" s="57"/>
-      <c r="EU24" s="57"/>
-      <c r="EV24" s="57"/>
-      <c r="EW24" s="57"/>
-      <c r="EX24" s="57"/>
-      <c r="EY24" s="57"/>
-      <c r="EZ24" s="57"/>
-      <c r="FA24" s="57"/>
-      <c r="FB24" s="57"/>
-      <c r="FC24" s="57"/>
-      <c r="FD24" s="57"/>
-      <c r="FE24" s="57"/>
-      <c r="FF24" s="57"/>
-      <c r="FG24" s="57"/>
-      <c r="FH24" s="57"/>
-      <c r="FI24" s="57"/>
-      <c r="FJ24" s="57"/>
-      <c r="FK24" s="57"/>
-      <c r="FL24" s="57"/>
-      <c r="FM24" s="57"/>
-      <c r="FN24" s="57"/>
-      <c r="FO24" s="57"/>
-      <c r="FP24" s="57"/>
-      <c r="FQ24" s="57"/>
-      <c r="FR24" s="57"/>
-      <c r="FS24" s="57"/>
-      <c r="FT24" s="57"/>
-      <c r="FU24" s="57"/>
-      <c r="FV24" s="57"/>
-      <c r="FW24" s="57"/>
-      <c r="FX24" s="57"/>
-      <c r="FY24" s="57"/>
-      <c r="FZ24" s="57"/>
-      <c r="GA24" s="57"/>
-      <c r="GB24" s="57"/>
-      <c r="GC24" s="57"/>
-      <c r="GD24" s="57"/>
-      <c r="GE24" s="57"/>
-      <c r="GF24" s="57"/>
-      <c r="GG24" s="57"/>
-      <c r="GH24" s="57"/>
-      <c r="GI24" s="57"/>
-      <c r="GJ24" s="57"/>
-      <c r="GK24" s="57"/>
-      <c r="GL24" s="57"/>
-      <c r="GM24" s="57"/>
-      <c r="GN24" s="57"/>
-      <c r="GO24" s="57"/>
-      <c r="GP24" s="57"/>
-      <c r="GQ24" s="57"/>
-      <c r="GR24" s="57"/>
-      <c r="GS24" s="57"/>
-      <c r="GT24" s="57"/>
-      <c r="GU24" s="57"/>
-      <c r="GV24" s="57"/>
-      <c r="GW24" s="57"/>
-      <c r="GX24" s="57"/>
-      <c r="GY24" s="57"/>
-      <c r="GZ24" s="57"/>
-      <c r="HA24" s="57"/>
-      <c r="HB24" s="57"/>
-      <c r="HC24" s="57"/>
-      <c r="HD24" s="57"/>
-      <c r="HE24" s="57"/>
-      <c r="HF24" s="57"/>
-      <c r="HG24" s="57"/>
-      <c r="HH24" s="57"/>
-      <c r="HI24" s="57"/>
-      <c r="HJ24" s="57"/>
-      <c r="HK24" s="57"/>
-      <c r="HL24" s="57"/>
-      <c r="HM24" s="57"/>
-      <c r="HN24" s="57"/>
-      <c r="HO24" s="57"/>
-      <c r="HP24" s="57"/>
-      <c r="HQ24" s="57"/>
-      <c r="HR24" s="57"/>
-      <c r="HS24" s="57"/>
-      <c r="HT24" s="57"/>
-      <c r="HU24" s="57"/>
-      <c r="HV24" s="57"/>
-      <c r="HW24" s="57"/>
-      <c r="HX24" s="57"/>
-      <c r="HY24" s="57"/>
-      <c r="HZ24" s="57"/>
-      <c r="IA24" s="57"/>
-      <c r="IB24" s="57"/>
-      <c r="IC24" s="57"/>
-      <c r="ID24" s="57"/>
-      <c r="IE24" s="57"/>
-      <c r="IF24" s="57"/>
-      <c r="IG24" s="57"/>
-      <c r="IH24" s="57"/>
-      <c r="II24" s="57"/>
-      <c r="IJ24" s="57"/>
-      <c r="IK24" s="57"/>
-      <c r="IL24" s="57"/>
-      <c r="IM24" s="57"/>
-      <c r="IN24" s="57"/>
-      <c r="IO24" s="57"/>
-      <c r="IP24" s="57"/>
-      <c r="IQ24" s="57"/>
-      <c r="IR24" s="57"/>
-      <c r="IS24" s="57"/>
-      <c r="IT24" s="57"/>
-      <c r="IU24" s="57"/>
-      <c r="IV24" s="57"/>
-    </row>
-    <row r="25" spans="1:256" ht="17.25">
-      <c r="A25" s="59" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="57"/>
-      <c r="P25" s="57"/>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="57"/>
-      <c r="S25" s="57"/>
-      <c r="T25" s="57"/>
-      <c r="U25" s="57"/>
-      <c r="V25" s="57"/>
-      <c r="W25" s="57"/>
-      <c r="X25" s="57"/>
-      <c r="Y25" s="57"/>
-      <c r="Z25" s="57"/>
-      <c r="AA25" s="57"/>
-      <c r="AB25" s="57"/>
-      <c r="AC25" s="57"/>
-      <c r="AD25" s="57"/>
-      <c r="AE25" s="57"/>
-      <c r="AF25" s="57"/>
-      <c r="AG25" s="57"/>
-      <c r="AH25" s="57"/>
-      <c r="AI25" s="57"/>
-      <c r="AJ25" s="57"/>
-      <c r="AK25" s="57"/>
-      <c r="AL25" s="57"/>
-      <c r="AM25" s="57"/>
-      <c r="AN25" s="57"/>
-      <c r="AO25" s="57"/>
-      <c r="AP25" s="57"/>
-      <c r="AQ25" s="57"/>
-      <c r="AR25" s="57"/>
-      <c r="AS25" s="57"/>
-      <c r="AT25" s="57"/>
-      <c r="AU25" s="57"/>
-      <c r="AV25" s="57"/>
-      <c r="AW25" s="57"/>
-      <c r="AX25" s="57"/>
-      <c r="AY25" s="57"/>
-      <c r="AZ25" s="57"/>
-      <c r="BA25" s="57"/>
-      <c r="BB25" s="57"/>
-      <c r="BC25" s="57"/>
-      <c r="BD25" s="57"/>
-      <c r="BE25" s="57"/>
-      <c r="BF25" s="57"/>
-      <c r="BG25" s="57"/>
-      <c r="BH25" s="57"/>
-      <c r="BI25" s="57"/>
-      <c r="BJ25" s="57"/>
-      <c r="BK25" s="57"/>
-      <c r="BL25" s="57"/>
-      <c r="BM25" s="57"/>
-      <c r="BN25" s="57"/>
-      <c r="BO25" s="57"/>
-      <c r="BP25" s="57"/>
-      <c r="BQ25" s="57"/>
-      <c r="BR25" s="57"/>
-      <c r="BS25" s="57"/>
-      <c r="BT25" s="57"/>
-      <c r="BU25" s="57"/>
-      <c r="BV25" s="57"/>
-      <c r="BW25" s="57"/>
-      <c r="BX25" s="57"/>
-      <c r="BY25" s="57"/>
-      <c r="BZ25" s="57"/>
-      <c r="CA25" s="57"/>
-      <c r="CB25" s="57"/>
-      <c r="CC25" s="57"/>
-      <c r="CD25" s="57"/>
-      <c r="CE25" s="57"/>
-      <c r="CF25" s="57"/>
-      <c r="CG25" s="57"/>
-      <c r="CH25" s="57"/>
-      <c r="CI25" s="57"/>
-      <c r="CJ25" s="57"/>
-      <c r="CK25" s="57"/>
-      <c r="CL25" s="57"/>
-      <c r="CM25" s="57"/>
-      <c r="CN25" s="57"/>
-      <c r="CO25" s="57"/>
-      <c r="CP25" s="57"/>
-      <c r="CQ25" s="57"/>
-      <c r="CR25" s="57"/>
-      <c r="CS25" s="57"/>
-      <c r="CT25" s="57"/>
-      <c r="CU25" s="57"/>
-      <c r="CV25" s="57"/>
-      <c r="CW25" s="57"/>
-      <c r="CX25" s="57"/>
-      <c r="CY25" s="57"/>
-      <c r="CZ25" s="57"/>
-      <c r="DA25" s="57"/>
-      <c r="DB25" s="57"/>
-      <c r="DC25" s="57"/>
-      <c r="DD25" s="57"/>
-      <c r="DE25" s="57"/>
-      <c r="DF25" s="57"/>
-      <c r="DG25" s="57"/>
-      <c r="DH25" s="57"/>
-      <c r="DI25" s="57"/>
-      <c r="DJ25" s="57"/>
-      <c r="DK25" s="57"/>
-      <c r="DL25" s="57"/>
-      <c r="DM25" s="57"/>
-      <c r="DN25" s="57"/>
-      <c r="DO25" s="57"/>
-      <c r="DP25" s="57"/>
-      <c r="DQ25" s="57"/>
-      <c r="DR25" s="57"/>
-      <c r="DS25" s="57"/>
-      <c r="DT25" s="57"/>
-      <c r="DU25" s="57"/>
-      <c r="DV25" s="57"/>
-      <c r="DW25" s="57"/>
-      <c r="DX25" s="57"/>
-      <c r="DY25" s="57"/>
-      <c r="DZ25" s="57"/>
-      <c r="EA25" s="57"/>
-      <c r="EB25" s="57"/>
-      <c r="EC25" s="57"/>
-      <c r="ED25" s="57"/>
-      <c r="EE25" s="57"/>
-      <c r="EF25" s="57"/>
-      <c r="EG25" s="57"/>
-      <c r="EH25" s="57"/>
-      <c r="EI25" s="57"/>
-      <c r="EJ25" s="57"/>
-      <c r="EK25" s="57"/>
-      <c r="EL25" s="57"/>
-      <c r="EM25" s="57"/>
-      <c r="EN25" s="57"/>
-      <c r="EO25" s="57"/>
-      <c r="EP25" s="57"/>
-      <c r="EQ25" s="57"/>
-      <c r="ER25" s="57"/>
-      <c r="ES25" s="57"/>
-      <c r="ET25" s="57"/>
-      <c r="EU25" s="57"/>
-      <c r="EV25" s="57"/>
-      <c r="EW25" s="57"/>
-      <c r="EX25" s="57"/>
-      <c r="EY25" s="57"/>
-      <c r="EZ25" s="57"/>
-      <c r="FA25" s="57"/>
-      <c r="FB25" s="57"/>
-      <c r="FC25" s="57"/>
-      <c r="FD25" s="57"/>
-      <c r="FE25" s="57"/>
-      <c r="FF25" s="57"/>
-      <c r="FG25" s="57"/>
-      <c r="FH25" s="57"/>
-      <c r="FI25" s="57"/>
-      <c r="FJ25" s="57"/>
-      <c r="FK25" s="57"/>
-      <c r="FL25" s="57"/>
-      <c r="FM25" s="57"/>
-      <c r="FN25" s="57"/>
-      <c r="FO25" s="57"/>
-      <c r="FP25" s="57"/>
-      <c r="FQ25" s="57"/>
-      <c r="FR25" s="57"/>
-      <c r="FS25" s="57"/>
-      <c r="FT25" s="57"/>
-      <c r="FU25" s="57"/>
-      <c r="FV25" s="57"/>
-      <c r="FW25" s="57"/>
-      <c r="FX25" s="57"/>
-      <c r="FY25" s="57"/>
-      <c r="FZ25" s="57"/>
-      <c r="GA25" s="57"/>
-      <c r="GB25" s="57"/>
-      <c r="GC25" s="57"/>
-      <c r="GD25" s="57"/>
-      <c r="GE25" s="57"/>
-      <c r="GF25" s="57"/>
-      <c r="GG25" s="57"/>
-      <c r="GH25" s="57"/>
-      <c r="GI25" s="57"/>
-      <c r="GJ25" s="57"/>
-      <c r="GK25" s="57"/>
-      <c r="GL25" s="57"/>
-      <c r="GM25" s="57"/>
-      <c r="GN25" s="57"/>
-      <c r="GO25" s="57"/>
-      <c r="GP25" s="57"/>
-      <c r="GQ25" s="57"/>
-      <c r="GR25" s="57"/>
-      <c r="GS25" s="57"/>
-      <c r="GT25" s="57"/>
-      <c r="GU25" s="57"/>
-      <c r="GV25" s="57"/>
-      <c r="GW25" s="57"/>
-      <c r="GX25" s="57"/>
-      <c r="GY25" s="57"/>
-      <c r="GZ25" s="57"/>
-      <c r="HA25" s="57"/>
-      <c r="HB25" s="57"/>
-      <c r="HC25" s="57"/>
-      <c r="HD25" s="57"/>
-      <c r="HE25" s="57"/>
-      <c r="HF25" s="57"/>
-      <c r="HG25" s="57"/>
-      <c r="HH25" s="57"/>
-      <c r="HI25" s="57"/>
-      <c r="HJ25" s="57"/>
-      <c r="HK25" s="57"/>
-      <c r="HL25" s="57"/>
-      <c r="HM25" s="57"/>
-      <c r="HN25" s="57"/>
-      <c r="HO25" s="57"/>
-      <c r="HP25" s="57"/>
-      <c r="HQ25" s="57"/>
-      <c r="HR25" s="57"/>
-      <c r="HS25" s="57"/>
-      <c r="HT25" s="57"/>
-      <c r="HU25" s="57"/>
-      <c r="HV25" s="57"/>
-      <c r="HW25" s="57"/>
-      <c r="HX25" s="57"/>
-      <c r="HY25" s="57"/>
-      <c r="HZ25" s="57"/>
-      <c r="IA25" s="57"/>
-      <c r="IB25" s="57"/>
-      <c r="IC25" s="57"/>
-      <c r="ID25" s="57"/>
-      <c r="IE25" s="57"/>
-      <c r="IF25" s="57"/>
-      <c r="IG25" s="57"/>
-      <c r="IH25" s="57"/>
-      <c r="II25" s="57"/>
-      <c r="IJ25" s="57"/>
-      <c r="IK25" s="57"/>
-      <c r="IL25" s="57"/>
-      <c r="IM25" s="57"/>
-      <c r="IN25" s="57"/>
-      <c r="IO25" s="57"/>
-      <c r="IP25" s="57"/>
-      <c r="IQ25" s="57"/>
-      <c r="IR25" s="57"/>
-      <c r="IS25" s="57"/>
-      <c r="IT25" s="57"/>
-      <c r="IU25" s="57"/>
-      <c r="IV25" s="57"/>
-    </row>
-    <row r="26" spans="1:256">
-      <c r="A26" s="58" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="57"/>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="57"/>
-      <c r="R26" s="57"/>
-      <c r="S26" s="57"/>
-      <c r="T26" s="57"/>
-      <c r="U26" s="57"/>
-      <c r="V26" s="57"/>
-      <c r="W26" s="57"/>
-      <c r="X26" s="57"/>
-      <c r="Y26" s="57"/>
-      <c r="Z26" s="57"/>
-      <c r="AA26" s="57"/>
-      <c r="AB26" s="57"/>
-      <c r="AC26" s="57"/>
-      <c r="AD26" s="57"/>
-      <c r="AE26" s="57"/>
-      <c r="AF26" s="57"/>
-      <c r="AG26" s="57"/>
-      <c r="AH26" s="57"/>
-      <c r="AI26" s="57"/>
-      <c r="AJ26" s="57"/>
-      <c r="AK26" s="57"/>
-      <c r="AL26" s="57"/>
-      <c r="AM26" s="57"/>
-      <c r="AN26" s="57"/>
-      <c r="AO26" s="57"/>
-      <c r="AP26" s="57"/>
-      <c r="AQ26" s="57"/>
-      <c r="AR26" s="57"/>
-      <c r="AS26" s="57"/>
-      <c r="AT26" s="57"/>
-      <c r="AU26" s="57"/>
-      <c r="AV26" s="57"/>
-      <c r="AW26" s="57"/>
-      <c r="AX26" s="57"/>
-      <c r="AY26" s="57"/>
-      <c r="AZ26" s="57"/>
-      <c r="BA26" s="57"/>
-      <c r="BB26" s="57"/>
-      <c r="BC26" s="57"/>
-      <c r="BD26" s="57"/>
-      <c r="BE26" s="57"/>
-      <c r="BF26" s="57"/>
-      <c r="BG26" s="57"/>
-      <c r="BH26" s="57"/>
-      <c r="BI26" s="57"/>
-      <c r="BJ26" s="57"/>
-      <c r="BK26" s="57"/>
-      <c r="BL26" s="57"/>
-      <c r="BM26" s="57"/>
-      <c r="BN26" s="57"/>
-      <c r="BO26" s="57"/>
-      <c r="BP26" s="57"/>
-      <c r="BQ26" s="57"/>
-      <c r="BR26" s="57"/>
-      <c r="BS26" s="57"/>
-      <c r="BT26" s="57"/>
-      <c r="BU26" s="57"/>
-      <c r="BV26" s="57"/>
-      <c r="BW26" s="57"/>
-      <c r="BX26" s="57"/>
-      <c r="BY26" s="57"/>
-      <c r="BZ26" s="57"/>
-      <c r="CA26" s="57"/>
-      <c r="CB26" s="57"/>
-      <c r="CC26" s="57"/>
-      <c r="CD26" s="57"/>
-      <c r="CE26" s="57"/>
-      <c r="CF26" s="57"/>
-      <c r="CG26" s="57"/>
-      <c r="CH26" s="57"/>
-      <c r="CI26" s="57"/>
-      <c r="CJ26" s="57"/>
-      <c r="CK26" s="57"/>
-      <c r="CL26" s="57"/>
-      <c r="CM26" s="57"/>
-      <c r="CN26" s="57"/>
-      <c r="CO26" s="57"/>
-      <c r="CP26" s="57"/>
-      <c r="CQ26" s="57"/>
-      <c r="CR26" s="57"/>
-      <c r="CS26" s="57"/>
-      <c r="CT26" s="57"/>
-      <c r="CU26" s="57"/>
-      <c r="CV26" s="57"/>
-      <c r="CW26" s="57"/>
-      <c r="CX26" s="57"/>
-      <c r="CY26" s="57"/>
-      <c r="CZ26" s="57"/>
-      <c r="DA26" s="57"/>
-      <c r="DB26" s="57"/>
-      <c r="DC26" s="57"/>
-      <c r="DD26" s="57"/>
-      <c r="DE26" s="57"/>
-      <c r="DF26" s="57"/>
-      <c r="DG26" s="57"/>
-      <c r="DH26" s="57"/>
-      <c r="DI26" s="57"/>
-      <c r="DJ26" s="57"/>
-      <c r="DK26" s="57"/>
-      <c r="DL26" s="57"/>
-      <c r="DM26" s="57"/>
-      <c r="DN26" s="57"/>
-      <c r="DO26" s="57"/>
-      <c r="DP26" s="57"/>
-      <c r="DQ26" s="57"/>
-      <c r="DR26" s="57"/>
-      <c r="DS26" s="57"/>
-      <c r="DT26" s="57"/>
-      <c r="DU26" s="57"/>
-      <c r="DV26" s="57"/>
-      <c r="DW26" s="57"/>
-      <c r="DX26" s="57"/>
-      <c r="DY26" s="57"/>
-      <c r="DZ26" s="57"/>
-      <c r="EA26" s="57"/>
-      <c r="EB26" s="57"/>
-      <c r="EC26" s="57"/>
-      <c r="ED26" s="57"/>
-      <c r="EE26" s="57"/>
-      <c r="EF26" s="57"/>
-      <c r="EG26" s="57"/>
-      <c r="EH26" s="57"/>
-      <c r="EI26" s="57"/>
-      <c r="EJ26" s="57"/>
-      <c r="EK26" s="57"/>
-      <c r="EL26" s="57"/>
-      <c r="EM26" s="57"/>
-      <c r="EN26" s="57"/>
-      <c r="EO26" s="57"/>
-      <c r="EP26" s="57"/>
-      <c r="EQ26" s="57"/>
-      <c r="ER26" s="57"/>
-      <c r="ES26" s="57"/>
-      <c r="ET26" s="57"/>
-      <c r="EU26" s="57"/>
-      <c r="EV26" s="57"/>
-      <c r="EW26" s="57"/>
-      <c r="EX26" s="57"/>
-      <c r="EY26" s="57"/>
-      <c r="EZ26" s="57"/>
-      <c r="FA26" s="57"/>
-      <c r="FB26" s="57"/>
-      <c r="FC26" s="57"/>
-      <c r="FD26" s="57"/>
-      <c r="FE26" s="57"/>
-      <c r="FF26" s="57"/>
-      <c r="FG26" s="57"/>
-      <c r="FH26" s="57"/>
-      <c r="FI26" s="57"/>
-      <c r="FJ26" s="57"/>
-      <c r="FK26" s="57"/>
-      <c r="FL26" s="57"/>
-      <c r="FM26" s="57"/>
-      <c r="FN26" s="57"/>
-      <c r="FO26" s="57"/>
-      <c r="FP26" s="57"/>
-      <c r="FQ26" s="57"/>
-      <c r="FR26" s="57"/>
-      <c r="FS26" s="57"/>
-      <c r="FT26" s="57"/>
-      <c r="FU26" s="57"/>
-      <c r="FV26" s="57"/>
-      <c r="FW26" s="57"/>
-      <c r="FX26" s="57"/>
-      <c r="FY26" s="57"/>
-      <c r="FZ26" s="57"/>
-      <c r="GA26" s="57"/>
-      <c r="GB26" s="57"/>
-      <c r="GC26" s="57"/>
-      <c r="GD26" s="57"/>
-      <c r="GE26" s="57"/>
-      <c r="GF26" s="57"/>
-      <c r="GG26" s="57"/>
-      <c r="GH26" s="57"/>
-      <c r="GI26" s="57"/>
-      <c r="GJ26" s="57"/>
-      <c r="GK26" s="57"/>
-      <c r="GL26" s="57"/>
-      <c r="GM26" s="57"/>
-      <c r="GN26" s="57"/>
-      <c r="GO26" s="57"/>
-      <c r="GP26" s="57"/>
-      <c r="GQ26" s="57"/>
-      <c r="GR26" s="57"/>
-      <c r="GS26" s="57"/>
-      <c r="GT26" s="57"/>
-      <c r="GU26" s="57"/>
-      <c r="GV26" s="57"/>
-      <c r="GW26" s="57"/>
-      <c r="GX26" s="57"/>
-      <c r="GY26" s="57"/>
-      <c r="GZ26" s="57"/>
-      <c r="HA26" s="57"/>
-      <c r="HB26" s="57"/>
-      <c r="HC26" s="57"/>
-      <c r="HD26" s="57"/>
-      <c r="HE26" s="57"/>
-      <c r="HF26" s="57"/>
-      <c r="HG26" s="57"/>
-      <c r="HH26" s="57"/>
-      <c r="HI26" s="57"/>
-      <c r="HJ26" s="57"/>
-      <c r="HK26" s="57"/>
-      <c r="HL26" s="57"/>
-      <c r="HM26" s="57"/>
-      <c r="HN26" s="57"/>
-      <c r="HO26" s="57"/>
-      <c r="HP26" s="57"/>
-      <c r="HQ26" s="57"/>
-      <c r="HR26" s="57"/>
-      <c r="HS26" s="57"/>
-      <c r="HT26" s="57"/>
-      <c r="HU26" s="57"/>
-      <c r="HV26" s="57"/>
-      <c r="HW26" s="57"/>
-      <c r="HX26" s="57"/>
-      <c r="HY26" s="57"/>
-      <c r="HZ26" s="57"/>
-      <c r="IA26" s="57"/>
-      <c r="IB26" s="57"/>
-      <c r="IC26" s="57"/>
-      <c r="ID26" s="57"/>
-      <c r="IE26" s="57"/>
-      <c r="IF26" s="57"/>
-      <c r="IG26" s="57"/>
-      <c r="IH26" s="57"/>
-      <c r="II26" s="57"/>
-      <c r="IJ26" s="57"/>
-      <c r="IK26" s="57"/>
-      <c r="IL26" s="57"/>
-      <c r="IM26" s="57"/>
-      <c r="IN26" s="57"/>
-      <c r="IO26" s="57"/>
-      <c r="IP26" s="57"/>
-      <c r="IQ26" s="57"/>
-      <c r="IR26" s="57"/>
-      <c r="IS26" s="57"/>
-      <c r="IT26" s="57"/>
-      <c r="IU26" s="57"/>
-      <c r="IV26" s="57"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A6:A7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/datakas.xlsx
+++ b/datakas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3437E1BC-0624-4DE2-AAF2-9AC1D6941D52}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61410493-8206-4EA8-993F-285D2EBCCFE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="691" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="190">
   <si>
     <t>LAPORAN KEUANGAN RW.014 GRIYA PERMATA RAYA</t>
   </si>
@@ -601,6 +601,21 @@
   <si>
     <t>JUMLAH</t>
   </si>
+  <si>
+    <t>TANGGAL</t>
+  </si>
+  <si>
+    <t>KETERANGAN</t>
+  </si>
+  <si>
+    <t>PEMASUKAN</t>
+  </si>
+  <si>
+    <t>SALDO</t>
+  </si>
+  <si>
+    <t>PENGELUARAN</t>
+  </si>
 </sst>
 </file>
 
@@ -1083,14 +1098,26 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1101,22 +1128,10 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1440,7 +1455,7 @@
     <col min="1" max="1" width="16.140625" style="23" customWidth="1"/>
     <col min="2" max="2" width="62.85546875" style="24" customWidth="1"/>
     <col min="3" max="4" width="17.42578125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="26" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="4" style="24" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="24" customWidth="1"/>
     <col min="8" max="8" width="35.5703125" style="24" customWidth="1"/>
@@ -1449,26 +1464,26 @@
   <sheetData>
     <row r="1" spans="1:7" s="17" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="31" t="s">
-        <v>2</v>
+        <v>185</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>3</v>
+        <v>186</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>5</v>
+        <v>189</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="82"/>
+      <c r="B2" s="84"/>
       <c r="C2" s="35">
         <v>-334000</v>
       </c>
@@ -1479,7 +1494,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="19" customFormat="1" ht="30">
-      <c r="A3" s="86">
+      <c r="A3" s="80">
         <v>46023</v>
       </c>
       <c r="B3" s="38" t="s">
@@ -1496,7 +1511,7 @@
       <c r="G3" s="41"/>
     </row>
     <row r="4" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="87"/>
+      <c r="A4" s="82"/>
       <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
@@ -1511,7 +1526,7 @@
       <c r="G4" s="42"/>
     </row>
     <row r="5" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A5" s="88"/>
+      <c r="A5" s="81"/>
       <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
@@ -1543,7 +1558,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="86">
+      <c r="A7" s="80">
         <v>46031</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -1560,7 +1575,7 @@
       <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A8" s="88"/>
+      <c r="A8" s="81"/>
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
@@ -1575,7 +1590,7 @@
       <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="86">
+      <c r="A9" s="80">
         <v>46033</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -1592,7 +1607,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A10" s="88"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -1624,7 +1639,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A12" s="86">
+      <c r="A12" s="80">
         <v>46039</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -1641,7 +1656,7 @@
       <c r="G12" s="42"/>
     </row>
     <row r="13" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A13" s="88"/>
+      <c r="A13" s="81"/>
       <c r="B13" s="8" t="s">
         <v>18</v>
       </c>
@@ -1656,7 +1671,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="86">
+      <c r="A14" s="80">
         <v>46041</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -1673,7 +1688,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A15" s="88"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="8" t="s">
         <v>11</v>
       </c>
@@ -1749,7 +1764,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A19" s="86">
+      <c r="A19" s="80">
         <v>46052</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -1771,7 +1786,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A20" s="87"/>
+      <c r="A20" s="82"/>
       <c r="B20" s="8" t="s">
         <v>24</v>
       </c>
@@ -1791,7 +1806,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A21" s="88"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="8" t="s">
         <v>11</v>
       </c>
@@ -1843,7 +1858,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="86">
+      <c r="A24" s="80">
         <v>46064</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -1859,7 +1874,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="88"/>
+      <c r="A25" s="81"/>
       <c r="B25" s="8" t="s">
         <v>40</v>
       </c>
@@ -1905,7 +1920,7 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="86">
+      <c r="A28" s="80">
         <v>46072</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -1921,7 +1936,7 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="88"/>
+      <c r="A29" s="81"/>
       <c r="B29" s="8" t="s">
         <v>11</v>
       </c>
@@ -1967,7 +1982,7 @@
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="86">
+      <c r="A32" s="80">
         <v>46081</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -1983,7 +1998,7 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="88"/>
+      <c r="A33" s="81"/>
       <c r="B33" s="8" t="s">
         <v>46</v>
       </c>
@@ -2029,7 +2044,7 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="86">
+      <c r="A36" s="80">
         <v>46084</v>
       </c>
       <c r="B36" s="38" t="s">
@@ -2045,7 +2060,7 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="88"/>
+      <c r="A37" s="81"/>
       <c r="B37" s="8" t="s">
         <v>97</v>
       </c>
@@ -2123,7 +2138,7 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="86">
+      <c r="A42" s="80">
         <v>46096</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -2139,7 +2154,7 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="88"/>
+      <c r="A43" s="81"/>
       <c r="B43" s="8" t="s">
         <v>13</v>
       </c>
@@ -2153,7 +2168,7 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="91">
+      <c r="A44" s="83">
         <v>46101</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -2169,7 +2184,7 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="91"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="8" t="s">
         <v>103</v>
       </c>
@@ -2183,7 +2198,7 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="87">
+      <c r="A46" s="82">
         <v>46107</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -2199,7 +2214,7 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="87"/>
+      <c r="A47" s="82"/>
       <c r="B47" s="8" t="s">
         <v>105</v>
       </c>
@@ -2213,7 +2228,7 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="88"/>
+      <c r="A48" s="81"/>
       <c r="B48" s="8" t="s">
         <v>106</v>
       </c>
@@ -2227,7 +2242,7 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="87">
+      <c r="A49" s="82">
         <v>46109</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -2243,7 +2258,7 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="88"/>
+      <c r="A50" s="81"/>
       <c r="B50" s="8" t="s">
         <v>104</v>
       </c>
@@ -2273,7 +2288,7 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="86">
+      <c r="A52" s="80">
         <v>46112</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -2289,7 +2304,7 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="88"/>
+      <c r="A53" s="81"/>
       <c r="B53" s="8" t="s">
         <v>110</v>
       </c>
@@ -2383,7 +2398,7 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="86">
+      <c r="A59" s="80">
         <v>46132</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -2399,7 +2414,7 @@
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="88"/>
+      <c r="A60" s="81"/>
       <c r="B60" s="8" t="s">
         <v>98</v>
       </c>
@@ -2477,7 +2492,7 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="86">
+      <c r="A65" s="80">
         <v>46145</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -2493,7 +2508,7 @@
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="88"/>
+      <c r="A66" s="81"/>
       <c r="B66" s="8" t="s">
         <v>128</v>
       </c>
@@ -2523,7 +2538,7 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="86">
+      <c r="A68" s="80">
         <v>46148</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -2539,7 +2554,7 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="88"/>
+      <c r="A69" s="81"/>
       <c r="B69" s="8" t="s">
         <v>11</v>
       </c>
@@ -2553,7 +2568,7 @@
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="86">
+      <c r="A70" s="80">
         <v>46151</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -2569,7 +2584,7 @@
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="88"/>
+      <c r="A71" s="81"/>
       <c r="B71" s="8" t="s">
         <v>132</v>
       </c>
@@ -2599,7 +2614,7 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="86">
+      <c r="A73" s="80">
         <v>46155</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -2615,7 +2630,7 @@
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="88"/>
+      <c r="A74" s="81"/>
       <c r="B74" s="8" t="s">
         <v>134</v>
       </c>
@@ -2629,7 +2644,7 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="86">
+      <c r="A75" s="80">
         <v>46158</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -2645,7 +2660,7 @@
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="88"/>
+      <c r="A76" s="81"/>
       <c r="B76" s="8" t="s">
         <v>135</v>
       </c>
@@ -2691,7 +2706,7 @@
       </c>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="86">
+      <c r="A79" s="80">
         <v>46165</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -2707,7 +2722,7 @@
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="88"/>
+      <c r="A80" s="81"/>
       <c r="B80" s="8" t="s">
         <v>13</v>
       </c>
@@ -3088,6 +3103,20 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
     <mergeCell ref="A73:A74"/>
     <mergeCell ref="A75:A76"/>
     <mergeCell ref="A79:A80"/>
@@ -3097,20 +3126,6 @@
     <mergeCell ref="A65:A66"/>
     <mergeCell ref="A68:A69"/>
     <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="1" right="0.5" top="0.75" bottom="0.75" header="0.30972222222222201" footer="0.30972222222222201"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -3136,13 +3151,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -3171,10 +3186,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="84" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="35">
         <f>'Apr''26'!E15</f>
         <v>6032500</v>
@@ -3197,7 +3212,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="86"/>
+      <c r="A6" s="80"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -3208,7 +3223,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="88"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -3321,10 +3336,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="83"/>
+      <c r="B15" s="87"/>
       <c r="C15" s="46">
         <f>SUM(C4:C14)</f>
         <v>6032500</v>
@@ -3350,10 +3365,10 @@
       <c r="E16" s="50"/>
     </row>
     <row r="17" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="84"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="51">
         <f>C15-C4</f>
         <v>0</v>
@@ -3373,10 +3388,10 @@
       <c r="E18" s="50"/>
     </row>
     <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="85" t="s">
+      <c r="A19" s="89" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="85"/>
+      <c r="B19" s="89"/>
       <c r="C19" s="54">
         <f>D15</f>
         <v>0</v>
@@ -5537,13 +5552,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -5572,10 +5587,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="35">
         <v>-334000</v>
       </c>
@@ -5586,7 +5601,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" s="19" customFormat="1" ht="30">
-      <c r="A5" s="86">
+      <c r="A5" s="80">
         <v>46023</v>
       </c>
       <c r="B5" s="38" t="s">
@@ -5603,7 +5618,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A6" s="87"/>
+      <c r="A6" s="82"/>
       <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
@@ -5618,7 +5633,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="88"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="8" t="s">
         <v>10</v>
       </c>
@@ -5650,7 +5665,7 @@
       <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="86">
+      <c r="A9" s="80">
         <v>46031</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -5667,7 +5682,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A10" s="88"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
@@ -5682,7 +5697,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A11" s="86">
+      <c r="A11" s="80">
         <v>46033</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -5699,7 +5714,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A12" s="88"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
@@ -5731,7 +5746,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="86">
+      <c r="A14" s="80">
         <v>46039</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -5748,7 +5763,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A15" s="88"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="8" t="s">
         <v>18</v>
       </c>
@@ -5763,7 +5778,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A16" s="86">
+      <c r="A16" s="80">
         <v>46041</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -5780,7 +5795,7 @@
       <c r="G16" s="42"/>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A17" s="88"/>
+      <c r="A17" s="81"/>
       <c r="B17" s="8" t="s">
         <v>11</v>
       </c>
@@ -5856,7 +5871,7 @@
       </c>
     </row>
     <row r="21" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A21" s="86">
+      <c r="A21" s="80">
         <v>46052</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -5878,7 +5893,7 @@
       </c>
     </row>
     <row r="22" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A22" s="87"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="8" t="s">
         <v>24</v>
       </c>
@@ -5898,7 +5913,7 @@
       </c>
     </row>
     <row r="23" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A23" s="88"/>
+      <c r="A23" s="81"/>
       <c r="B23" s="8" t="s">
         <v>11</v>
       </c>
@@ -5918,10 +5933,10 @@
       </c>
     </row>
     <row r="24" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="83" t="s">
+      <c r="A24" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="83"/>
+      <c r="B24" s="87"/>
       <c r="C24" s="46">
         <f>SUM(C4:C23)</f>
         <v>3212000</v>
@@ -5947,10 +5962,10 @@
       <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="84"/>
+      <c r="B26" s="88"/>
       <c r="C26" s="51">
         <f>C24-C4</f>
         <v>3546000</v>
@@ -5970,10 +5985,10 @@
       <c r="E27" s="50"/>
     </row>
     <row r="28" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A28" s="85" t="s">
+      <c r="A28" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="85"/>
+      <c r="B28" s="89"/>
       <c r="C28" s="54">
         <f>D24</f>
         <v>1200000</v>
@@ -7813,13 +7828,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -7848,10 +7863,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="35">
         <f>'Jan''26'!E24</f>
         <v>2012000</v>
@@ -7897,7 +7912,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="86">
+      <c r="A7" s="80">
         <v>46064</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -7914,7 +7929,7 @@
       <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A8" s="88"/>
+      <c r="A8" s="81"/>
       <c r="B8" s="8" t="s">
         <v>40</v>
       </c>
@@ -7963,7 +7978,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="86">
+      <c r="A11" s="80">
         <v>46072</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -7980,7 +7995,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="88"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -8044,7 +8059,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="86">
+      <c r="A15" s="80">
         <v>46081</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -8066,7 +8081,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="88"/>
+      <c r="A16" s="81"/>
       <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
@@ -8086,10 +8101,10 @@
       </c>
     </row>
     <row r="17" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="83"/>
+      <c r="B17" s="87"/>
       <c r="C17" s="46">
         <f>SUM(C4:C16)</f>
         <v>5139000</v>
@@ -8115,10 +8130,10 @@
       <c r="E18" s="50"/>
     </row>
     <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="84"/>
+      <c r="B19" s="88"/>
       <c r="C19" s="51">
         <f>C17-C4</f>
         <v>3127000</v>
@@ -8138,10 +8153,10 @@
       <c r="E20" s="50"/>
     </row>
     <row r="21" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="85"/>
+      <c r="B21" s="89"/>
       <c r="C21" s="54">
         <f>D17</f>
         <v>1141000</v>
@@ -9975,24 +9990,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
     </row>
     <row r="2" spans="1:6" ht="21" customHeight="1">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
     </row>
     <row r="3" spans="1:6" ht="6.95" customHeight="1"/>
     <row r="4" spans="1:6" s="66" customFormat="1" ht="21" customHeight="1">
@@ -10644,10 +10659,10 @@
       <c r="F40" s="71"/>
     </row>
     <row r="41" spans="1:6" ht="21" customHeight="1">
-      <c r="A41" s="90" t="s">
+      <c r="A41" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="90"/>
+      <c r="B41" s="91"/>
       <c r="C41" s="73">
         <f>SUM(C5:C40)</f>
         <v>2564000</v>
@@ -10688,13 +10703,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:7" ht="18.75">
       <c r="A2" s="27" t="s">
@@ -10723,10 +10738,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="35">
         <f>'Feb''26'!E17</f>
         <v>3998000</v>
@@ -10772,7 +10787,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A7" s="86">
+      <c r="A7" s="80">
         <v>46084</v>
       </c>
       <c r="B7" s="38" t="s">
@@ -10789,7 +10804,7 @@
       <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A8" s="88"/>
+      <c r="A8" s="81"/>
       <c r="B8" s="8" t="s">
         <v>97</v>
       </c>
@@ -10872,7 +10887,7 @@
       <c r="G12" s="42"/>
     </row>
     <row r="13" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A13" s="86">
+      <c r="A13" s="80">
         <v>46096</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -10889,7 +10904,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A14" s="88"/>
+      <c r="A14" s="81"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -10904,7 +10919,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A15" s="91">
+      <c r="A15" s="83">
         <v>46101</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -10921,7 +10936,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A16" s="91"/>
+      <c r="A16" s="83"/>
       <c r="B16" s="8" t="s">
         <v>103</v>
       </c>
@@ -10936,7 +10951,7 @@
       <c r="G16" s="42"/>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A17" s="87">
+      <c r="A17" s="82">
         <v>46107</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -10953,7 +10968,7 @@
       <c r="G17" s="42"/>
     </row>
     <row r="18" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A18" s="87"/>
+      <c r="A18" s="82"/>
       <c r="B18" s="8" t="s">
         <v>105</v>
       </c>
@@ -10968,7 +10983,7 @@
       <c r="G18" s="42"/>
     </row>
     <row r="19" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A19" s="88"/>
+      <c r="A19" s="81"/>
       <c r="B19" s="8" t="s">
         <v>106</v>
       </c>
@@ -10985,7 +11000,7 @@
       </c>
     </row>
     <row r="20" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A20" s="87">
+      <c r="A20" s="82">
         <v>46109</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -11007,7 +11022,7 @@
       </c>
     </row>
     <row r="21" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A21" s="88"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="8" t="s">
         <v>104</v>
       </c>
@@ -11049,7 +11064,7 @@
       </c>
     </row>
     <row r="23" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A23" s="86">
+      <c r="A23" s="80">
         <v>46112</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -11071,7 +11086,7 @@
       </c>
     </row>
     <row r="24" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A24" s="88"/>
+      <c r="A24" s="81"/>
       <c r="B24" s="8" t="s">
         <v>110</v>
       </c>
@@ -11091,10 +11106,10 @@
       </c>
     </row>
     <row r="25" spans="1:256" s="21" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A25" s="83" t="s">
+      <c r="A25" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="83"/>
+      <c r="B25" s="87"/>
       <c r="C25" s="46">
         <f>SUM(C4:C24)</f>
         <v>7845000</v>
@@ -11120,10 +11135,10 @@
       <c r="E26" s="50"/>
     </row>
     <row r="27" spans="1:256" s="22" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A27" s="84" t="s">
+      <c r="A27" s="88" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="84"/>
+      <c r="B27" s="88"/>
       <c r="C27" s="51">
         <f>C25-C4</f>
         <v>3847000</v>
@@ -11143,10 +11158,10 @@
       <c r="E28" s="50"/>
     </row>
     <row r="29" spans="1:256" s="22" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A29" s="85" t="s">
+      <c r="A29" s="89" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="85"/>
+      <c r="B29" s="89"/>
       <c r="C29" s="54">
         <f>D25</f>
         <v>2689500</v>
@@ -12986,13 +13001,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -13021,10 +13036,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="84" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="35">
         <f>'Mar''26'!E25</f>
         <v>5155500</v>
@@ -13121,7 +13136,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A10" s="86">
+      <c r="A10" s="80">
         <v>46132</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -13143,7 +13158,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="88"/>
+      <c r="A11" s="81"/>
       <c r="B11" s="8" t="s">
         <v>98</v>
       </c>
@@ -13229,10 +13244,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="83"/>
+      <c r="B15" s="87"/>
       <c r="C15" s="46">
         <f>SUM(C4:C14)</f>
         <v>6784500</v>
@@ -13258,10 +13273,10 @@
       <c r="E16" s="50"/>
     </row>
     <row r="17" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="88" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="84"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="51">
         <f>C15-C4</f>
         <v>1629000</v>
@@ -13281,10 +13296,10 @@
       <c r="E18" s="50"/>
     </row>
     <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="85" t="s">
+      <c r="A19" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="85"/>
+      <c r="B19" s="89"/>
       <c r="C19" s="54">
         <f>D15</f>
         <v>752000</v>
@@ -15119,13 +15134,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -15154,10 +15169,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="84" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="35">
         <f>'Apr''26'!E15</f>
         <v>6032500</v>
@@ -15186,7 +15201,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="86">
+      <c r="A6" s="80">
         <v>46145</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -15203,7 +15218,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="88"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="8" t="s">
         <v>128</v>
       </c>
@@ -15235,7 +15250,7 @@
       <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="86">
+      <c r="A9" s="80">
         <v>46148</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -15252,7 +15267,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A10" s="88"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
@@ -15267,7 +15282,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="86">
+      <c r="A11" s="80">
         <v>46151</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -15284,7 +15299,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="88"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="8" t="s">
         <v>132</v>
       </c>
@@ -15316,7 +15331,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A14" s="86">
+      <c r="A14" s="80">
         <v>46155</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -15333,7 +15348,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="88"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="8" t="s">
         <v>134</v>
       </c>
@@ -15348,7 +15363,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="86">
+      <c r="A16" s="80">
         <v>46158</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -15364,7 +15379,7 @@
       </c>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A17" s="88"/>
+      <c r="A17" s="81"/>
       <c r="B17" s="8" t="s">
         <v>135</v>
       </c>
@@ -15428,7 +15443,7 @@
       </c>
     </row>
     <row r="20" spans="1:256" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A20" s="86">
+      <c r="A20" s="80">
         <v>46165</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -15450,7 +15465,7 @@
       </c>
     </row>
     <row r="21" spans="1:256" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A21" s="88"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="8" t="s">
         <v>13</v>
       </c>
@@ -15470,10 +15485,10 @@
       </c>
     </row>
     <row r="22" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="83"/>
+      <c r="B22" s="87"/>
       <c r="C22" s="46">
         <f>SUM(C4:C21)</f>
         <v>8832500</v>
@@ -15499,10 +15514,10 @@
       <c r="E23" s="50"/>
     </row>
     <row r="24" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="84" t="s">
+      <c r="A24" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="84"/>
+      <c r="B24" s="88"/>
       <c r="C24" s="51">
         <f>C22-C4</f>
         <v>2800000</v>
@@ -15522,10 +15537,10 @@
       <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="85" t="s">
+      <c r="A26" s="89" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="85"/>
+      <c r="B26" s="89"/>
       <c r="C26" s="54">
         <f>D22</f>
         <v>2495500</v>
@@ -17365,13 +17380,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -17400,10 +17415,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="84" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="35">
         <f>'Mei''26'!E22</f>
         <v>6337000</v>
@@ -17841,10 +17856,10 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A29" s="83" t="s">
+      <c r="A29" s="87" t="s">
         <v>162</v>
       </c>
-      <c r="B29" s="83"/>
+      <c r="B29" s="87"/>
       <c r="C29" s="46">
         <f>SUM(C4:C28)</f>
         <v>12356000</v>
@@ -17871,10 +17886,10 @@
       <c r="E30" s="50"/>
     </row>
     <row r="31" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A31" s="84" t="s">
+      <c r="A31" s="88" t="s">
         <v>163</v>
       </c>
-      <c r="B31" s="84"/>
+      <c r="B31" s="88"/>
       <c r="C31" s="51">
         <f>C29-C4</f>
         <v>6019000</v>
@@ -17894,10 +17909,10 @@
       <c r="E32" s="50"/>
     </row>
     <row r="33" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A33" s="85" t="s">
+      <c r="A33" s="89" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="85"/>
+      <c r="B33" s="89"/>
       <c r="C33" s="54">
         <f>D29</f>
         <v>2722000</v>
@@ -19741,13 +19756,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -19776,10 +19791,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="84" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="35">
         <f>'Juni''26'!E29</f>
         <v>9634000</v>
@@ -20036,10 +20051,10 @@
       </c>
     </row>
     <row r="24" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="83" t="s">
+      <c r="A24" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B24" s="83"/>
+      <c r="B24" s="87"/>
       <c r="C24" s="46">
         <f>SUM(C4:C23)</f>
         <v>9744000</v>
@@ -20065,10 +20080,10 @@
       <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="88" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="84"/>
+      <c r="B26" s="88"/>
       <c r="C26" s="51">
         <f>C24-C4</f>
         <v>110000</v>
@@ -20088,10 +20103,10 @@
       <c r="E27" s="50"/>
     </row>
     <row r="28" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A28" s="85" t="s">
+      <c r="A28" s="89" t="s">
         <v>169</v>
       </c>
-      <c r="B28" s="85"/>
+      <c r="B28" s="89"/>
       <c r="C28" s="54">
         <f>D24</f>
         <v>0</v>

--- a/datakas.xlsx
+++ b/datakas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61410493-8206-4EA8-993F-285D2EBCCFE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9AD12F-3050-4CD3-BC8F-58046120E10E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="691" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -871,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1098,20 +1098,20 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1139,6 +1139,15 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1463,16 +1472,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="17" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="94" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="95" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="96" t="s">
         <v>187</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="96" t="s">
         <v>189</v>
       </c>
       <c r="E1" s="34" t="s">
@@ -1480,10 +1489,10 @@
       </c>
     </row>
     <row r="2" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="84"/>
+      <c r="B2" s="83"/>
       <c r="C2" s="35">
         <v>-334000</v>
       </c>
@@ -1494,7 +1503,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="19" customFormat="1" ht="30">
-      <c r="A3" s="80">
+      <c r="A3" s="82">
         <v>46023</v>
       </c>
       <c r="B3" s="38" t="s">
@@ -1511,7 +1520,7 @@
       <c r="G3" s="41"/>
     </row>
     <row r="4" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="82"/>
+      <c r="A4" s="80"/>
       <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
@@ -1558,7 +1567,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="80">
+      <c r="A7" s="82">
         <v>46031</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -1590,7 +1599,7 @@
       <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="80">
+      <c r="A9" s="82">
         <v>46033</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -1639,7 +1648,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A12" s="80">
+      <c r="A12" s="82">
         <v>46039</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -1671,7 +1680,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="80">
+      <c r="A14" s="82">
         <v>46041</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -1764,7 +1773,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A19" s="80">
+      <c r="A19" s="82">
         <v>46052</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -1786,7 +1795,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A20" s="82"/>
+      <c r="A20" s="80"/>
       <c r="B20" s="8" t="s">
         <v>24</v>
       </c>
@@ -1858,7 +1867,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="80">
+      <c r="A24" s="82">
         <v>46064</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -1920,7 +1929,7 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="80">
+      <c r="A28" s="82">
         <v>46072</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -1982,7 +1991,7 @@
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="80">
+      <c r="A32" s="82">
         <v>46081</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -2044,7 +2053,7 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="80">
+      <c r="A36" s="82">
         <v>46084</v>
       </c>
       <c r="B36" s="38" t="s">
@@ -2138,7 +2147,7 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="80">
+      <c r="A42" s="82">
         <v>46096</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -2168,7 +2177,7 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="83">
+      <c r="A44" s="84">
         <v>46101</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -2184,7 +2193,7 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="83"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="8" t="s">
         <v>103</v>
       </c>
@@ -2198,7 +2207,7 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="82">
+      <c r="A46" s="80">
         <v>46107</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -2214,7 +2223,7 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="82"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="8" t="s">
         <v>105</v>
       </c>
@@ -2242,7 +2251,7 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="82">
+      <c r="A49" s="80">
         <v>46109</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -2288,7 +2297,7 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="80">
+      <c r="A52" s="82">
         <v>46112</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -2398,7 +2407,7 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="80">
+      <c r="A59" s="82">
         <v>46132</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -2492,7 +2501,7 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="80">
+      <c r="A65" s="82">
         <v>46145</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -2538,7 +2547,7 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="80">
+      <c r="A68" s="82">
         <v>46148</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -2568,7 +2577,7 @@
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="80">
+      <c r="A70" s="82">
         <v>46151</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -2614,7 +2623,7 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="80">
+      <c r="A73" s="82">
         <v>46155</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -2644,7 +2653,7 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="80">
+      <c r="A75" s="82">
         <v>46158</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -2706,7 +2715,7 @@
       </c>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="80">
+      <c r="A79" s="82">
         <v>46165</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -3103,6 +3112,15 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A70:A71"/>
     <mergeCell ref="A46:A48"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A19:A21"/>
@@ -3117,15 +3135,6 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A70:A71"/>
   </mergeCells>
   <pageMargins left="1" right="0.5" top="0.75" bottom="0.75" header="0.30972222222222201" footer="0.30972222222222201"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
@@ -3186,10 +3195,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="35">
         <f>'Apr''26'!E15</f>
         <v>6032500</v>
@@ -3212,7 +3221,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="80"/>
+      <c r="A6" s="82"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -5587,10 +5596,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="35">
         <v>-334000</v>
       </c>
@@ -5601,7 +5610,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" s="19" customFormat="1" ht="30">
-      <c r="A5" s="80">
+      <c r="A5" s="82">
         <v>46023</v>
       </c>
       <c r="B5" s="38" t="s">
@@ -5618,7 +5627,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A6" s="82"/>
+      <c r="A6" s="80"/>
       <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
@@ -5665,7 +5674,7 @@
       <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="80">
+      <c r="A9" s="82">
         <v>46031</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -5697,7 +5706,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A11" s="80">
+      <c r="A11" s="82">
         <v>46033</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -5746,7 +5755,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="80">
+      <c r="A14" s="82">
         <v>46039</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -5778,7 +5787,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A16" s="80">
+      <c r="A16" s="82">
         <v>46041</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -5871,7 +5880,7 @@
       </c>
     </row>
     <row r="21" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A21" s="80">
+      <c r="A21" s="82">
         <v>46052</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -5893,7 +5902,7 @@
       </c>
     </row>
     <row r="22" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A22" s="82"/>
+      <c r="A22" s="80"/>
       <c r="B22" s="8" t="s">
         <v>24</v>
       </c>
@@ -7863,10 +7872,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="35">
         <f>'Jan''26'!E24</f>
         <v>2012000</v>
@@ -7912,7 +7921,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="80">
+      <c r="A7" s="82">
         <v>46064</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -7978,7 +7987,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="80">
+      <c r="A11" s="82">
         <v>46072</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -8059,7 +8068,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="80">
+      <c r="A15" s="82">
         <v>46081</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -10738,10 +10747,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="35">
         <f>'Feb''26'!E17</f>
         <v>3998000</v>
@@ -10787,7 +10796,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A7" s="80">
+      <c r="A7" s="82">
         <v>46084</v>
       </c>
       <c r="B7" s="38" t="s">
@@ -10887,7 +10896,7 @@
       <c r="G12" s="42"/>
     </row>
     <row r="13" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A13" s="80">
+      <c r="A13" s="82">
         <v>46096</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -10919,7 +10928,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A15" s="83">
+      <c r="A15" s="84">
         <v>46101</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -10936,7 +10945,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A16" s="83"/>
+      <c r="A16" s="84"/>
       <c r="B16" s="8" t="s">
         <v>103</v>
       </c>
@@ -10951,7 +10960,7 @@
       <c r="G16" s="42"/>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A17" s="82">
+      <c r="A17" s="80">
         <v>46107</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -10968,7 +10977,7 @@
       <c r="G17" s="42"/>
     </row>
     <row r="18" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A18" s="82"/>
+      <c r="A18" s="80"/>
       <c r="B18" s="8" t="s">
         <v>105</v>
       </c>
@@ -11000,7 +11009,7 @@
       </c>
     </row>
     <row r="20" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A20" s="82">
+      <c r="A20" s="80">
         <v>46109</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -11064,7 +11073,7 @@
       </c>
     </row>
     <row r="23" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A23" s="80">
+      <c r="A23" s="82">
         <v>46112</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -13036,10 +13045,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="35">
         <f>'Mar''26'!E25</f>
         <v>5155500</v>
@@ -13136,7 +13145,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A10" s="80">
+      <c r="A10" s="82">
         <v>46132</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -15169,10 +15178,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="35">
         <f>'Apr''26'!E15</f>
         <v>6032500</v>
@@ -15201,7 +15210,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="80">
+      <c r="A6" s="82">
         <v>46145</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -15250,7 +15259,7 @@
       <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="80">
+      <c r="A9" s="82">
         <v>46148</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -15282,7 +15291,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="80">
+      <c r="A11" s="82">
         <v>46151</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -15331,7 +15340,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A14" s="80">
+      <c r="A14" s="82">
         <v>46155</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -15363,7 +15372,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="80">
+      <c r="A16" s="82">
         <v>46158</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -15443,7 +15452,7 @@
       </c>
     </row>
     <row r="20" spans="1:256" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A20" s="80">
+      <c r="A20" s="82">
         <v>46165</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -17415,10 +17424,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="35">
         <f>'Mei''26'!E22</f>
         <v>6337000</v>
@@ -19791,10 +19800,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="35">
         <f>'Juni''26'!E29</f>
         <v>9634000</v>

--- a/datakas.xlsx
+++ b/datakas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9AD12F-3050-4CD3-BC8F-58046120E10E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F54358-B32A-4BF3-BDC2-22DDCBBD9F77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="691" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -871,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1089,22 +1089,28 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1140,13 +1146,31 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1463,8 +1487,9 @@
   <cols>
     <col min="1" max="1" width="16.140625" style="23" customWidth="1"/>
     <col min="2" max="2" width="62.85546875" style="24" customWidth="1"/>
-    <col min="3" max="4" width="17.42578125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="26" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" style="25" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="26" customWidth="1"/>
     <col min="6" max="6" width="4" style="24" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="24" customWidth="1"/>
     <col min="8" max="8" width="35.5703125" style="24" customWidth="1"/>
@@ -1472,27 +1497,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="17" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="80" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="81" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="96" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="97"/>
+      <c r="B2" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="83"/>
       <c r="C2" s="35">
         <v>-334000</v>
       </c>
@@ -1503,7 +1528,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="19" customFormat="1" ht="30">
-      <c r="A3" s="82">
+      <c r="A3" s="98">
         <v>46023</v>
       </c>
       <c r="B3" s="38" t="s">
@@ -1520,7 +1545,7 @@
       <c r="G3" s="41"/>
     </row>
     <row r="4" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="80"/>
+      <c r="A4" s="99"/>
       <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
@@ -1535,7 +1560,7 @@
       <c r="G4" s="42"/>
     </row>
     <row r="5" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A5" s="81"/>
+      <c r="A5" s="100"/>
       <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
@@ -1550,7 +1575,7 @@
       <c r="G5" s="42"/>
     </row>
     <row r="6" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A6" s="10">
+      <c r="A6" s="101">
         <v>46026</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1567,7 +1592,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="82">
+      <c r="A7" s="98">
         <v>46031</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -1584,7 +1609,7 @@
       <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A8" s="81"/>
+      <c r="A8" s="100"/>
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
@@ -1599,7 +1624,7 @@
       <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="82">
+      <c r="A9" s="98">
         <v>46033</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -1616,7 +1641,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A10" s="81"/>
+      <c r="A10" s="100"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -1631,7 +1656,7 @@
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A11" s="10">
+      <c r="A11" s="101">
         <v>46036</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -1648,7 +1673,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A12" s="82">
+      <c r="A12" s="98">
         <v>46039</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -1665,7 +1690,7 @@
       <c r="G12" s="42"/>
     </row>
     <row r="13" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A13" s="81"/>
+      <c r="A13" s="100"/>
       <c r="B13" s="8" t="s">
         <v>18</v>
       </c>
@@ -1680,7 +1705,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="82">
+      <c r="A14" s="98">
         <v>46041</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -1697,7 +1722,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A15" s="81"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="8" t="s">
         <v>11</v>
       </c>
@@ -1712,7 +1737,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A16" s="10">
+      <c r="A16" s="101">
         <v>46043</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -1729,7 +1754,7 @@
       <c r="G16" s="42"/>
     </row>
     <row r="17" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A17" s="10">
+      <c r="A17" s="101">
         <v>46046</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -1751,7 +1776,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A18" s="10">
+      <c r="A18" s="101">
         <v>46047</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -1773,7 +1798,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A19" s="82">
+      <c r="A19" s="98">
         <v>46052</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -1795,7 +1820,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A20" s="80"/>
+      <c r="A20" s="99"/>
       <c r="B20" s="8" t="s">
         <v>24</v>
       </c>
@@ -1815,7 +1840,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A21" s="81"/>
+      <c r="A21" s="100"/>
       <c r="B21" s="8" t="s">
         <v>11</v>
       </c>
@@ -1835,7 +1860,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="77">
+      <c r="A22" s="102">
         <v>46057</v>
       </c>
       <c r="B22" s="38" t="s">
@@ -1851,7 +1876,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="77">
+      <c r="A23" s="102">
         <v>46060</v>
       </c>
       <c r="B23" s="38" t="s">
@@ -1867,7 +1892,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="82">
+      <c r="A24" s="98">
         <v>46064</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -1883,7 +1908,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="81"/>
+      <c r="A25" s="100"/>
       <c r="B25" s="8" t="s">
         <v>40</v>
       </c>
@@ -1897,7 +1922,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="77">
+      <c r="A26" s="102">
         <v>46066</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -1913,7 +1938,7 @@
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="77">
+      <c r="A27" s="102">
         <v>46071</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -1929,7 +1954,7 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="82">
+      <c r="A28" s="98">
         <v>46072</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -1945,7 +1970,7 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="81"/>
+      <c r="A29" s="100"/>
       <c r="B29" s="8" t="s">
         <v>11</v>
       </c>
@@ -1959,7 +1984,7 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="10">
+      <c r="A30" s="101">
         <v>46074</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -1975,7 +2000,7 @@
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="10">
+      <c r="A31" s="101">
         <v>46080</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -1991,7 +2016,7 @@
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="82">
+      <c r="A32" s="98">
         <v>46081</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -2007,7 +2032,7 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="81"/>
+      <c r="A33" s="100"/>
       <c r="B33" s="8" t="s">
         <v>46</v>
       </c>
@@ -2021,7 +2046,7 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="77">
+      <c r="A34" s="102">
         <v>46082</v>
       </c>
       <c r="B34" s="38" t="s">
@@ -2037,7 +2062,7 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="77">
+      <c r="A35" s="102">
         <v>46083</v>
       </c>
       <c r="B35" s="38" t="s">
@@ -2053,7 +2078,7 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="82">
+      <c r="A36" s="98">
         <v>46084</v>
       </c>
       <c r="B36" s="38" t="s">
@@ -2069,7 +2094,7 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="81"/>
+      <c r="A37" s="100"/>
       <c r="B37" s="8" t="s">
         <v>97</v>
       </c>
@@ -2083,7 +2108,7 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="77">
+      <c r="A38" s="102">
         <v>46085</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -2099,7 +2124,7 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="77">
+      <c r="A39" s="102">
         <v>46086</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -2115,7 +2140,7 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="77">
+      <c r="A40" s="102">
         <v>46092</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -2131,7 +2156,7 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="77">
+      <c r="A41" s="102">
         <v>46095</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -2147,7 +2172,7 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="82">
+      <c r="A42" s="98">
         <v>46096</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -2163,7 +2188,7 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="81"/>
+      <c r="A43" s="100"/>
       <c r="B43" s="8" t="s">
         <v>13</v>
       </c>
@@ -2177,7 +2202,7 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="84">
+      <c r="A44" s="102">
         <v>46101</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -2193,7 +2218,7 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="84"/>
+      <c r="A45" s="102"/>
       <c r="B45" s="8" t="s">
         <v>103</v>
       </c>
@@ -2207,7 +2232,7 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="80">
+      <c r="A46" s="99">
         <v>46107</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -2223,7 +2248,7 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="80"/>
+      <c r="A47" s="99"/>
       <c r="B47" s="8" t="s">
         <v>105</v>
       </c>
@@ -2237,7 +2262,7 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="81"/>
+      <c r="A48" s="100"/>
       <c r="B48" s="8" t="s">
         <v>106</v>
       </c>
@@ -2251,7 +2276,7 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="80">
+      <c r="A49" s="99">
         <v>46109</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -2267,7 +2292,7 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="81"/>
+      <c r="A50" s="100"/>
       <c r="B50" s="8" t="s">
         <v>104</v>
       </c>
@@ -2281,7 +2306,7 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="77">
+      <c r="A51" s="102">
         <v>46110</v>
       </c>
       <c r="B51" s="8" t="s">
@@ -2297,7 +2322,7 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="82">
+      <c r="A52" s="98">
         <v>46112</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -2313,7 +2338,7 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="81"/>
+      <c r="A53" s="100"/>
       <c r="B53" s="8" t="s">
         <v>110</v>
       </c>
@@ -2327,7 +2352,7 @@
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="77">
+      <c r="A54" s="102">
         <v>46114</v>
       </c>
       <c r="B54" s="38" t="s">
@@ -2343,7 +2368,7 @@
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="77">
+      <c r="A55" s="102">
         <v>46118</v>
       </c>
       <c r="B55" s="38" t="s">
@@ -2359,7 +2384,7 @@
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="77">
+      <c r="A56" s="102">
         <v>46122</v>
       </c>
       <c r="B56" s="38" t="s">
@@ -2375,7 +2400,7 @@
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="77">
+      <c r="A57" s="102">
         <v>46130</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -2391,7 +2416,7 @@
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="77">
+      <c r="A58" s="102">
         <v>46131</v>
       </c>
       <c r="B58" s="8" t="s">
@@ -2407,7 +2432,7 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="82">
+      <c r="A59" s="98">
         <v>46132</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -2423,7 +2448,7 @@
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="81"/>
+      <c r="A60" s="100"/>
       <c r="B60" s="8" t="s">
         <v>98</v>
       </c>
@@ -2437,7 +2462,7 @@
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="77">
+      <c r="A61" s="102">
         <v>46134</v>
       </c>
       <c r="B61" s="8" t="s">
@@ -2453,7 +2478,7 @@
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="77">
+      <c r="A62" s="102">
         <v>46136</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -2469,7 +2494,7 @@
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="77">
+      <c r="A63" s="102">
         <v>46140</v>
       </c>
       <c r="B63" s="8" t="s">
@@ -2485,7 +2510,7 @@
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="77">
+      <c r="A64" s="102">
         <v>46144</v>
       </c>
       <c r="B64" s="38" t="s">
@@ -2501,7 +2526,7 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="82">
+      <c r="A65" s="98">
         <v>46145</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -2517,7 +2542,7 @@
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="81"/>
+      <c r="A66" s="100"/>
       <c r="B66" s="8" t="s">
         <v>128</v>
       </c>
@@ -2531,7 +2556,7 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="77">
+      <c r="A67" s="102">
         <v>46147</v>
       </c>
       <c r="B67" s="8" t="s">
@@ -2547,7 +2572,7 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="82">
+      <c r="A68" s="98">
         <v>46148</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -2563,7 +2588,7 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="81"/>
+      <c r="A69" s="100"/>
       <c r="B69" s="8" t="s">
         <v>11</v>
       </c>
@@ -2577,7 +2602,7 @@
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="82">
+      <c r="A70" s="98">
         <v>46151</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -2593,7 +2618,7 @@
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="81"/>
+      <c r="A71" s="100"/>
       <c r="B71" s="8" t="s">
         <v>132</v>
       </c>
@@ -2607,7 +2632,7 @@
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="77">
+      <c r="A72" s="102">
         <v>46154</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -2623,7 +2648,7 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="82">
+      <c r="A73" s="98">
         <v>46155</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -2639,7 +2664,7 @@
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="81"/>
+      <c r="A74" s="100"/>
       <c r="B74" s="8" t="s">
         <v>134</v>
       </c>
@@ -2653,7 +2678,7 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="82">
+      <c r="A75" s="98">
         <v>46158</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -2669,7 +2694,7 @@
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="81"/>
+      <c r="A76" s="100"/>
       <c r="B76" s="8" t="s">
         <v>135</v>
       </c>
@@ -2683,7 +2708,7 @@
       </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="77">
+      <c r="A77" s="102">
         <v>46160</v>
       </c>
       <c r="B77" s="8" t="s">
@@ -2699,7 +2724,7 @@
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="77">
+      <c r="A78" s="102">
         <v>46162</v>
       </c>
       <c r="B78" s="8" t="s">
@@ -2715,7 +2740,7 @@
       </c>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="82">
+      <c r="A79" s="98">
         <v>46165</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -2731,7 +2756,7 @@
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="81"/>
+      <c r="A80" s="100"/>
       <c r="B80" s="8" t="s">
         <v>13</v>
       </c>
@@ -2745,7 +2770,7 @@
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="77">
+      <c r="A81" s="102">
         <v>46175</v>
       </c>
       <c r="B81" s="8" t="s">
@@ -2761,7 +2786,7 @@
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="79"/>
+      <c r="A82" s="99"/>
       <c r="B82" s="8" t="s">
         <v>146</v>
       </c>
@@ -2775,7 +2800,7 @@
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="61"/>
+      <c r="A83" s="100"/>
       <c r="B83" s="8" t="s">
         <v>13</v>
       </c>
@@ -2789,7 +2814,7 @@
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="63">
+      <c r="A84" s="103">
         <v>46176</v>
       </c>
       <c r="B84" s="8" t="s">
@@ -2805,7 +2830,7 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="63">
+      <c r="A85" s="103">
         <v>46177</v>
       </c>
       <c r="B85" s="8" t="s">
@@ -2821,7 +2846,7 @@
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="63">
+      <c r="A86" s="103">
         <v>46178</v>
       </c>
       <c r="B86" s="8" t="s">
@@ -2837,7 +2862,7 @@
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="77">
+      <c r="A87" s="102">
         <v>46180</v>
       </c>
       <c r="B87" s="8" t="s">
@@ -2853,7 +2878,7 @@
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="64">
+      <c r="A88" s="104">
         <v>46182</v>
       </c>
       <c r="B88" s="8" t="s">
@@ -2869,7 +2894,7 @@
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="64">
+      <c r="A89" s="104">
         <v>46183</v>
       </c>
       <c r="B89" s="8" t="s">
@@ -2885,7 +2910,7 @@
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="43"/>
+      <c r="A90" s="101"/>
       <c r="B90" s="8" t="s">
         <v>149</v>
       </c>
@@ -2899,7 +2924,7 @@
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="43"/>
+      <c r="A91" s="101"/>
       <c r="B91" s="8" t="s">
         <v>150</v>
       </c>
@@ -2913,7 +2938,7 @@
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="43"/>
+      <c r="A92" s="101"/>
       <c r="B92" s="8" t="s">
         <v>151</v>
       </c>
@@ -2927,7 +2952,7 @@
       </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="43"/>
+      <c r="A93" s="101"/>
       <c r="B93" s="8" t="s">
         <v>152</v>
       </c>
@@ -2941,7 +2966,7 @@
       </c>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="43"/>
+      <c r="A94" s="101"/>
       <c r="B94" s="8" t="s">
         <v>153</v>
       </c>
@@ -2955,7 +2980,7 @@
       </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="43"/>
+      <c r="A95" s="101"/>
       <c r="B95" s="8" t="s">
         <v>154</v>
       </c>
@@ -2969,7 +2994,7 @@
       </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="77">
+      <c r="A96" s="102">
         <v>46186</v>
       </c>
       <c r="B96" s="12" t="s">
@@ -2985,7 +3010,7 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="77">
+      <c r="A97" s="102">
         <v>46187</v>
       </c>
       <c r="B97" s="12" t="s">
@@ -3001,7 +3026,7 @@
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="77">
+      <c r="A98" s="102">
         <v>46191</v>
       </c>
       <c r="B98" s="12" t="s">
@@ -3017,7 +3042,7 @@
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="77">
+      <c r="A99" s="102">
         <v>46193</v>
       </c>
       <c r="B99" s="12" t="s">
@@ -3033,7 +3058,7 @@
       </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="77">
+      <c r="A100" s="102">
         <v>46196</v>
       </c>
       <c r="B100" s="12" t="s">
@@ -3049,7 +3074,7 @@
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="77">
+      <c r="A101" s="102">
         <v>46197</v>
       </c>
       <c r="B101" s="12" t="s">
@@ -3065,7 +3090,7 @@
       </c>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="63">
+      <c r="A102" s="103">
         <v>46200</v>
       </c>
       <c r="B102" s="12" t="s">
@@ -3081,7 +3106,7 @@
       </c>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="63">
+      <c r="A103" s="103">
         <v>46203</v>
       </c>
       <c r="B103" s="8" t="s">
@@ -3111,31 +3136,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-  </mergeCells>
   <pageMargins left="1" right="0.5" top="0.75" bottom="0.75" header="0.30972222222222201" footer="0.30972222222222201"/>
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
@@ -3160,13 +3160,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -3195,10 +3195,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="85" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="83"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="35">
         <f>'Apr''26'!E15</f>
         <v>6032500</v>
@@ -3232,7 +3232,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="81"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -3345,10 +3345,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="87"/>
+      <c r="B15" s="89"/>
       <c r="C15" s="46">
         <f>SUM(C4:C14)</f>
         <v>6032500</v>
@@ -3374,10 +3374,10 @@
       <c r="E16" s="50"/>
     </row>
     <row r="17" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="90" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="88"/>
+      <c r="B17" s="90"/>
       <c r="C17" s="51">
         <f>C15-C4</f>
         <v>0</v>
@@ -3397,10 +3397,10 @@
       <c r="E18" s="50"/>
     </row>
     <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="89" t="s">
+      <c r="A19" s="91" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="89"/>
+      <c r="B19" s="91"/>
       <c r="C19" s="54">
         <f>D15</f>
         <v>0</v>
@@ -5235,12 +5235,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="94" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
     </row>
     <row r="2" spans="1:4" ht="18.75">
       <c r="A2" s="1" t="s">
@@ -5419,12 +5419,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="94" t="s">
         <v>175</v>
       </c>
-      <c r="B20" s="92"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
+      <c r="B20" s="94"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
     </row>
     <row r="21" spans="1:4" ht="18.75">
       <c r="A21" s="1" t="s">
@@ -5561,13 +5561,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -5596,10 +5596,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="83"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="35">
         <v>-334000</v>
       </c>
@@ -5627,7 +5627,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A6" s="80"/>
+      <c r="A6" s="84"/>
       <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
@@ -5642,7 +5642,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="81"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="8" t="s">
         <v>10</v>
       </c>
@@ -5691,7 +5691,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A10" s="81"/>
+      <c r="A10" s="83"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
@@ -5723,7 +5723,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A12" s="81"/>
+      <c r="A12" s="83"/>
       <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
@@ -5772,7 +5772,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A15" s="81"/>
+      <c r="A15" s="83"/>
       <c r="B15" s="8" t="s">
         <v>18</v>
       </c>
@@ -5804,7 +5804,7 @@
       <c r="G16" s="42"/>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A17" s="81"/>
+      <c r="A17" s="83"/>
       <c r="B17" s="8" t="s">
         <v>11</v>
       </c>
@@ -5902,7 +5902,7 @@
       </c>
     </row>
     <row r="22" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A22" s="80"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="8" t="s">
         <v>24</v>
       </c>
@@ -5922,7 +5922,7 @@
       </c>
     </row>
     <row r="23" spans="1:256" s="20" customFormat="1" ht="18" customHeight="1">
-      <c r="A23" s="81"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="8" t="s">
         <v>11</v>
       </c>
@@ -5942,10 +5942,10 @@
       </c>
     </row>
     <row r="24" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="87"/>
+      <c r="B24" s="89"/>
       <c r="C24" s="46">
         <f>SUM(C4:C23)</f>
         <v>3212000</v>
@@ -5971,10 +5971,10 @@
       <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="88" t="s">
+      <c r="A26" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="88"/>
+      <c r="B26" s="90"/>
       <c r="C26" s="51">
         <f>C24-C4</f>
         <v>3546000</v>
@@ -5994,10 +5994,10 @@
       <c r="E27" s="50"/>
     </row>
     <row r="28" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="89"/>
+      <c r="B28" s="91"/>
       <c r="C28" s="54">
         <f>D24</f>
         <v>1200000</v>
@@ -7837,13 +7837,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -7872,10 +7872,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="83"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="35">
         <f>'Jan''26'!E24</f>
         <v>2012000</v>
@@ -7938,7 +7938,7 @@
       <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A8" s="81"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="8" t="s">
         <v>40</v>
       </c>
@@ -8004,7 +8004,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="81"/>
+      <c r="A12" s="83"/>
       <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
@@ -8090,7 +8090,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="81"/>
+      <c r="A16" s="83"/>
       <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
@@ -8110,10 +8110,10 @@
       </c>
     </row>
     <row r="17" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="87" t="s">
+      <c r="A17" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="87"/>
+      <c r="B17" s="89"/>
       <c r="C17" s="46">
         <f>SUM(C4:C16)</f>
         <v>5139000</v>
@@ -8139,10 +8139,10 @@
       <c r="E18" s="50"/>
     </row>
     <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="88" t="s">
+      <c r="A19" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="88"/>
+      <c r="B19" s="90"/>
       <c r="C19" s="51">
         <f>C17-C4</f>
         <v>3127000</v>
@@ -8162,10 +8162,10 @@
       <c r="E20" s="50"/>
     </row>
     <row r="21" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A21" s="89" t="s">
+      <c r="A21" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="89"/>
+      <c r="B21" s="91"/>
       <c r="C21" s="54">
         <f>D17</f>
         <v>1141000</v>
@@ -9999,24 +9999,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
     </row>
     <row r="2" spans="1:6" ht="21" customHeight="1">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
     </row>
     <row r="3" spans="1:6" ht="6.95" customHeight="1"/>
     <row r="4" spans="1:6" s="66" customFormat="1" ht="21" customHeight="1">
@@ -10668,10 +10668,10 @@
       <c r="F40" s="71"/>
     </row>
     <row r="41" spans="1:6" ht="21" customHeight="1">
-      <c r="A41" s="91" t="s">
+      <c r="A41" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="91"/>
+      <c r="B41" s="93"/>
       <c r="C41" s="73">
         <f>SUM(C5:C40)</f>
         <v>2564000</v>
@@ -10712,13 +10712,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:7" ht="18.75">
       <c r="A2" s="27" t="s">
@@ -10747,10 +10747,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="83"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="35">
         <f>'Feb''26'!E17</f>
         <v>3998000</v>
@@ -10813,7 +10813,7 @@
       <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A8" s="81"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="8" t="s">
         <v>97</v>
       </c>
@@ -10913,7 +10913,7 @@
       <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A14" s="81"/>
+      <c r="A14" s="83"/>
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
@@ -10928,7 +10928,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A15" s="84">
+      <c r="A15" s="86">
         <v>46101</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -10945,7 +10945,7 @@
       <c r="G15" s="42"/>
     </row>
     <row r="16" spans="1:7" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A16" s="84"/>
+      <c r="A16" s="86"/>
       <c r="B16" s="8" t="s">
         <v>103</v>
       </c>
@@ -10960,7 +10960,7 @@
       <c r="G16" s="42"/>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A17" s="80">
+      <c r="A17" s="84">
         <v>46107</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -10977,7 +10977,7 @@
       <c r="G17" s="42"/>
     </row>
     <row r="18" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A18" s="80"/>
+      <c r="A18" s="84"/>
       <c r="B18" s="8" t="s">
         <v>105</v>
       </c>
@@ -10992,7 +10992,7 @@
       <c r="G18" s="42"/>
     </row>
     <row r="19" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A19" s="81"/>
+      <c r="A19" s="83"/>
       <c r="B19" s="8" t="s">
         <v>106</v>
       </c>
@@ -11009,7 +11009,7 @@
       </c>
     </row>
     <row r="20" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A20" s="80">
+      <c r="A20" s="84">
         <v>46109</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -11031,7 +11031,7 @@
       </c>
     </row>
     <row r="21" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A21" s="81"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="8" t="s">
         <v>104</v>
       </c>
@@ -11095,7 +11095,7 @@
       </c>
     </row>
     <row r="24" spans="1:256" s="20" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A24" s="81"/>
+      <c r="A24" s="83"/>
       <c r="B24" s="8" t="s">
         <v>110</v>
       </c>
@@ -11115,10 +11115,10 @@
       </c>
     </row>
     <row r="25" spans="1:256" s="21" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A25" s="87" t="s">
+      <c r="A25" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="87"/>
+      <c r="B25" s="89"/>
       <c r="C25" s="46">
         <f>SUM(C4:C24)</f>
         <v>7845000</v>
@@ -11144,10 +11144,10 @@
       <c r="E26" s="50"/>
     </row>
     <row r="27" spans="1:256" s="22" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="90" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="88"/>
+      <c r="B27" s="90"/>
       <c r="C27" s="51">
         <f>C25-C4</f>
         <v>3847000</v>
@@ -11167,10 +11167,10 @@
       <c r="E28" s="50"/>
     </row>
     <row r="29" spans="1:256" s="22" customFormat="1" ht="18.95" customHeight="1">
-      <c r="A29" s="89" t="s">
+      <c r="A29" s="91" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="89"/>
+      <c r="B29" s="91"/>
       <c r="C29" s="54">
         <f>D25</f>
         <v>2689500</v>
@@ -13010,13 +13010,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -13045,10 +13045,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="83"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="35">
         <f>'Mar''26'!E25</f>
         <v>5155500</v>
@@ -13167,7 +13167,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="81"/>
+      <c r="A11" s="83"/>
       <c r="B11" s="8" t="s">
         <v>98</v>
       </c>
@@ -13253,10 +13253,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="89" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="87"/>
+      <c r="B15" s="89"/>
       <c r="C15" s="46">
         <f>SUM(C4:C14)</f>
         <v>6784500</v>
@@ -13282,10 +13282,10 @@
       <c r="E16" s="50"/>
     </row>
     <row r="17" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="88"/>
+      <c r="B17" s="90"/>
       <c r="C17" s="51">
         <f>C15-C4</f>
         <v>1629000</v>
@@ -13305,10 +13305,10 @@
       <c r="E18" s="50"/>
     </row>
     <row r="19" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A19" s="89" t="s">
+      <c r="A19" s="91" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="89"/>
+      <c r="B19" s="91"/>
       <c r="C19" s="54">
         <f>D15</f>
         <v>752000</v>
@@ -15143,13 +15143,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -15178,10 +15178,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="85" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="83"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="35">
         <f>'Apr''26'!E15</f>
         <v>6032500</v>
@@ -15227,7 +15227,7 @@
       <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="81"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="8" t="s">
         <v>128</v>
       </c>
@@ -15276,7 +15276,7 @@
       <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A10" s="81"/>
+      <c r="A10" s="83"/>
       <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
@@ -15308,7 +15308,7 @@
       <c r="G11" s="42"/>
     </row>
     <row r="12" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="81"/>
+      <c r="A12" s="83"/>
       <c r="B12" s="8" t="s">
         <v>132</v>
       </c>
@@ -15357,7 +15357,7 @@
       <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="81"/>
+      <c r="A15" s="83"/>
       <c r="B15" s="8" t="s">
         <v>134</v>
       </c>
@@ -15388,7 +15388,7 @@
       </c>
     </row>
     <row r="17" spans="1:256" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A17" s="81"/>
+      <c r="A17" s="83"/>
       <c r="B17" s="8" t="s">
         <v>135</v>
       </c>
@@ -15474,7 +15474,7 @@
       </c>
     </row>
     <row r="21" spans="1:256" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A21" s="81"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="8" t="s">
         <v>13</v>
       </c>
@@ -15494,10 +15494,10 @@
       </c>
     </row>
     <row r="22" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A22" s="87" t="s">
+      <c r="A22" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="87"/>
+      <c r="B22" s="89"/>
       <c r="C22" s="46">
         <f>SUM(C4:C21)</f>
         <v>8832500</v>
@@ -15523,10 +15523,10 @@
       <c r="E23" s="50"/>
     </row>
     <row r="24" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="90" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="88"/>
+      <c r="B24" s="90"/>
       <c r="C24" s="51">
         <f>C22-C4</f>
         <v>2800000</v>
@@ -15546,10 +15546,10 @@
       <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="91" t="s">
         <v>138</v>
       </c>
-      <c r="B26" s="89"/>
+      <c r="B26" s="91"/>
       <c r="C26" s="54">
         <f>D22</f>
         <v>2495500</v>
@@ -17389,13 +17389,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -17424,10 +17424,10 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="85" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="83"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="35">
         <f>'Mei''26'!E22</f>
         <v>6337000</v>
@@ -17439,7 +17439,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" s="19" customFormat="1" ht="21" customHeight="1">
-      <c r="A5" s="78">
+      <c r="A5" s="77">
         <v>46175</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -17456,7 +17456,7 @@
       <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A6" s="79"/>
+      <c r="A6" s="78"/>
       <c r="B6" s="8" t="s">
         <v>146</v>
       </c>
@@ -17823,7 +17823,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A27" s="78">
+      <c r="A27" s="77">
         <v>46203</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -17865,10 +17865,10 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="20" customFormat="1" ht="21" customHeight="1">
-      <c r="A29" s="87" t="s">
+      <c r="A29" s="89" t="s">
         <v>162</v>
       </c>
-      <c r="B29" s="87"/>
+      <c r="B29" s="89"/>
       <c r="C29" s="46">
         <f>SUM(C4:C28)</f>
         <v>12356000</v>
@@ -17895,10 +17895,10 @@
       <c r="E30" s="50"/>
     </row>
     <row r="31" spans="1:8" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A31" s="88" t="s">
+      <c r="A31" s="90" t="s">
         <v>163</v>
       </c>
-      <c r="B31" s="88"/>
+      <c r="B31" s="90"/>
       <c r="C31" s="51">
         <f>C29-C4</f>
         <v>6019000</v>
@@ -17918,10 +17918,10 @@
       <c r="E32" s="50"/>
     </row>
     <row r="33" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A33" s="89" t="s">
+      <c r="A33" s="91" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="89"/>
+      <c r="B33" s="91"/>
       <c r="C33" s="54">
         <f>D29</f>
         <v>2722000</v>
@@ -19765,13 +19765,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -19800,10 +19800,10 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="18" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="85" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="83"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="35">
         <f>'Juni''26'!E29</f>
         <v>9634000</v>
@@ -20060,10 +20060,10 @@
       </c>
     </row>
     <row r="24" spans="1:256" s="21" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="89" t="s">
         <v>167</v>
       </c>
-      <c r="B24" s="87"/>
+      <c r="B24" s="89"/>
       <c r="C24" s="46">
         <f>SUM(C4:C23)</f>
         <v>9744000</v>
@@ -20089,10 +20089,10 @@
       <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A26" s="88" t="s">
+      <c r="A26" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="88"/>
+      <c r="B26" s="90"/>
       <c r="C26" s="51">
         <f>C24-C4</f>
         <v>110000</v>
@@ -20112,10 +20112,10 @@
       <c r="E27" s="50"/>
     </row>
     <row r="28" spans="1:256" s="22" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="91" t="s">
         <v>169</v>
       </c>
-      <c r="B28" s="89"/>
+      <c r="B28" s="91"/>
       <c r="C28" s="54">
         <f>D24</f>
         <v>0</v>
